--- a/app/static/storage/June 2026 MTC BUENAVISTA, AGUSAN DEL NORTE.xlsx
+++ b/app/static/storage/June 2026 MTC BUENAVISTA, AGUSAN DEL NORTE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PyZar\app\static\storage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07244ECC-B659-48AE-916E-2C00B1D6B327}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C354453-22FF-4932-9B30-A01E2D053F3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="363" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="363" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Page 1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Page 1'!$A$1:$O$31</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Page 2'!$A$1:$L$31</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'Page 3'!$A$1:$G$32</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Page 3'!$A$1:$G$30</definedName>
   </definedNames>
   <calcPr calcId="191029" refMode="R1C1"/>
   <extLst>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="237">
   <si>
     <t>SC FORM MRC-FLC UPDATED JANUARY 2018 VER. 2.0</t>
   </si>
@@ -683,24 +683,6 @@
     <t xml:space="preserve">                  WE  HEREBY  DECLARE  UNDER  OATH  THAT  THE  INFORMATION  IN  THIS  MONTHLY  REPORT  IS  TRUE  AND  CORRECT OF OUR OWN PERSONAL KNOWLEDGE,  PURSUANT TO THE PROVISIONS OF EXISTING RULES/ ADMINISTRATIVE CIRCULARS.</t>
   </si>
   <si>
-    <t>HON. SAIDAMEN M. GANIA</t>
-  </si>
-  <si>
-    <t>NASHRIA U. IMAM    09126085463</t>
-  </si>
-  <si>
-    <t>JUDGE</t>
-  </si>
-  <si>
-    <t>OIC - CLERK OF COURT II</t>
-  </si>
-  <si>
-    <t>(Presiding / Acting / Assisting Judge/ Pairing Judge)</t>
-  </si>
-  <si>
-    <t>(Clerk of Court/Branch Clerk of Court/OIC)</t>
-  </si>
-  <si>
     <t>Administrative Order/Administrative Matter No. ___________ dated _______________.</t>
   </si>
   <si>
@@ -719,21 +701,9 @@
     <t xml:space="preserve">day of </t>
   </si>
   <si>
-    <t>January</t>
-  </si>
-  <si>
     <t>at</t>
   </si>
   <si>
-    <t>2024</t>
-  </si>
-  <si>
-    <t>.</t>
-  </si>
-  <si>
-    <t>HON. MARIGEL S. DAGANI-HUGO</t>
-  </si>
-  <si>
     <t>ADMINSTERING OFFICER</t>
   </si>
   <si>
@@ -756,17 +726,48 @@
   </si>
   <si>
     <t>PRINT ALL SHEETS IN FOLIO SIZE</t>
+  </si>
+  <si>
+    <t>HRS. OF MAGDALINA TIMTIM NAMELY: EVANGELINE A. ALEGADO, NILDA M. ALEGADO, ZENAIDA A. ANDOY, ALBERTO BETARMOS, MIGUEL D. YONSON, FLORENCIO A. NAKILA, PACITA F. MARTINEZ, MARCELINA A. AMPO, DONATO T. ALEGADO, EMILIO T. ALEGADO ALL REP. BY RICARDO A. TAC-AN VS. CORAZON BUAL-CUYNO, ROEL B. ALNGOG, EVANGELINE A. DUMAGAN, SPS. RAMMEL &amp; MERIEL AUTOR, &amp; FICCO, &amp; THE REGISTRY OF DEEDS OF AGUSAN DEL NORTE</t>
+  </si>
+  <si>
+    <t>HON.SAIDAMEN M. GANIA</t>
+  </si>
+  <si>
+    <t>Not yet due</t>
+  </si>
+  <si>
+    <t>HRS. OF FLOCERPIDA A. SAAGUNDO, REP BY FLORLITA SAAGUNDO ASIO VS. TIRSO CANATOY, JR.</t>
+  </si>
+  <si>
+    <t>GHAIZAR A. BAUTISTA - 09277294457</t>
+  </si>
+  <si>
+    <t>CLERK  II</t>
+  </si>
+  <si>
+    <t>HON. SAIDAMEN M. GANIA - 09177983808</t>
+  </si>
+  <si>
+    <t>PRESIDING JUDGE</t>
+  </si>
+  <si>
+    <t>July 2026</t>
+  </si>
+  <si>
+    <t>Buenavista, Agusan Del Norte, Philippines</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="mm/dd/yy;@"/>
     <numFmt numFmtId="165" formatCode="mm/dd/yy"/>
+    <numFmt numFmtId="166" formatCode="[$-3409]mmm\ dd\,\ yyyy;@"/>
   </numFmts>
-  <fonts count="31" x14ac:knownFonts="1">
+  <fonts count="30" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -939,12 +940,6 @@
       <name val="Arial Narrow"/>
       <family val="2"/>
     </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FFFF0000"/>
-      <name val="Arial Narrow"/>
-      <family val="2"/>
-    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -984,7 +979,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="130">
+  <borders count="131">
     <border>
       <left/>
       <right/>
@@ -2653,11 +2648,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="333">
+  <cellXfs count="337">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -2981,15 +2985,6 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="0" borderId="58" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -3247,6 +3242,93 @@
     <xf numFmtId="3" fontId="29" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="100" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="22" fillId="0" borderId="58" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="58" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="130" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="63" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="63" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -3262,6 +3344,14 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="81" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="120" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="83" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="122" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="76" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3291,10 +3381,16 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="81" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="120" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="109" xfId="0" applyBorder="1"/>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="77" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="75" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3302,33 +3398,19 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="121" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="82" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="10" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="109" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="118" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="119" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="83" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="122" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="73" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="111" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="73" xfId="0" applyBorder="1"/>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="77" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="84" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3340,25 +3422,41 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="127" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="128" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="85" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="125" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="126" xfId="0" applyBorder="1"/>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="78" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="78" xfId="0" applyBorder="1"/>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="87" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="78" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="85" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="125" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="126" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="88" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="112" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="88" xfId="0" applyBorder="1"/>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="78" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="89" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="62" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="129" xfId="0" applyBorder="1"/>
+    <xf numFmtId="1" fontId="20" fillId="0" borderId="89" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="89" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="20" fillId="0" borderId="89" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3366,82 +3464,10 @@
     <xf numFmtId="164" fontId="20" fillId="0" borderId="89" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="89" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="62" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="129" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="20" fillId="0" borderId="89" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="89" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="63" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="63" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -3458,21 +3484,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="3" fontId="30" fillId="0" borderId="96" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="3" fontId="30" fillId="0" borderId="95" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="3" fontId="30" fillId="0" borderId="100" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="3" fontId="30" fillId="0" borderId="99" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3960,23 +3973,23 @@
       <c r="O2" s="4"/>
     </row>
     <row r="3" spans="1:20" s="8" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="254" t="s">
+      <c r="A3" s="282" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="255"/>
-      <c r="C3" s="255"/>
-      <c r="D3" s="255"/>
-      <c r="E3" s="255"/>
-      <c r="F3" s="255"/>
-      <c r="G3" s="255"/>
-      <c r="H3" s="255"/>
-      <c r="I3" s="255"/>
-      <c r="J3" s="255"/>
-      <c r="K3" s="255"/>
-      <c r="L3" s="255"/>
-      <c r="M3" s="255"/>
-      <c r="N3" s="255"/>
-      <c r="O3" s="255"/>
+      <c r="B3" s="283"/>
+      <c r="C3" s="283"/>
+      <c r="D3" s="283"/>
+      <c r="E3" s="283"/>
+      <c r="F3" s="283"/>
+      <c r="G3" s="283"/>
+      <c r="H3" s="283"/>
+      <c r="I3" s="283"/>
+      <c r="J3" s="283"/>
+      <c r="K3" s="283"/>
+      <c r="L3" s="283"/>
+      <c r="M3" s="283"/>
+      <c r="N3" s="283"/>
+      <c r="O3" s="283"/>
       <c r="P3" s="6"/>
       <c r="Q3" s="6"/>
       <c r="R3" s="6"/>
@@ -3984,23 +3997,23 @@
       <c r="T3" s="7"/>
     </row>
     <row r="4" spans="1:20" s="11" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="264" t="s">
+      <c r="A4" s="287" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="255"/>
-      <c r="C4" s="255"/>
-      <c r="D4" s="255"/>
-      <c r="E4" s="255"/>
-      <c r="F4" s="255"/>
-      <c r="G4" s="255"/>
-      <c r="H4" s="255"/>
-      <c r="I4" s="255"/>
-      <c r="J4" s="255"/>
-      <c r="K4" s="255"/>
-      <c r="L4" s="255"/>
-      <c r="M4" s="255"/>
-      <c r="N4" s="255"/>
-      <c r="O4" s="255"/>
+      <c r="B4" s="283"/>
+      <c r="C4" s="283"/>
+      <c r="D4" s="283"/>
+      <c r="E4" s="283"/>
+      <c r="F4" s="283"/>
+      <c r="G4" s="283"/>
+      <c r="H4" s="283"/>
+      <c r="I4" s="283"/>
+      <c r="J4" s="283"/>
+      <c r="K4" s="283"/>
+      <c r="L4" s="283"/>
+      <c r="M4" s="283"/>
+      <c r="N4" s="283"/>
+      <c r="O4" s="283"/>
       <c r="P4" s="9"/>
       <c r="Q4" s="9"/>
       <c r="R4" s="9"/>
@@ -4025,62 +4038,62 @@
       <c r="O5" s="12"/>
     </row>
     <row r="6" spans="1:20" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="248" t="s">
+      <c r="A6" s="276" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="249"/>
-      <c r="C6" s="249"/>
-      <c r="D6" s="250"/>
-      <c r="E6" s="266" t="s">
+      <c r="B6" s="277"/>
+      <c r="C6" s="277"/>
+      <c r="D6" s="278"/>
+      <c r="E6" s="288" t="s">
         <v>5</v>
       </c>
-      <c r="F6" s="267"/>
-      <c r="G6" s="267"/>
-      <c r="H6" s="267"/>
-      <c r="I6" s="267"/>
-      <c r="J6" s="267"/>
-      <c r="K6" s="267"/>
-      <c r="L6" s="267"/>
-      <c r="M6" s="267"/>
-      <c r="N6" s="267"/>
-      <c r="O6" s="236"/>
+      <c r="F6" s="289"/>
+      <c r="G6" s="289"/>
+      <c r="H6" s="289"/>
+      <c r="I6" s="289"/>
+      <c r="J6" s="289"/>
+      <c r="K6" s="289"/>
+      <c r="L6" s="289"/>
+      <c r="M6" s="289"/>
+      <c r="N6" s="289"/>
+      <c r="O6" s="260"/>
     </row>
     <row r="7" spans="1:20" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="251"/>
-      <c r="B7" s="252"/>
-      <c r="C7" s="252"/>
-      <c r="D7" s="253"/>
-      <c r="E7" s="273" t="s">
+      <c r="A7" s="279"/>
+      <c r="B7" s="280"/>
+      <c r="C7" s="280"/>
+      <c r="D7" s="281"/>
+      <c r="E7" s="298" t="s">
         <v>6</v>
       </c>
-      <c r="F7" s="238" t="s">
+      <c r="F7" s="262" t="s">
         <v>7</v>
       </c>
-      <c r="G7" s="238" t="s">
+      <c r="G7" s="262" t="s">
         <v>8</v>
       </c>
-      <c r="H7" s="261" t="s">
+      <c r="H7" s="291" t="s">
         <v>9</v>
       </c>
-      <c r="I7" s="261" t="s">
+      <c r="I7" s="291" t="s">
         <v>10</v>
       </c>
-      <c r="J7" s="261" t="s">
+      <c r="J7" s="291" t="s">
         <v>11</v>
       </c>
-      <c r="K7" s="238" t="s">
+      <c r="K7" s="262" t="s">
         <v>12</v>
       </c>
-      <c r="L7" s="238" t="s">
+      <c r="L7" s="262" t="s">
         <v>13</v>
       </c>
-      <c r="M7" s="261" t="s">
+      <c r="M7" s="291" t="s">
         <v>14</v>
       </c>
-      <c r="N7" s="242" t="s">
+      <c r="N7" s="270" t="s">
         <v>15</v>
       </c>
-      <c r="O7" s="276" t="s">
+      <c r="O7" s="290" t="s">
         <v>16</v>
       </c>
     </row>
@@ -4091,17 +4104,17 @@
       <c r="B8" s="14"/>
       <c r="C8" s="14"/>
       <c r="D8" s="15"/>
-      <c r="E8" s="274"/>
-      <c r="F8" s="239"/>
-      <c r="G8" s="239"/>
-      <c r="H8" s="239"/>
-      <c r="I8" s="239"/>
-      <c r="J8" s="239"/>
-      <c r="K8" s="239"/>
-      <c r="L8" s="239"/>
-      <c r="M8" s="239"/>
-      <c r="N8" s="243"/>
-      <c r="O8" s="258"/>
+      <c r="E8" s="299"/>
+      <c r="F8" s="263"/>
+      <c r="G8" s="263"/>
+      <c r="H8" s="263"/>
+      <c r="I8" s="263"/>
+      <c r="J8" s="263"/>
+      <c r="K8" s="263"/>
+      <c r="L8" s="263"/>
+      <c r="M8" s="263"/>
+      <c r="N8" s="271"/>
+      <c r="O8" s="286"/>
     </row>
     <row r="9" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="16" t="s">
@@ -4112,86 +4125,86 @@
       <c r="D9" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="E9" s="274"/>
-      <c r="F9" s="239"/>
-      <c r="G9" s="239"/>
-      <c r="H9" s="239"/>
-      <c r="I9" s="239"/>
-      <c r="J9" s="239"/>
-      <c r="K9" s="239"/>
-      <c r="L9" s="239"/>
-      <c r="M9" s="239"/>
-      <c r="N9" s="243"/>
-      <c r="O9" s="258"/>
+      <c r="E9" s="299"/>
+      <c r="F9" s="263"/>
+      <c r="G9" s="263"/>
+      <c r="H9" s="263"/>
+      <c r="I9" s="263"/>
+      <c r="J9" s="263"/>
+      <c r="K9" s="263"/>
+      <c r="L9" s="263"/>
+      <c r="M9" s="263"/>
+      <c r="N9" s="271"/>
+      <c r="O9" s="286"/>
     </row>
     <row r="10" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="245" t="s">
+      <c r="A10" s="273" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="246"/>
-      <c r="C10" s="247"/>
+      <c r="B10" s="274"/>
+      <c r="C10" s="275"/>
       <c r="D10" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="E10" s="274"/>
-      <c r="F10" s="239"/>
-      <c r="G10" s="239"/>
-      <c r="H10" s="239"/>
-      <c r="I10" s="239"/>
-      <c r="J10" s="239"/>
-      <c r="K10" s="239"/>
-      <c r="L10" s="239"/>
-      <c r="M10" s="239"/>
-      <c r="N10" s="243"/>
-      <c r="O10" s="258"/>
+      <c r="E10" s="299"/>
+      <c r="F10" s="263"/>
+      <c r="G10" s="263"/>
+      <c r="H10" s="263"/>
+      <c r="I10" s="263"/>
+      <c r="J10" s="263"/>
+      <c r="K10" s="263"/>
+      <c r="L10" s="263"/>
+      <c r="M10" s="263"/>
+      <c r="N10" s="271"/>
+      <c r="O10" s="286"/>
     </row>
     <row r="11" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="245" t="s">
+      <c r="A11" s="273" t="s">
         <v>22</v>
       </c>
-      <c r="B11" s="246"/>
-      <c r="C11" s="247"/>
+      <c r="B11" s="274"/>
+      <c r="C11" s="275"/>
       <c r="D11" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="E11" s="274"/>
-      <c r="F11" s="239"/>
-      <c r="G11" s="239"/>
-      <c r="H11" s="239"/>
-      <c r="I11" s="239"/>
-      <c r="J11" s="239"/>
-      <c r="K11" s="239"/>
-      <c r="L11" s="239"/>
-      <c r="M11" s="239"/>
-      <c r="N11" s="243"/>
-      <c r="O11" s="258"/>
+      <c r="E11" s="299"/>
+      <c r="F11" s="263"/>
+      <c r="G11" s="263"/>
+      <c r="H11" s="263"/>
+      <c r="I11" s="263"/>
+      <c r="J11" s="263"/>
+      <c r="K11" s="263"/>
+      <c r="L11" s="263"/>
+      <c r="M11" s="263"/>
+      <c r="N11" s="271"/>
+      <c r="O11" s="286"/>
     </row>
     <row r="12" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="245" t="s">
+      <c r="A12" s="273" t="s">
         <v>24</v>
       </c>
-      <c r="B12" s="246"/>
-      <c r="C12" s="247"/>
+      <c r="B12" s="274"/>
+      <c r="C12" s="275"/>
       <c r="D12" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="E12" s="275"/>
-      <c r="F12" s="240"/>
-      <c r="G12" s="240"/>
-      <c r="H12" s="240"/>
-      <c r="I12" s="240"/>
-      <c r="J12" s="240"/>
-      <c r="K12" s="240"/>
-      <c r="L12" s="240"/>
-      <c r="M12" s="240"/>
-      <c r="N12" s="244"/>
-      <c r="O12" s="253"/>
+      <c r="E12" s="300"/>
+      <c r="F12" s="264"/>
+      <c r="G12" s="264"/>
+      <c r="H12" s="264"/>
+      <c r="I12" s="264"/>
+      <c r="J12" s="264"/>
+      <c r="K12" s="264"/>
+      <c r="L12" s="264"/>
+      <c r="M12" s="264"/>
+      <c r="N12" s="272"/>
+      <c r="O12" s="281"/>
     </row>
     <row r="13" spans="1:20" s="25" customFormat="1" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="256"/>
-      <c r="B13" s="257"/>
-      <c r="C13" s="257"/>
-      <c r="D13" s="258"/>
+      <c r="A13" s="284"/>
+      <c r="B13" s="285"/>
+      <c r="C13" s="285"/>
+      <c r="D13" s="286"/>
       <c r="E13" s="20" t="s">
         <v>26</v>
       </c>
@@ -4233,41 +4246,41 @@
       <c r="B14" s="27" t="s">
         <v>38</v>
       </c>
-      <c r="C14" s="241" t="s">
+      <c r="C14" s="265" t="s">
         <v>39</v>
       </c>
-      <c r="D14" s="236"/>
-      <c r="E14" s="212">
-        <v>0</v>
-      </c>
-      <c r="F14" s="212">
-        <v>0</v>
-      </c>
-      <c r="G14" s="212">
+      <c r="D14" s="260"/>
+      <c r="E14" s="209">
+        <v>0</v>
+      </c>
+      <c r="F14" s="209">
+        <v>0</v>
+      </c>
+      <c r="G14" s="209">
         <v>12</v>
       </c>
-      <c r="H14" s="212">
-        <v>0</v>
-      </c>
-      <c r="I14" s="212">
+      <c r="H14" s="209">
+        <v>0</v>
+      </c>
+      <c r="I14" s="209">
         <v>1</v>
       </c>
-      <c r="J14" s="212">
+      <c r="J14" s="209">
         <v>2</v>
       </c>
-      <c r="K14" s="212">
-        <v>0</v>
-      </c>
-      <c r="L14" s="212">
-        <v>0</v>
-      </c>
-      <c r="M14" s="212">
-        <v>0</v>
-      </c>
-      <c r="N14" s="212">
+      <c r="K14" s="209">
+        <v>0</v>
+      </c>
+      <c r="L14" s="209">
+        <v>0</v>
+      </c>
+      <c r="M14" s="209">
+        <v>0</v>
+      </c>
+      <c r="N14" s="209">
         <v>6</v>
       </c>
-      <c r="O14" s="224">
+      <c r="O14" s="221">
         <f t="shared" ref="O14:O25" si="0">SUM(E14:N14)</f>
         <v>21</v>
       </c>
@@ -4279,185 +4292,185 @@
       <c r="B15" s="30" t="s">
         <v>40</v>
       </c>
-      <c r="C15" s="237" t="s">
+      <c r="C15" s="261" t="s">
         <v>41</v>
       </c>
-      <c r="D15" s="236"/>
-      <c r="E15" s="212">
+      <c r="D15" s="260"/>
+      <c r="E15" s="209">
         <f t="shared" ref="E15:N15" si="1">SUM(E16:E18)</f>
         <v>0</v>
       </c>
-      <c r="F15" s="217">
+      <c r="F15" s="214">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G15" s="217">
+      <c r="G15" s="214">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H15" s="217">
+      <c r="H15" s="214">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I15" s="217">
+      <c r="I15" s="214">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J15" s="217">
+      <c r="J15" s="214">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K15" s="217">
+      <c r="K15" s="214">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L15" s="217">
+      <c r="L15" s="214">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="M15" s="217">
+      <c r="M15" s="214">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N15" s="221">
+      <c r="N15" s="218">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="O15" s="225">
+      <c r="O15" s="222">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:20" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="268" t="s">
+      <c r="A16" s="295" t="s">
         <v>42</v>
       </c>
       <c r="B16" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="C16" s="259" t="s">
+      <c r="C16" s="266" t="s">
         <v>44</v>
       </c>
-      <c r="D16" s="260"/>
-      <c r="E16" s="213">
-        <v>0</v>
-      </c>
-      <c r="F16" s="218">
-        <v>0</v>
-      </c>
-      <c r="G16" s="218">
-        <v>0</v>
-      </c>
-      <c r="H16" s="218">
-        <v>0</v>
-      </c>
-      <c r="I16" s="218">
-        <v>0</v>
-      </c>
-      <c r="J16" s="218">
-        <v>0</v>
-      </c>
-      <c r="K16" s="218">
-        <v>0</v>
-      </c>
-      <c r="L16" s="218">
-        <v>0</v>
-      </c>
-      <c r="M16" s="218">
-        <v>0</v>
-      </c>
-      <c r="N16" s="222">
+      <c r="D16" s="267"/>
+      <c r="E16" s="210">
+        <v>0</v>
+      </c>
+      <c r="F16" s="215">
+        <v>0</v>
+      </c>
+      <c r="G16" s="215">
+        <v>0</v>
+      </c>
+      <c r="H16" s="215">
+        <v>0</v>
+      </c>
+      <c r="I16" s="215">
+        <v>0</v>
+      </c>
+      <c r="J16" s="215">
+        <v>0</v>
+      </c>
+      <c r="K16" s="215">
+        <v>0</v>
+      </c>
+      <c r="L16" s="215">
+        <v>0</v>
+      </c>
+      <c r="M16" s="215">
+        <v>0</v>
+      </c>
+      <c r="N16" s="219">
         <v>3</v>
       </c>
-      <c r="O16" s="226">
+      <c r="O16" s="223">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
     <row r="17" spans="1:15" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="269"/>
+      <c r="A17" s="296"/>
       <c r="B17" s="32" t="s">
         <v>45</v>
       </c>
-      <c r="C17" s="262" t="s">
+      <c r="C17" s="292" t="s">
         <v>46</v>
       </c>
-      <c r="D17" s="263"/>
-      <c r="E17" s="213">
-        <v>0</v>
-      </c>
-      <c r="F17" s="218">
-        <v>0</v>
-      </c>
-      <c r="G17" s="218">
-        <v>0</v>
-      </c>
-      <c r="H17" s="218">
-        <v>0</v>
-      </c>
-      <c r="I17" s="218">
-        <v>0</v>
-      </c>
-      <c r="J17" s="218">
-        <v>0</v>
-      </c>
-      <c r="K17" s="218">
-        <v>0</v>
-      </c>
-      <c r="L17" s="218">
-        <v>0</v>
-      </c>
-      <c r="M17" s="218">
-        <v>0</v>
-      </c>
-      <c r="N17" s="222">
-        <v>0</v>
-      </c>
-      <c r="O17" s="227">
+      <c r="D17" s="293"/>
+      <c r="E17" s="210">
+        <v>0</v>
+      </c>
+      <c r="F17" s="215">
+        <v>0</v>
+      </c>
+      <c r="G17" s="215">
+        <v>0</v>
+      </c>
+      <c r="H17" s="215">
+        <v>0</v>
+      </c>
+      <c r="I17" s="215">
+        <v>0</v>
+      </c>
+      <c r="J17" s="215">
+        <v>0</v>
+      </c>
+      <c r="K17" s="215">
+        <v>0</v>
+      </c>
+      <c r="L17" s="215">
+        <v>0</v>
+      </c>
+      <c r="M17" s="215">
+        <v>0</v>
+      </c>
+      <c r="N17" s="219">
+        <v>0</v>
+      </c>
+      <c r="O17" s="224">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:15" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="270"/>
+      <c r="A18" s="297"/>
       <c r="B18" s="36" t="s">
         <v>47</v>
       </c>
-      <c r="C18" s="271" t="s">
+      <c r="C18" s="268" t="s">
         <v>48</v>
       </c>
-      <c r="D18" s="272"/>
-      <c r="E18" s="213">
-        <v>0</v>
-      </c>
-      <c r="F18" s="218">
-        <v>0</v>
-      </c>
-      <c r="G18" s="218">
-        <v>0</v>
-      </c>
-      <c r="H18" s="218">
-        <v>0</v>
-      </c>
-      <c r="I18" s="218">
-        <v>0</v>
-      </c>
-      <c r="J18" s="218">
-        <v>0</v>
-      </c>
-      <c r="K18" s="218">
-        <v>0</v>
-      </c>
-      <c r="L18" s="218">
-        <v>0</v>
-      </c>
-      <c r="M18" s="218">
-        <v>0</v>
-      </c>
-      <c r="N18" s="222">
-        <v>0</v>
-      </c>
-      <c r="O18" s="228">
+      <c r="D18" s="269"/>
+      <c r="E18" s="210">
+        <v>0</v>
+      </c>
+      <c r="F18" s="215">
+        <v>0</v>
+      </c>
+      <c r="G18" s="215">
+        <v>0</v>
+      </c>
+      <c r="H18" s="215">
+        <v>0</v>
+      </c>
+      <c r="I18" s="215">
+        <v>0</v>
+      </c>
+      <c r="J18" s="215">
+        <v>0</v>
+      </c>
+      <c r="K18" s="215">
+        <v>0</v>
+      </c>
+      <c r="L18" s="215">
+        <v>0</v>
+      </c>
+      <c r="M18" s="215">
+        <v>0</v>
+      </c>
+      <c r="N18" s="219">
+        <v>0</v>
+      </c>
+      <c r="O18" s="225">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -4469,229 +4482,229 @@
       <c r="B19" s="30" t="s">
         <v>49</v>
       </c>
-      <c r="C19" s="237" t="s">
+      <c r="C19" s="261" t="s">
         <v>50</v>
       </c>
-      <c r="D19" s="236"/>
-      <c r="E19" s="212">
+      <c r="D19" s="260"/>
+      <c r="E19" s="209">
         <f t="shared" ref="E19:N19" si="2">SUM(E20:E23)</f>
         <v>0</v>
       </c>
-      <c r="F19" s="217">
+      <c r="F19" s="214">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="G19" s="217">
+      <c r="G19" s="214">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H19" s="217">
+      <c r="H19" s="214">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I19" s="217">
+      <c r="I19" s="214">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J19" s="217">
+      <c r="J19" s="214">
         <f t="shared" si="2"/>
-        <v>2</v>
-      </c>
-      <c r="K19" s="217">
+        <v>1</v>
+      </c>
+      <c r="K19" s="214">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L19" s="217">
+      <c r="L19" s="214">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="M19" s="217">
+      <c r="M19" s="214">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="N19" s="221">
+      <c r="N19" s="218">
         <f t="shared" si="2"/>
-        <v>6</v>
-      </c>
-      <c r="O19" s="225">
+        <v>3</v>
+      </c>
+      <c r="O19" s="222">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20" spans="1:15" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="268" t="s">
+      <c r="A20" s="295" t="s">
         <v>51</v>
       </c>
       <c r="B20" s="37" t="s">
         <v>52</v>
       </c>
-      <c r="C20" s="259" t="s">
+      <c r="C20" s="266" t="s">
         <v>53</v>
       </c>
-      <c r="D20" s="260"/>
-      <c r="E20" s="214">
-        <v>0</v>
-      </c>
-      <c r="F20" s="219">
-        <v>0</v>
-      </c>
-      <c r="G20" s="219">
-        <v>0</v>
-      </c>
-      <c r="H20" s="219">
-        <v>0</v>
-      </c>
-      <c r="I20" s="219">
-        <v>0</v>
-      </c>
-      <c r="J20" s="329">
+      <c r="D20" s="267"/>
+      <c r="E20" s="211">
+        <v>0</v>
+      </c>
+      <c r="F20" s="216">
+        <v>0</v>
+      </c>
+      <c r="G20" s="216">
+        <v>0</v>
+      </c>
+      <c r="H20" s="216">
+        <v>0</v>
+      </c>
+      <c r="I20" s="216">
+        <v>0</v>
+      </c>
+      <c r="J20" s="216">
         <v>1</v>
       </c>
-      <c r="K20" s="219">
-        <v>0</v>
-      </c>
-      <c r="L20" s="219">
-        <v>0</v>
-      </c>
-      <c r="M20" s="219">
-        <v>0</v>
-      </c>
-      <c r="N20" s="331">
+      <c r="K20" s="216">
+        <v>0</v>
+      </c>
+      <c r="L20" s="216">
+        <v>0</v>
+      </c>
+      <c r="M20" s="216">
+        <v>0</v>
+      </c>
+      <c r="N20" s="232">
         <v>3</v>
       </c>
-      <c r="O20" s="226">
+      <c r="O20" s="223">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
     <row r="21" spans="1:15" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="269"/>
+      <c r="A21" s="296"/>
       <c r="B21" s="32" t="s">
         <v>54</v>
       </c>
-      <c r="C21" s="265" t="s">
+      <c r="C21" s="294" t="s">
         <v>55</v>
       </c>
-      <c r="D21" s="263"/>
-      <c r="E21" s="213">
-        <v>0</v>
-      </c>
-      <c r="F21" s="218">
-        <v>0</v>
-      </c>
-      <c r="G21" s="218">
-        <v>0</v>
-      </c>
-      <c r="H21" s="218">
-        <v>0</v>
-      </c>
-      <c r="I21" s="218">
-        <v>0</v>
-      </c>
-      <c r="J21" s="330">
-        <v>1</v>
-      </c>
-      <c r="K21" s="218">
-        <v>0</v>
-      </c>
-      <c r="L21" s="218">
-        <v>0</v>
-      </c>
-      <c r="M21" s="218">
-        <v>0</v>
-      </c>
-      <c r="N21" s="332">
-        <v>3</v>
-      </c>
-      <c r="O21" s="227">
+      <c r="D21" s="293"/>
+      <c r="E21" s="210">
+        <v>0</v>
+      </c>
+      <c r="F21" s="215">
+        <v>0</v>
+      </c>
+      <c r="G21" s="215">
+        <v>0</v>
+      </c>
+      <c r="H21" s="215">
+        <v>0</v>
+      </c>
+      <c r="I21" s="215">
+        <v>0</v>
+      </c>
+      <c r="J21" s="215">
+        <v>0</v>
+      </c>
+      <c r="K21" s="215">
+        <v>0</v>
+      </c>
+      <c r="L21" s="215">
+        <v>0</v>
+      </c>
+      <c r="M21" s="215">
+        <v>0</v>
+      </c>
+      <c r="N21" s="219">
+        <v>0</v>
+      </c>
+      <c r="O21" s="224">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:15" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="269"/>
+      <c r="A22" s="296"/>
       <c r="B22" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="C22" s="262" t="s">
+      <c r="C22" s="292" t="s">
         <v>57</v>
       </c>
-      <c r="D22" s="263"/>
-      <c r="E22" s="213">
-        <v>0</v>
-      </c>
-      <c r="F22" s="218">
-        <v>0</v>
-      </c>
-      <c r="G22" s="218">
-        <v>0</v>
-      </c>
-      <c r="H22" s="218">
-        <v>0</v>
-      </c>
-      <c r="I22" s="218">
-        <v>0</v>
-      </c>
-      <c r="J22" s="218">
-        <v>0</v>
-      </c>
-      <c r="K22" s="218">
-        <v>0</v>
-      </c>
-      <c r="L22" s="218">
-        <v>0</v>
-      </c>
-      <c r="M22" s="218">
-        <v>0</v>
-      </c>
-      <c r="N22" s="222">
-        <v>0</v>
-      </c>
-      <c r="O22" s="227">
+      <c r="D22" s="293"/>
+      <c r="E22" s="210">
+        <v>0</v>
+      </c>
+      <c r="F22" s="215">
+        <v>0</v>
+      </c>
+      <c r="G22" s="215">
+        <v>0</v>
+      </c>
+      <c r="H22" s="215">
+        <v>0</v>
+      </c>
+      <c r="I22" s="215">
+        <v>0</v>
+      </c>
+      <c r="J22" s="215">
+        <v>0</v>
+      </c>
+      <c r="K22" s="215">
+        <v>0</v>
+      </c>
+      <c r="L22" s="215">
+        <v>0</v>
+      </c>
+      <c r="M22" s="215">
+        <v>0</v>
+      </c>
+      <c r="N22" s="219">
+        <v>0</v>
+      </c>
+      <c r="O22" s="224">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:15" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="270"/>
+      <c r="A23" s="297"/>
       <c r="B23" s="38" t="s">
         <v>58</v>
       </c>
-      <c r="C23" s="271" t="s">
+      <c r="C23" s="268" t="s">
         <v>59</v>
       </c>
-      <c r="D23" s="272"/>
-      <c r="E23" s="215">
-        <v>0</v>
-      </c>
-      <c r="F23" s="220">
-        <v>0</v>
-      </c>
-      <c r="G23" s="220">
-        <v>0</v>
-      </c>
-      <c r="H23" s="220">
-        <v>0</v>
-      </c>
-      <c r="I23" s="220">
-        <v>0</v>
-      </c>
-      <c r="J23" s="220">
-        <v>0</v>
-      </c>
-      <c r="K23" s="220">
-        <v>0</v>
-      </c>
-      <c r="L23" s="220">
-        <v>0</v>
-      </c>
-      <c r="M23" s="220">
-        <v>0</v>
-      </c>
-      <c r="N23" s="223">
-        <v>0</v>
-      </c>
-      <c r="O23" s="228">
+      <c r="D23" s="269"/>
+      <c r="E23" s="212">
+        <v>0</v>
+      </c>
+      <c r="F23" s="217">
+        <v>0</v>
+      </c>
+      <c r="G23" s="217">
+        <v>0</v>
+      </c>
+      <c r="H23" s="217">
+        <v>0</v>
+      </c>
+      <c r="I23" s="217">
+        <v>0</v>
+      </c>
+      <c r="J23" s="217">
+        <v>0</v>
+      </c>
+      <c r="K23" s="217">
+        <v>0</v>
+      </c>
+      <c r="L23" s="217">
+        <v>0</v>
+      </c>
+      <c r="M23" s="217">
+        <v>0</v>
+      </c>
+      <c r="N23" s="220">
+        <v>0</v>
+      </c>
+      <c r="O23" s="225">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -4703,12 +4716,12 @@
       <c r="B24" s="30" t="s">
         <v>60</v>
       </c>
-      <c r="C24" s="235" t="s">
+      <c r="C24" s="259" t="s">
         <v>61</v>
       </c>
-      <c r="D24" s="236"/>
+      <c r="D24" s="260"/>
       <c r="E24" s="29">
-        <f t="shared" ref="E24:N24" si="3">(E14+E15)-E19</f>
+        <f t="shared" ref="E24:M24" si="3">(E14+E15)-E19</f>
         <v>0</v>
       </c>
       <c r="F24" s="29">
@@ -4729,7 +4742,7 @@
       </c>
       <c r="J24" s="29">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" s="29">
         <f t="shared" si="3"/>
@@ -4744,12 +4757,12 @@
         <v>0</v>
       </c>
       <c r="N24" s="29">
-        <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
-      <c r="O24" s="229">
+        <f>(N14+N15)-N19</f>
+        <v>6</v>
+      </c>
+      <c r="O24" s="226">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="25" spans="1:15" s="43" customFormat="1" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -4759,12 +4772,12 @@
       <c r="B25" s="30" t="s">
         <v>62</v>
       </c>
-      <c r="C25" s="235" t="s">
+      <c r="C25" s="259" t="s">
         <v>63</v>
       </c>
-      <c r="D25" s="236"/>
+      <c r="D25" s="260"/>
       <c r="E25" s="41"/>
-      <c r="F25" s="216"/>
+      <c r="F25" s="213"/>
       <c r="G25" s="41"/>
       <c r="H25" s="41"/>
       <c r="I25" s="41"/>
@@ -4773,7 +4786,7 @@
       <c r="L25" s="41"/>
       <c r="M25" s="42"/>
       <c r="N25" s="42"/>
-      <c r="O25" s="229">
+      <c r="O25" s="226">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -4959,8 +4972,8 @@
     <mergeCell ref="C18:D18"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.5" right="0.5" top="0.25" bottom="0.25" header="0.51180555555555551" footer="0.51180555555555551"/>
-  <pageSetup paperSize="14" scale="74" firstPageNumber="0" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.23622047244094491" bottom="0.23622047244094491" header="0.51181102362204722" footer="0.51181102362204722"/>
+  <pageSetup paperSize="133" scale="90" firstPageNumber="0" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -5012,98 +5025,98 @@
       <c r="L2" s="68"/>
     </row>
     <row r="3" spans="1:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="277" t="s">
+      <c r="A3" s="301" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="278"/>
-      <c r="C3" s="278"/>
-      <c r="D3" s="278"/>
-      <c r="E3" s="278"/>
-      <c r="F3" s="278"/>
-      <c r="G3" s="278"/>
-      <c r="H3" s="278"/>
-      <c r="I3" s="278"/>
-      <c r="J3" s="278"/>
-      <c r="K3" s="278"/>
-      <c r="L3" s="279"/>
+      <c r="B3" s="302"/>
+      <c r="C3" s="302"/>
+      <c r="D3" s="302"/>
+      <c r="E3" s="302"/>
+      <c r="F3" s="302"/>
+      <c r="G3" s="302"/>
+      <c r="H3" s="302"/>
+      <c r="I3" s="302"/>
+      <c r="J3" s="302"/>
+      <c r="K3" s="302"/>
+      <c r="L3" s="303"/>
     </row>
     <row r="4" spans="1:12" s="11" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="286" t="s">
+      <c r="A4" s="308" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="287"/>
-      <c r="C4" s="287"/>
-      <c r="D4" s="287"/>
-      <c r="E4" s="287"/>
-      <c r="F4" s="287"/>
-      <c r="G4" s="287"/>
-      <c r="H4" s="287"/>
-      <c r="I4" s="287"/>
-      <c r="J4" s="287"/>
-      <c r="K4" s="287"/>
-      <c r="L4" s="288"/>
+      <c r="B4" s="309"/>
+      <c r="C4" s="309"/>
+      <c r="D4" s="309"/>
+      <c r="E4" s="309"/>
+      <c r="F4" s="309"/>
+      <c r="G4" s="309"/>
+      <c r="H4" s="309"/>
+      <c r="I4" s="309"/>
+      <c r="J4" s="309"/>
+      <c r="K4" s="309"/>
+      <c r="L4" s="310"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="12"/>
       <c r="B5" s="12"/>
       <c r="C5" s="12"/>
       <c r="D5" s="12"/>
-      <c r="E5" s="280"/>
-      <c r="F5" s="281"/>
-      <c r="G5" s="281"/>
-      <c r="H5" s="281"/>
-      <c r="I5" s="281"/>
-      <c r="J5" s="281"/>
-      <c r="K5" s="281"/>
-      <c r="L5" s="282"/>
+      <c r="E5" s="304"/>
+      <c r="F5" s="305"/>
+      <c r="G5" s="305"/>
+      <c r="H5" s="305"/>
+      <c r="I5" s="305"/>
+      <c r="J5" s="305"/>
+      <c r="K5" s="305"/>
+      <c r="L5" s="306"/>
     </row>
     <row r="6" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="248" t="s">
+      <c r="A6" s="276" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="249"/>
-      <c r="C6" s="249"/>
-      <c r="D6" s="250"/>
-      <c r="E6" s="293" t="s">
+      <c r="B6" s="277"/>
+      <c r="C6" s="277"/>
+      <c r="D6" s="278"/>
+      <c r="E6" s="313" t="s">
         <v>72</v>
       </c>
-      <c r="F6" s="267"/>
-      <c r="G6" s="267"/>
-      <c r="H6" s="267"/>
-      <c r="I6" s="267"/>
-      <c r="J6" s="267"/>
-      <c r="K6" s="236"/>
-      <c r="L6" s="284" t="s">
+      <c r="F6" s="289"/>
+      <c r="G6" s="289"/>
+      <c r="H6" s="289"/>
+      <c r="I6" s="289"/>
+      <c r="J6" s="289"/>
+      <c r="K6" s="260"/>
+      <c r="L6" s="314" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="7" spans="1:12" s="69" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="251"/>
-      <c r="B7" s="252"/>
-      <c r="C7" s="252"/>
-      <c r="D7" s="253"/>
-      <c r="E7" s="273" t="s">
+      <c r="A7" s="279"/>
+      <c r="B7" s="280"/>
+      <c r="C7" s="280"/>
+      <c r="D7" s="281"/>
+      <c r="E7" s="298" t="s">
         <v>74</v>
       </c>
-      <c r="F7" s="261" t="s">
+      <c r="F7" s="291" t="s">
         <v>75</v>
       </c>
-      <c r="G7" s="238" t="s">
+      <c r="G7" s="262" t="s">
         <v>76</v>
       </c>
-      <c r="H7" s="238" t="s">
+      <c r="H7" s="262" t="s">
         <v>77</v>
       </c>
-      <c r="I7" s="238" t="s">
+      <c r="I7" s="262" t="s">
         <v>78</v>
       </c>
-      <c r="J7" s="289" t="s">
+      <c r="J7" s="315" t="s">
         <v>79</v>
       </c>
-      <c r="K7" s="292" t="s">
+      <c r="K7" s="311" t="s">
         <v>80</v>
       </c>
-      <c r="L7" s="285"/>
+      <c r="L7" s="312"/>
     </row>
     <row r="8" spans="1:12" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
@@ -5111,18 +5124,18 @@
       </c>
       <c r="B8" s="14"/>
       <c r="C8" s="14"/>
-      <c r="D8" s="231">
+      <c r="D8" s="228">
         <f>'Page 1'!D8</f>
         <v>0</v>
       </c>
-      <c r="E8" s="274"/>
-      <c r="F8" s="239"/>
-      <c r="G8" s="239"/>
-      <c r="H8" s="239"/>
-      <c r="I8" s="239"/>
-      <c r="J8" s="290"/>
-      <c r="K8" s="285"/>
-      <c r="L8" s="285"/>
+      <c r="E8" s="299"/>
+      <c r="F8" s="263"/>
+      <c r="G8" s="263"/>
+      <c r="H8" s="263"/>
+      <c r="I8" s="263"/>
+      <c r="J8" s="316"/>
+      <c r="K8" s="312"/>
+      <c r="L8" s="312"/>
     </row>
     <row r="9" spans="1:12" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="16" t="s">
@@ -5134,77 +5147,77 @@
         <f>'Page 1'!D9</f>
         <v>BUENAVISTA</v>
       </c>
-      <c r="E9" s="274"/>
-      <c r="F9" s="239"/>
-      <c r="G9" s="239"/>
-      <c r="H9" s="239"/>
-      <c r="I9" s="239"/>
-      <c r="J9" s="290"/>
-      <c r="K9" s="285"/>
-      <c r="L9" s="285"/>
+      <c r="E9" s="299"/>
+      <c r="F9" s="263"/>
+      <c r="G9" s="263"/>
+      <c r="H9" s="263"/>
+      <c r="I9" s="263"/>
+      <c r="J9" s="316"/>
+      <c r="K9" s="312"/>
+      <c r="L9" s="312"/>
     </row>
     <row r="10" spans="1:12" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="245" t="s">
+      <c r="A10" s="273" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="246"/>
-      <c r="C10" s="247"/>
+      <c r="B10" s="274"/>
+      <c r="C10" s="275"/>
       <c r="D10" s="71" t="str">
         <f>'Page 1'!D10</f>
         <v>AGUSAN DEL NORTE</v>
       </c>
-      <c r="E10" s="274"/>
-      <c r="F10" s="239"/>
-      <c r="G10" s="239"/>
-      <c r="H10" s="239"/>
-      <c r="I10" s="239"/>
-      <c r="J10" s="290"/>
-      <c r="K10" s="285"/>
-      <c r="L10" s="285"/>
+      <c r="E10" s="299"/>
+      <c r="F10" s="263"/>
+      <c r="G10" s="263"/>
+      <c r="H10" s="263"/>
+      <c r="I10" s="263"/>
+      <c r="J10" s="316"/>
+      <c r="K10" s="312"/>
+      <c r="L10" s="312"/>
     </row>
     <row r="11" spans="1:12" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="245" t="s">
+      <c r="A11" s="273" t="s">
         <v>22</v>
       </c>
-      <c r="B11" s="246"/>
-      <c r="C11" s="247"/>
+      <c r="B11" s="274"/>
+      <c r="C11" s="275"/>
       <c r="D11" s="72" t="str">
         <f>'Page 1'!D11</f>
         <v>10TH JUDICIAL REGION</v>
       </c>
-      <c r="E11" s="274"/>
-      <c r="F11" s="239"/>
-      <c r="G11" s="239"/>
-      <c r="H11" s="239"/>
-      <c r="I11" s="239"/>
-      <c r="J11" s="290"/>
-      <c r="K11" s="285"/>
-      <c r="L11" s="285"/>
+      <c r="E11" s="299"/>
+      <c r="F11" s="263"/>
+      <c r="G11" s="263"/>
+      <c r="H11" s="263"/>
+      <c r="I11" s="263"/>
+      <c r="J11" s="316"/>
+      <c r="K11" s="312"/>
+      <c r="L11" s="312"/>
     </row>
     <row r="12" spans="1:12" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="245" t="s">
+      <c r="A12" s="273" t="s">
         <v>24</v>
       </c>
-      <c r="B12" s="246"/>
-      <c r="C12" s="247"/>
-      <c r="D12" s="230" t="str">
+      <c r="B12" s="274"/>
+      <c r="C12" s="275"/>
+      <c r="D12" s="227" t="str">
         <f>'Page 1'!D12</f>
         <v>June 2026</v>
       </c>
-      <c r="E12" s="275"/>
-      <c r="F12" s="240"/>
-      <c r="G12" s="240"/>
-      <c r="H12" s="240"/>
-      <c r="I12" s="240"/>
-      <c r="J12" s="291"/>
-      <c r="K12" s="285"/>
-      <c r="L12" s="285"/>
+      <c r="E12" s="300"/>
+      <c r="F12" s="264"/>
+      <c r="G12" s="264"/>
+      <c r="H12" s="264"/>
+      <c r="I12" s="264"/>
+      <c r="J12" s="317"/>
+      <c r="K12" s="312"/>
+      <c r="L12" s="312"/>
     </row>
     <row r="13" spans="1:12" s="69" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="256"/>
-      <c r="B13" s="283"/>
-      <c r="C13" s="283"/>
-      <c r="D13" s="258"/>
+      <c r="A13" s="284"/>
+      <c r="B13" s="307"/>
+      <c r="C13" s="307"/>
+      <c r="D13" s="286"/>
       <c r="E13" s="73" t="s">
         <v>81</v>
       </c>
@@ -5237,10 +5250,10 @@
       <c r="B14" s="27" t="s">
         <v>38</v>
       </c>
-      <c r="C14" s="241" t="s">
+      <c r="C14" s="265" t="s">
         <v>39</v>
       </c>
-      <c r="D14" s="236"/>
+      <c r="D14" s="260"/>
       <c r="E14" s="28">
         <v>5</v>
       </c>
@@ -5263,7 +5276,7 @@
         <f t="shared" ref="K14:K24" si="0">SUM(E14:J14)</f>
         <v>13</v>
       </c>
-      <c r="L14" s="232">
+      <c r="L14" s="229">
         <f>'Page 1'!O14+'Page 2'!K14</f>
         <v>34</v>
       </c>
@@ -5275,21 +5288,21 @@
       <c r="B15" s="30" t="s">
         <v>40</v>
       </c>
-      <c r="C15" s="237" t="s">
+      <c r="C15" s="261" t="s">
         <v>41</v>
       </c>
-      <c r="D15" s="236"/>
+      <c r="D15" s="260"/>
       <c r="E15" s="28">
         <f t="shared" ref="E15:J15" si="1">SUM(E16:E18)</f>
         <v>1</v>
       </c>
       <c r="F15" s="76">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G15" s="76">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H15" s="76">
         <f t="shared" si="1"/>
@@ -5307,30 +5320,30 @@
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="L15" s="232">
+      <c r="L15" s="229">
         <f>'Page 1'!O15+'Page 2'!K15</f>
         <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:12" s="53" customFormat="1" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="268" t="s">
+      <c r="A16" s="295" t="s">
         <v>42</v>
       </c>
       <c r="B16" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="C16" s="259" t="s">
+      <c r="C16" s="266" t="s">
         <v>44</v>
       </c>
-      <c r="D16" s="260"/>
+      <c r="D16" s="267"/>
       <c r="E16" s="78">
         <v>1</v>
       </c>
       <c r="F16" s="79">
+        <v>0</v>
+      </c>
+      <c r="G16" s="80">
         <v>2</v>
-      </c>
-      <c r="G16" s="80">
-        <v>0</v>
       </c>
       <c r="H16" s="80">
         <v>0</v>
@@ -5345,20 +5358,20 @@
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="L16" s="233">
+      <c r="L16" s="230">
         <f>'Page 1'!O16+'Page 2'!K16</f>
         <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:27" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="269"/>
+      <c r="A17" s="296"/>
       <c r="B17" s="32" t="s">
         <v>45</v>
       </c>
-      <c r="C17" s="262" t="s">
+      <c r="C17" s="292" t="s">
         <v>46</v>
       </c>
-      <c r="D17" s="263"/>
+      <c r="D17" s="293"/>
       <c r="E17" s="33">
         <v>0</v>
       </c>
@@ -5381,20 +5394,20 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L17" s="234">
+      <c r="L17" s="231">
         <f>'Page 1'!O17+'Page 2'!K17</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:27" s="53" customFormat="1" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="270"/>
+      <c r="A18" s="297"/>
       <c r="B18" s="36" t="s">
         <v>47</v>
       </c>
-      <c r="C18" s="271" t="s">
+      <c r="C18" s="268" t="s">
         <v>48</v>
       </c>
-      <c r="D18" s="272"/>
+      <c r="D18" s="269"/>
       <c r="E18" s="85">
         <v>0</v>
       </c>
@@ -5417,7 +5430,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L18" s="234">
+      <c r="L18" s="231">
         <f>'Page 1'!O18+'Page 2'!K18</f>
         <v>0</v>
       </c>
@@ -5429,13 +5442,13 @@
       <c r="B19" s="30" t="s">
         <v>49</v>
       </c>
-      <c r="C19" s="237" t="s">
+      <c r="C19" s="261" t="s">
         <v>50</v>
       </c>
-      <c r="D19" s="236"/>
+      <c r="D19" s="260"/>
       <c r="E19" s="28">
         <f t="shared" ref="E19:J19" si="2">SUM(E20:E23)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F19" s="76">
         <f t="shared" si="2"/>
@@ -5447,7 +5460,7 @@
       </c>
       <c r="H19" s="76">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I19" s="76">
         <f t="shared" si="2"/>
@@ -5459,24 +5472,24 @@
       </c>
       <c r="K19" s="77">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="L19" s="232">
+        <v>3</v>
+      </c>
+      <c r="L19" s="229">
         <f>'Page 1'!O19+'Page 2'!K19</f>
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:27" s="53" customFormat="1" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="268" t="s">
+      <c r="A20" s="295" t="s">
         <v>51</v>
       </c>
       <c r="B20" s="37" t="s">
         <v>52</v>
       </c>
-      <c r="C20" s="259" t="s">
+      <c r="C20" s="266" t="s">
         <v>53</v>
       </c>
-      <c r="D20" s="260"/>
+      <c r="D20" s="267"/>
       <c r="E20" s="78">
         <v>0</v>
       </c>
@@ -5499,22 +5512,22 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L20" s="233">
+      <c r="L20" s="230">
         <f>'Page 1'!O20+'Page 2'!K20</f>
         <v>4</v>
       </c>
     </row>
     <row r="21" spans="1:27" s="53" customFormat="1" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="269"/>
+      <c r="A21" s="296"/>
       <c r="B21" s="32" t="s">
         <v>54</v>
       </c>
-      <c r="C21" s="265" t="s">
+      <c r="C21" s="294" t="s">
         <v>55</v>
       </c>
-      <c r="D21" s="263"/>
+      <c r="D21" s="293"/>
       <c r="E21" s="33">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F21" s="83">
         <v>0</v>
@@ -5523,7 +5536,7 @@
         <v>0</v>
       </c>
       <c r="H21" s="83">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21" s="83">
         <v>0</v>
@@ -5533,22 +5546,22 @@
       </c>
       <c r="K21" s="89">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="L21" s="234">
+        <v>3</v>
+      </c>
+      <c r="L21" s="231">
         <f>'Page 1'!O21+'Page 2'!K21</f>
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22" spans="1:27" s="53" customFormat="1" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="269"/>
+      <c r="A22" s="296"/>
       <c r="B22" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="C22" s="262" t="s">
+      <c r="C22" s="292" t="s">
         <v>57</v>
       </c>
-      <c r="D22" s="263"/>
+      <c r="D22" s="293"/>
       <c r="E22" s="33">
         <v>0</v>
       </c>
@@ -5571,20 +5584,20 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L22" s="234">
+      <c r="L22" s="231">
         <f>'Page 1'!O22+'Page 2'!K22</f>
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:27" s="53" customFormat="1" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="270"/>
+      <c r="A23" s="297"/>
       <c r="B23" s="38" t="s">
         <v>58</v>
       </c>
-      <c r="C23" s="271" t="s">
+      <c r="C23" s="268" t="s">
         <v>59</v>
       </c>
-      <c r="D23" s="272"/>
+      <c r="D23" s="269"/>
       <c r="E23" s="85">
         <v>0</v>
       </c>
@@ -5607,7 +5620,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L23" s="234">
+      <c r="L23" s="231">
         <f>'Page 1'!O23+'Page 2'!K23</f>
         <v>0</v>
       </c>
@@ -5622,25 +5635,25 @@
       <c r="B24" s="30" t="s">
         <v>60</v>
       </c>
-      <c r="C24" s="235" t="s">
+      <c r="C24" s="259" t="s">
         <v>61</v>
       </c>
-      <c r="D24" s="236"/>
+      <c r="D24" s="260"/>
       <c r="E24" s="28">
         <f>(E14+E15)-E19</f>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F24" s="76">
         <f>SUM(F14+F15)-F19</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G24" s="76">
         <f>SUM(G14+G15)-G19</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H24" s="76">
         <f>SUM(H14+H15)-H19</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I24" s="76">
         <f>SUM(I14+I15)-I19</f>
@@ -5652,11 +5665,11 @@
       </c>
       <c r="K24" s="77">
         <f t="shared" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="L24" s="232">
+        <v>13</v>
+      </c>
+      <c r="L24" s="229">
         <f>'Page 1'!O24+'Page 2'!K24</f>
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="25" spans="1:27" s="53" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -5666,10 +5679,10 @@
       <c r="B25" s="30" t="s">
         <v>62</v>
       </c>
-      <c r="C25" s="235" t="s">
+      <c r="C25" s="259" t="s">
         <v>90</v>
       </c>
-      <c r="D25" s="236"/>
+      <c r="D25" s="260"/>
       <c r="E25" s="40"/>
       <c r="F25" s="90"/>
       <c r="G25" s="41"/>
@@ -5867,14 +5880,14 @@
     <mergeCell ref="A12:C12"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
-  <pageMargins left="0" right="0" top="0" bottom="0" header="0.51180555555555551" footer="0.51180555555555551"/>
-  <pageSetup paperSize="14" scale="87" firstPageNumber="0" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <pageMargins left="0" right="0" top="0" bottom="0" header="0.51181102362204722" footer="0.51181102362204722"/>
+  <pageSetup paperSize="256" scale="95" firstPageNumber="0" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.140625" style="121" customWidth="1"/>
@@ -5901,85 +5914,85 @@
       <c r="G2" s="125"/>
     </row>
     <row r="3" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="299" t="s">
+      <c r="A3" s="318" t="s">
         <v>95</v>
       </c>
-      <c r="B3" s="300"/>
-      <c r="C3" s="301"/>
-      <c r="D3" s="301"/>
-      <c r="E3" s="301"/>
-      <c r="F3" s="300"/>
-      <c r="G3" s="300"/>
+      <c r="B3" s="319"/>
+      <c r="C3" s="320"/>
+      <c r="D3" s="320"/>
+      <c r="E3" s="320"/>
+      <c r="F3" s="319"/>
+      <c r="G3" s="319"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="302"/>
-      <c r="B4" s="300"/>
-      <c r="C4" s="301"/>
-      <c r="D4" s="301"/>
-      <c r="E4" s="301"/>
-      <c r="F4" s="300"/>
-      <c r="G4" s="300"/>
+      <c r="A4" s="254"/>
+      <c r="B4" s="319"/>
+      <c r="C4" s="320"/>
+      <c r="D4" s="320"/>
+      <c r="E4" s="320"/>
+      <c r="F4" s="319"/>
+      <c r="G4" s="319"/>
     </row>
     <row r="5" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="303" t="s">
+      <c r="A5" s="324" t="s">
         <v>96</v>
       </c>
-      <c r="B5" s="294" t="s">
+      <c r="B5" s="326" t="s">
         <v>97</v>
       </c>
-      <c r="C5" s="295" t="s">
+      <c r="C5" s="327" t="s">
         <v>98</v>
       </c>
-      <c r="D5" s="304" t="s">
+      <c r="D5" s="325" t="s">
         <v>99</v>
       </c>
-      <c r="E5" s="304" t="s">
+      <c r="E5" s="325" t="s">
         <v>100</v>
       </c>
-      <c r="F5" s="294" t="s">
+      <c r="F5" s="326" t="s">
         <v>101</v>
       </c>
-      <c r="G5" s="294" t="s">
+      <c r="G5" s="326" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="239"/>
-      <c r="B6" s="239"/>
-      <c r="C6" s="239"/>
-      <c r="D6" s="239"/>
-      <c r="E6" s="239"/>
-      <c r="F6" s="239"/>
-      <c r="G6" s="239"/>
+      <c r="A6" s="263"/>
+      <c r="B6" s="263"/>
+      <c r="C6" s="263"/>
+      <c r="D6" s="263"/>
+      <c r="E6" s="263"/>
+      <c r="F6" s="263"/>
+      <c r="G6" s="263"/>
     </row>
     <row r="7" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="239"/>
-      <c r="B7" s="239"/>
-      <c r="C7" s="239"/>
-      <c r="D7" s="239"/>
-      <c r="E7" s="239"/>
-      <c r="F7" s="239"/>
-      <c r="G7" s="239"/>
+      <c r="A7" s="263"/>
+      <c r="B7" s="263"/>
+      <c r="C7" s="263"/>
+      <c r="D7" s="263"/>
+      <c r="E7" s="263"/>
+      <c r="F7" s="263"/>
+      <c r="G7" s="263"/>
     </row>
     <row r="8" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="240"/>
-      <c r="B8" s="240"/>
-      <c r="C8" s="240"/>
-      <c r="D8" s="240"/>
-      <c r="E8" s="240"/>
-      <c r="F8" s="240"/>
-      <c r="G8" s="240"/>
+      <c r="A8" s="264"/>
+      <c r="B8" s="264"/>
+      <c r="C8" s="264"/>
+      <c r="D8" s="264"/>
+      <c r="E8" s="264"/>
+      <c r="F8" s="264"/>
+      <c r="G8" s="264"/>
     </row>
     <row r="9" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="296" t="s">
+      <c r="A9" s="321" t="s">
         <v>103</v>
       </c>
-      <c r="B9" s="297"/>
-      <c r="C9" s="297"/>
-      <c r="D9" s="297"/>
-      <c r="E9" s="297"/>
-      <c r="F9" s="297"/>
-      <c r="G9" s="298"/>
+      <c r="B9" s="322"/>
+      <c r="C9" s="322"/>
+      <c r="D9" s="322"/>
+      <c r="E9" s="322"/>
+      <c r="F9" s="322"/>
+      <c r="G9" s="323"/>
     </row>
     <row r="10" spans="1:7" s="130" customFormat="1" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="126"/>
@@ -6072,51 +6085,79 @@
       <c r="G19" s="136"/>
     </row>
     <row r="20" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="296" t="s">
+      <c r="A20" s="321" t="s">
         <v>104</v>
       </c>
-      <c r="B20" s="297"/>
-      <c r="C20" s="297"/>
-      <c r="D20" s="297"/>
-      <c r="E20" s="297"/>
-      <c r="F20" s="297"/>
-      <c r="G20" s="298"/>
-    </row>
-    <row r="21" spans="1:7" s="130" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="138"/>
-      <c r="B21" s="141"/>
-      <c r="C21" s="139"/>
-      <c r="D21" s="139"/>
-      <c r="E21" s="140"/>
-      <c r="F21" s="129"/>
-      <c r="G21" s="140"/>
-    </row>
-    <row r="22" spans="1:7" s="132" customFormat="1" ht="26.85" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="126"/>
-      <c r="B22" s="141"/>
-      <c r="C22" s="141"/>
-      <c r="D22" s="141"/>
-      <c r="E22" s="141"/>
-      <c r="F22" s="129"/>
-      <c r="G22" s="141"/>
+      <c r="B20" s="322"/>
+      <c r="C20" s="322"/>
+      <c r="D20" s="322"/>
+      <c r="E20" s="322"/>
+      <c r="F20" s="322"/>
+      <c r="G20" s="323"/>
+    </row>
+    <row r="21" spans="1:7" s="130" customFormat="1" ht="111" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="241">
+        <v>744</v>
+      </c>
+      <c r="B21" s="239" t="s">
+        <v>227</v>
+      </c>
+      <c r="C21" s="233">
+        <v>45215</v>
+      </c>
+      <c r="D21" s="233">
+        <v>46085</v>
+      </c>
+      <c r="E21" s="234">
+        <v>46179</v>
+      </c>
+      <c r="F21" s="235" t="s">
+        <v>228</v>
+      </c>
+      <c r="G21" s="236" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" s="132" customFormat="1" ht="26.85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="336">
+        <v>754</v>
+      </c>
+      <c r="B22" s="240" t="s">
+        <v>230</v>
+      </c>
+      <c r="C22" s="237">
+        <v>45530</v>
+      </c>
+      <c r="D22" s="237">
+        <v>46085</v>
+      </c>
+      <c r="E22" s="237">
+        <v>46179</v>
+      </c>
+      <c r="F22" s="235" t="s">
+        <v>228</v>
+      </c>
+      <c r="G22" s="238" t="s">
+        <v>229</v>
+      </c>
     </row>
     <row r="23" spans="1:7" s="132" customFormat="1" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="126"/>
-      <c r="B23" s="141"/>
-      <c r="C23" s="141"/>
-      <c r="D23" s="141"/>
-      <c r="E23" s="141"/>
+      <c r="A23" s="138"/>
+      <c r="B23" s="138"/>
+      <c r="C23" s="138"/>
+      <c r="D23" s="138"/>
+      <c r="E23" s="138"/>
       <c r="F23" s="129"/>
-      <c r="G23" s="141"/>
+      <c r="G23" s="138"/>
     </row>
     <row r="24" spans="1:7" s="132" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="141"/>
-      <c r="B24" s="141"/>
-      <c r="C24" s="141"/>
-      <c r="D24" s="141"/>
-      <c r="E24" s="141"/>
-      <c r="F24" s="141"/>
-      <c r="G24" s="141"/>
+      <c r="A24" s="138"/>
+      <c r="B24" s="138"/>
+      <c r="C24" s="138"/>
+      <c r="D24" s="138"/>
+      <c r="E24" s="138"/>
+      <c r="F24" s="138"/>
+      <c r="G24" s="138"/>
     </row>
     <row r="25" spans="1:7" s="132" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="133"/>
@@ -6127,7 +6168,7 @@
       <c r="F25" s="136"/>
       <c r="G25" s="136"/>
     </row>
-    <row r="26" spans="1:7" s="132" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" s="132" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="133"/>
       <c r="B26" s="134"/>
       <c r="C26" s="135"/>
@@ -6140,51 +6181,35 @@
       <c r="A27" s="133"/>
       <c r="B27" s="134"/>
       <c r="C27" s="135"/>
-      <c r="D27" s="135"/>
-      <c r="E27" s="135"/>
+      <c r="D27" s="139"/>
+      <c r="E27" s="139"/>
       <c r="F27" s="136"/>
       <c r="G27" s="136"/>
     </row>
-    <row r="28" spans="1:7" s="132" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="133"/>
-      <c r="B28" s="134"/>
-      <c r="C28" s="135"/>
-      <c r="D28" s="135"/>
-      <c r="E28" s="135"/>
-      <c r="F28" s="136"/>
-      <c r="G28" s="136"/>
-    </row>
-    <row r="29" spans="1:7" s="132" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="133"/>
-      <c r="B29" s="134"/>
-      <c r="C29" s="135"/>
-      <c r="D29" s="142"/>
-      <c r="E29" s="142"/>
-      <c r="F29" s="136"/>
-      <c r="G29" s="136"/>
-    </row>
-    <row r="30" spans="1:7" s="137" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="143"/>
-      <c r="B30" s="144"/>
-      <c r="C30" s="145"/>
-      <c r="D30" s="146"/>
-      <c r="E30" s="146"/>
-      <c r="F30" s="147"/>
-      <c r="G30" s="147"/>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C31" s="148"/>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="149" t="s">
+    <row r="28" spans="1:7" s="137" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="140"/>
+      <c r="B28" s="141"/>
+      <c r="C28" s="142"/>
+      <c r="D28" s="143"/>
+      <c r="E28" s="143"/>
+      <c r="F28" s="144"/>
+      <c r="G28" s="144"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C29" s="145"/>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="146" t="s">
         <v>105</v>
       </c>
-      <c r="B32" s="148"/>
-      <c r="F32" s="148"/>
-      <c r="G32" s="148"/>
+      <c r="B30" s="145"/>
+      <c r="F30" s="145"/>
+      <c r="G30" s="145"/>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A4:G4"/>
     <mergeCell ref="A20:G20"/>
     <mergeCell ref="A5:A8"/>
     <mergeCell ref="E5:E8"/>
@@ -6194,12 +6219,10 @@
     <mergeCell ref="B5:B8"/>
     <mergeCell ref="C5:C8"/>
     <mergeCell ref="A9:G9"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A4:G4"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.51180555555555551" footer="0.51180555555555551"/>
-  <pageSetup paperSize="14" scale="89" firstPageNumber="0" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.51181102362204722" bottom="0.51181102362204722" header="0.51181102362204722" footer="0.51181102362204722"/>
+  <pageSetup paperSize="256" scale="95" firstPageNumber="0" orientation="landscape" r:id="rId1"/>
   <colBreaks count="1" manualBreakCount="1">
     <brk id="7" max="1048575" man="1"/>
   </colBreaks>
@@ -6232,16 +6255,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A1" s="305" t="s">
+      <c r="A1" s="328" t="s">
         <v>106</v>
       </c>
-      <c r="B1" s="306"/>
-      <c r="C1" s="307"/>
-      <c r="F1" s="150" t="s">
+      <c r="B1" s="244"/>
+      <c r="C1" s="329"/>
+      <c r="F1" s="147" t="s">
         <v>107</v>
       </c>
-      <c r="G1" s="151"/>
-      <c r="H1" s="151"/>
+      <c r="G1" s="148"/>
+      <c r="H1" s="148"/>
       <c r="S1" s="118" t="s">
         <v>108</v>
       </c>
@@ -6250,11 +6273,11 @@
       <c r="B2" s="120" t="s">
         <v>109</v>
       </c>
-      <c r="C2" s="152">
+      <c r="C2" s="149">
         <f>SUM(D3:D6)</f>
         <v>0</v>
       </c>
-      <c r="D2" s="153"/>
+      <c r="D2" s="150"/>
       <c r="G2" s="120" t="s">
         <v>110</v>
       </c>
@@ -6266,15 +6289,13 @@
       <c r="B3" s="120" t="s">
         <v>112</v>
       </c>
-      <c r="C3" s="153"/>
-      <c r="D3" s="154">
-        <v>0</v>
-      </c>
+      <c r="C3" s="150"/>
+      <c r="D3" s="151"/>
       <c r="H3" s="120" t="s">
         <v>113</v>
       </c>
-      <c r="I3" s="155"/>
-      <c r="O3" s="156">
+      <c r="I3" s="152"/>
+      <c r="O3" s="153">
         <v>0</v>
       </c>
     </row>
@@ -6282,15 +6303,13 @@
       <c r="B4" s="120" t="s">
         <v>114</v>
       </c>
-      <c r="C4" s="153"/>
-      <c r="D4" s="157">
-        <v>0</v>
-      </c>
+      <c r="C4" s="150"/>
+      <c r="D4" s="154"/>
       <c r="H4" s="120" t="s">
         <v>115</v>
       </c>
-      <c r="I4" s="155"/>
-      <c r="O4" s="156">
+      <c r="I4" s="152"/>
+      <c r="O4" s="153">
         <v>0</v>
       </c>
     </row>
@@ -6298,33 +6317,29 @@
       <c r="B5" s="120" t="s">
         <v>116</v>
       </c>
-      <c r="C5" s="153"/>
-      <c r="D5" s="157">
-        <v>0</v>
-      </c>
+      <c r="C5" s="150"/>
+      <c r="D5" s="154"/>
       <c r="H5" s="120" t="s">
         <v>117</v>
       </c>
-      <c r="I5" s="155"/>
-      <c r="O5" s="156">
+      <c r="I5" s="152"/>
+      <c r="O5" s="153">
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:19" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="158" t="s">
+      <c r="B6" s="155" t="s">
         <v>118</v>
       </c>
-      <c r="C6" s="159"/>
-      <c r="D6" s="160">
-        <v>0</v>
-      </c>
+      <c r="C6" s="156"/>
+      <c r="D6" s="157"/>
     </row>
     <row r="7" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="120" t="s">
         <v>119</v>
       </c>
-      <c r="C7" s="153"/>
-      <c r="D7" s="161">
+      <c r="C7" s="150"/>
+      <c r="D7" s="158">
         <f>SUM(C8:C13)</f>
         <v>0</v>
       </c>
@@ -6336,85 +6351,73 @@
       </c>
     </row>
     <row r="8" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="162" t="s">
+      <c r="B8" s="159" t="s">
         <v>122</v>
       </c>
-      <c r="C8" s="163">
-        <v>0</v>
-      </c>
-      <c r="D8" s="164"/>
+      <c r="C8" s="160"/>
+      <c r="D8" s="161"/>
       <c r="H8" s="120" t="s">
         <v>123</v>
       </c>
-      <c r="I8" s="165"/>
-      <c r="O8" s="166">
+      <c r="I8" s="162"/>
+      <c r="O8" s="163">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="162" t="s">
+      <c r="B9" s="159" t="s">
         <v>124</v>
       </c>
-      <c r="C9" s="157">
-        <v>0</v>
-      </c>
-      <c r="D9" s="153"/>
+      <c r="C9" s="154"/>
+      <c r="D9" s="150"/>
       <c r="H9" s="120" t="s">
         <v>125</v>
       </c>
-      <c r="I9" s="165"/>
-      <c r="O9" s="167">
+      <c r="I9" s="162"/>
+      <c r="O9" s="164">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="162" t="s">
+      <c r="B10" s="159" t="s">
         <v>126</v>
       </c>
-      <c r="C10" s="157">
-        <v>0</v>
-      </c>
-      <c r="D10" s="153"/>
+      <c r="C10" s="154"/>
+      <c r="D10" s="150"/>
       <c r="H10" s="120" t="s">
         <v>127</v>
       </c>
-      <c r="I10" s="165"/>
-      <c r="O10" s="167">
-        <v>0</v>
-      </c>
-      <c r="R10" s="168"/>
+      <c r="I10" s="162"/>
+      <c r="O10" s="164">
+        <v>0</v>
+      </c>
+      <c r="R10" s="165"/>
     </row>
     <row r="11" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="162" t="s">
+      <c r="B11" s="159" t="s">
         <v>128</v>
       </c>
-      <c r="C11" s="157">
-        <v>0</v>
-      </c>
-      <c r="D11" s="153"/>
-      <c r="I11" s="165"/>
-      <c r="K11" s="165"/>
+      <c r="C11" s="154"/>
+      <c r="D11" s="150"/>
+      <c r="I11" s="162"/>
+      <c r="K11" s="162"/>
     </row>
     <row r="12" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="162" t="s">
+      <c r="B12" s="159" t="s">
         <v>129</v>
       </c>
-      <c r="C12" s="157">
-        <v>0</v>
-      </c>
-      <c r="D12" s="153"/>
-      <c r="I12" s="165"/>
-      <c r="K12" s="165"/>
+      <c r="C12" s="154"/>
+      <c r="D12" s="150"/>
+      <c r="I12" s="162"/>
+      <c r="K12" s="162"/>
     </row>
     <row r="13" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="162" t="s">
+      <c r="B13" s="159" t="s">
         <v>130</v>
       </c>
-      <c r="C13" s="157">
-        <v>0</v>
-      </c>
+      <c r="C13" s="154"/>
       <c r="M13" s="118"/>
-      <c r="O13" s="169" t="s">
+      <c r="O13" s="166" t="s">
         <v>131</v>
       </c>
     </row>
@@ -6425,24 +6428,24 @@
       <c r="H14" s="120" t="s">
         <v>133</v>
       </c>
-      <c r="M14" s="169" t="s">
+      <c r="M14" s="166" t="s">
         <v>134</v>
       </c>
-      <c r="O14" s="169" t="s">
+      <c r="O14" s="166" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="15" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="151" t="s">
+      <c r="A15" s="148" t="s">
         <v>136</v>
       </c>
       <c r="H15" s="120" t="s">
         <v>137</v>
       </c>
-      <c r="M15" s="166">
-        <v>0</v>
-      </c>
-      <c r="O15" s="166">
+      <c r="M15" s="163">
+        <v>0</v>
+      </c>
+      <c r="O15" s="163">
         <v>0</v>
       </c>
     </row>
@@ -6450,17 +6453,17 @@
       <c r="B16" s="120" t="s">
         <v>138</v>
       </c>
-      <c r="C16" s="153"/>
-      <c r="D16" s="154">
-        <v>0</v>
+      <c r="C16" s="150"/>
+      <c r="D16" s="151">
+        <v>1</v>
       </c>
       <c r="H16" s="120" t="s">
         <v>139</v>
       </c>
-      <c r="M16" s="167">
-        <v>0</v>
-      </c>
-      <c r="O16" s="167">
+      <c r="M16" s="164">
+        <v>0</v>
+      </c>
+      <c r="O16" s="164">
         <v>0</v>
       </c>
     </row>
@@ -6468,48 +6471,48 @@
       <c r="B17" s="120" t="s">
         <v>140</v>
       </c>
-      <c r="C17" s="153"/>
-      <c r="D17" s="154">
-        <v>0</v>
-      </c>
-      <c r="I17" s="165"/>
-      <c r="K17" s="165"/>
+      <c r="C17" s="150"/>
+      <c r="D17" s="151">
+        <v>0</v>
+      </c>
+      <c r="I17" s="162"/>
+      <c r="K17" s="162"/>
     </row>
     <row r="18" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="148" t="s">
+      <c r="B18" s="145" t="s">
         <v>141</v>
       </c>
-      <c r="C18" s="170"/>
-      <c r="D18" s="171">
+      <c r="C18" s="167"/>
+      <c r="D18" s="168">
         <f>SUM(C19:C20)</f>
-        <v>0</v>
-      </c>
-      <c r="I18" s="165"/>
-      <c r="K18" s="165"/>
+        <v>2</v>
+      </c>
+      <c r="I18" s="162"/>
+      <c r="K18" s="162"/>
     </row>
     <row r="19" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="120" t="s">
         <v>142</v>
       </c>
-      <c r="C19" s="154">
-        <v>0</v>
-      </c>
-      <c r="D19" s="153"/>
+      <c r="C19" s="151">
+        <v>1</v>
+      </c>
+      <c r="D19" s="150"/>
     </row>
     <row r="20" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="120" t="s">
         <v>143</v>
       </c>
-      <c r="C20" s="157">
-        <v>0</v>
-      </c>
-      <c r="D20" s="153"/>
-      <c r="F20" s="305" t="s">
+      <c r="C20" s="154">
+        <v>1</v>
+      </c>
+      <c r="D20" s="150"/>
+      <c r="F20" s="328" t="s">
         <v>144</v>
       </c>
-      <c r="G20" s="306"/>
-      <c r="H20" s="306"/>
-      <c r="K20" s="169" t="s">
+      <c r="G20" s="244"/>
+      <c r="H20" s="244"/>
+      <c r="K20" s="166" t="s">
         <v>145</v>
       </c>
       <c r="M20" s="120" t="s">
@@ -6521,7 +6524,7 @@
       <c r="Q20" s="118" t="s">
         <v>147</v>
       </c>
-      <c r="S20" s="172" t="s">
+      <c r="S20" s="169" t="s">
         <v>148</v>
       </c>
     </row>
@@ -6529,15 +6532,15 @@
       <c r="B21" s="120" t="s">
         <v>149</v>
       </c>
-      <c r="C21" s="153"/>
-      <c r="D21" s="171">
+      <c r="C21" s="150"/>
+      <c r="D21" s="168">
         <f>SUM(D16:D17)-D18</f>
-        <v>0</v>
-      </c>
-      <c r="I21" s="169" t="s">
+        <v>-1</v>
+      </c>
+      <c r="I21" s="166" t="s">
         <v>150</v>
       </c>
-      <c r="K21" s="169" t="s">
+      <c r="K21" s="166" t="s">
         <v>151</v>
       </c>
       <c r="M21" s="120" t="s">
@@ -6546,155 +6549,155 @@
       <c r="O21" s="120" t="s">
         <v>152</v>
       </c>
-      <c r="Q21" s="169" t="s">
+      <c r="Q21" s="166" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="22" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C22" s="153"/>
-      <c r="D22" s="153"/>
+      <c r="C22" s="150"/>
+      <c r="D22" s="150"/>
       <c r="G22" s="120" t="s">
         <v>110</v>
       </c>
       <c r="H22" s="120" t="s">
         <v>154</v>
       </c>
-      <c r="I22" s="173">
-        <v>0</v>
+      <c r="I22" s="170">
+        <v>20</v>
       </c>
       <c r="J22" s="124"/>
-      <c r="K22" s="173">
-        <v>0</v>
+      <c r="K22" s="170">
+        <v>10</v>
       </c>
       <c r="L22" s="124"/>
-      <c r="M22" s="173">
+      <c r="M22" s="170">
         <v>0</v>
       </c>
       <c r="N22" s="124"/>
-      <c r="O22" s="173">
+      <c r="O22" s="170">
         <v>0</v>
       </c>
       <c r="P22" s="124"/>
-      <c r="Q22" s="173">
+      <c r="Q22" s="170">
         <v>0</v>
       </c>
       <c r="R22" s="124"/>
-      <c r="S22" s="174">
+      <c r="S22" s="171">
         <f t="shared" ref="S22:S32" si="0">SUM(I22+K22+M22+O22+Q22)</f>
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="23" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="151" t="s">
+      <c r="A23" s="148" t="s">
         <v>155</v>
       </c>
-      <c r="C23" s="153"/>
-      <c r="D23" s="153"/>
+      <c r="C23" s="150"/>
+      <c r="D23" s="150"/>
       <c r="G23" s="120" t="s">
         <v>120</v>
       </c>
       <c r="H23" s="120" t="s">
         <v>156</v>
       </c>
-      <c r="I23" s="175">
+      <c r="I23" s="172">
         <v>0</v>
       </c>
       <c r="J23" s="124"/>
-      <c r="K23" s="175">
-        <v>0</v>
+      <c r="K23" s="172">
+        <v>2</v>
       </c>
       <c r="L23" s="124"/>
-      <c r="M23" s="175">
+      <c r="M23" s="172">
         <v>0</v>
       </c>
       <c r="N23" s="124"/>
-      <c r="O23" s="175">
+      <c r="O23" s="172">
         <v>0</v>
       </c>
       <c r="P23" s="124"/>
-      <c r="Q23" s="175">
+      <c r="Q23" s="172">
         <v>0</v>
       </c>
       <c r="R23" s="124"/>
-      <c r="S23" s="174">
+      <c r="S23" s="171">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24" s="120" t="s">
         <v>157</v>
       </c>
-      <c r="C24" s="166">
-        <v>0</v>
-      </c>
-      <c r="D24" s="153"/>
+      <c r="C24" s="163">
+        <v>1</v>
+      </c>
+      <c r="D24" s="150"/>
       <c r="G24" s="120" t="s">
         <v>132</v>
       </c>
       <c r="H24" s="120" t="s">
         <v>158</v>
       </c>
-      <c r="I24" s="175">
+      <c r="I24" s="172">
         <v>0</v>
       </c>
       <c r="J24" s="124"/>
-      <c r="K24" s="175">
-        <v>0</v>
+      <c r="K24" s="172">
+        <v>1</v>
       </c>
       <c r="L24" s="124"/>
-      <c r="M24" s="175">
+      <c r="M24" s="172">
         <v>0</v>
       </c>
       <c r="N24" s="124"/>
-      <c r="O24" s="175">
+      <c r="O24" s="172">
         <v>0</v>
       </c>
       <c r="P24" s="124"/>
-      <c r="Q24" s="175">
+      <c r="Q24" s="172">
         <v>0</v>
       </c>
       <c r="R24" s="124"/>
-      <c r="S24" s="174">
+      <c r="S24" s="171">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="120" t="s">
         <v>159</v>
       </c>
-      <c r="C25" s="167">
-        <v>0</v>
-      </c>
-      <c r="D25" s="153"/>
+      <c r="C25" s="164">
+        <v>1</v>
+      </c>
+      <c r="D25" s="150"/>
       <c r="G25" s="120" t="s">
         <v>160</v>
       </c>
       <c r="H25" s="120" t="s">
         <v>161</v>
       </c>
-      <c r="I25" s="175">
+      <c r="I25" s="172">
         <v>0</v>
       </c>
       <c r="J25" s="124"/>
-      <c r="K25" s="175">
+      <c r="K25" s="172">
         <v>0</v>
       </c>
       <c r="L25" s="124"/>
-      <c r="M25" s="175">
+      <c r="M25" s="172">
         <v>0</v>
       </c>
       <c r="N25" s="124"/>
-      <c r="O25" s="175">
+      <c r="O25" s="172">
         <v>0</v>
       </c>
       <c r="P25" s="124"/>
-      <c r="Q25" s="175">
+      <c r="Q25" s="172">
         <v>0</v>
       </c>
       <c r="R25" s="124"/>
-      <c r="S25" s="174">
+      <c r="S25" s="171">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -6703,37 +6706,37 @@
       <c r="B26" s="120" t="s">
         <v>162</v>
       </c>
-      <c r="C26" s="167">
-        <v>0</v>
-      </c>
-      <c r="D26" s="153"/>
+      <c r="C26" s="164">
+        <v>0</v>
+      </c>
+      <c r="D26" s="150"/>
       <c r="G26" s="120" t="s">
         <v>163</v>
       </c>
       <c r="H26" s="120" t="s">
         <v>164</v>
       </c>
-      <c r="I26" s="175">
+      <c r="I26" s="172">
         <v>0</v>
       </c>
       <c r="J26" s="124"/>
-      <c r="K26" s="175">
+      <c r="K26" s="172">
         <v>0</v>
       </c>
       <c r="L26" s="124"/>
-      <c r="M26" s="175">
+      <c r="M26" s="172">
         <v>0</v>
       </c>
       <c r="N26" s="124"/>
-      <c r="O26" s="175">
+      <c r="O26" s="172">
         <v>0</v>
       </c>
       <c r="P26" s="124"/>
-      <c r="Q26" s="175">
+      <c r="Q26" s="172">
         <v>0</v>
       </c>
       <c r="R26" s="124"/>
-      <c r="S26" s="174">
+      <c r="S26" s="171">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -6742,37 +6745,37 @@
       <c r="B27" s="120" t="s">
         <v>165</v>
       </c>
-      <c r="C27" s="167">
-        <v>0</v>
-      </c>
-      <c r="D27" s="153"/>
+      <c r="C27" s="164">
+        <v>0</v>
+      </c>
+      <c r="D27" s="150"/>
       <c r="G27" s="120" t="s">
         <v>166</v>
       </c>
       <c r="H27" s="120" t="s">
         <v>167</v>
       </c>
-      <c r="I27" s="175">
+      <c r="I27" s="172">
         <v>0</v>
       </c>
       <c r="J27" s="124"/>
-      <c r="K27" s="175">
+      <c r="K27" s="172">
         <v>0</v>
       </c>
       <c r="L27" s="124"/>
-      <c r="M27" s="175">
+      <c r="M27" s="172">
         <v>0</v>
       </c>
       <c r="N27" s="124"/>
-      <c r="O27" s="175">
+      <c r="O27" s="172">
         <v>0</v>
       </c>
       <c r="P27" s="124"/>
-      <c r="Q27" s="175">
+      <c r="Q27" s="172">
         <v>0</v>
       </c>
       <c r="R27" s="124"/>
-      <c r="S27" s="174">
+      <c r="S27" s="171">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -6781,38 +6784,38 @@
       <c r="B28" s="120" t="s">
         <v>168</v>
       </c>
-      <c r="C28" s="161">
+      <c r="C28" s="158">
         <f>SUM(C24:C25)-SUM(C26:C27)</f>
-        <v>0</v>
-      </c>
-      <c r="D28" s="153"/>
+        <v>2</v>
+      </c>
+      <c r="D28" s="150"/>
       <c r="G28" s="120" t="s">
         <v>169</v>
       </c>
       <c r="H28" s="120" t="s">
         <v>170</v>
       </c>
-      <c r="I28" s="175">
+      <c r="I28" s="172">
         <v>0</v>
       </c>
       <c r="J28" s="124"/>
-      <c r="K28" s="175">
+      <c r="K28" s="172">
         <v>0</v>
       </c>
       <c r="L28" s="124"/>
-      <c r="M28" s="175">
+      <c r="M28" s="172">
         <v>0</v>
       </c>
       <c r="N28" s="124"/>
-      <c r="O28" s="175">
+      <c r="O28" s="172">
         <v>0</v>
       </c>
       <c r="P28" s="124"/>
-      <c r="Q28" s="175">
+      <c r="Q28" s="172">
         <v>0</v>
       </c>
       <c r="R28" s="124"/>
-      <c r="S28" s="174">
+      <c r="S28" s="171">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -6821,35 +6824,35 @@
       <c r="B29" s="120" t="s">
         <v>171</v>
       </c>
-      <c r="C29" s="164"/>
-      <c r="D29" s="153"/>
+      <c r="C29" s="161"/>
+      <c r="D29" s="150"/>
       <c r="G29" s="120" t="s">
         <v>172</v>
       </c>
       <c r="H29" s="120" t="s">
         <v>173</v>
       </c>
-      <c r="I29" s="175">
+      <c r="I29" s="172">
         <v>0</v>
       </c>
       <c r="J29" s="124"/>
-      <c r="K29" s="175">
+      <c r="K29" s="172">
         <v>0</v>
       </c>
       <c r="L29" s="124"/>
-      <c r="M29" s="175">
+      <c r="M29" s="172">
         <v>0</v>
       </c>
       <c r="N29" s="124"/>
-      <c r="O29" s="175">
+      <c r="O29" s="172">
         <v>0</v>
       </c>
       <c r="P29" s="124"/>
-      <c r="Q29" s="175">
+      <c r="Q29" s="172">
         <v>0</v>
       </c>
       <c r="R29" s="124"/>
-      <c r="S29" s="174">
+      <c r="S29" s="171">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -6858,37 +6861,37 @@
       <c r="B30" s="120" t="s">
         <v>174</v>
       </c>
-      <c r="C30" s="156">
-        <v>0</v>
-      </c>
-      <c r="D30" s="153"/>
+      <c r="C30" s="153">
+        <v>0</v>
+      </c>
+      <c r="D30" s="150"/>
       <c r="G30" s="120" t="s">
         <v>175</v>
       </c>
       <c r="H30" s="120" t="s">
         <v>176</v>
       </c>
-      <c r="I30" s="175">
+      <c r="I30" s="172">
         <v>0</v>
       </c>
       <c r="J30" s="124"/>
-      <c r="K30" s="175">
+      <c r="K30" s="172">
         <v>0</v>
       </c>
       <c r="L30" s="124"/>
-      <c r="M30" s="175">
+      <c r="M30" s="172">
         <v>0</v>
       </c>
       <c r="N30" s="124"/>
-      <c r="O30" s="175">
+      <c r="O30" s="172">
         <v>0</v>
       </c>
       <c r="P30" s="124"/>
-      <c r="Q30" s="175">
+      <c r="Q30" s="172">
         <v>0</v>
       </c>
       <c r="R30" s="124"/>
-      <c r="S30" s="174">
+      <c r="S30" s="171">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -6897,195 +6900,195 @@
       <c r="B31" s="120" t="s">
         <v>177</v>
       </c>
-      <c r="C31" s="176">
-        <v>0</v>
-      </c>
-      <c r="D31" s="153"/>
+      <c r="C31" s="173">
+        <v>0</v>
+      </c>
+      <c r="D31" s="150"/>
       <c r="G31" s="120" t="s">
         <v>178</v>
       </c>
       <c r="H31" s="120" t="s">
         <v>179</v>
       </c>
-      <c r="I31" s="175">
+      <c r="I31" s="172">
         <v>0</v>
       </c>
       <c r="J31" s="124"/>
-      <c r="K31" s="175">
+      <c r="K31" s="172">
         <v>0</v>
       </c>
       <c r="L31" s="124"/>
-      <c r="M31" s="175">
+      <c r="M31" s="172">
         <v>0</v>
       </c>
       <c r="N31" s="124"/>
-      <c r="O31" s="175">
+      <c r="O31" s="172">
         <v>0</v>
       </c>
       <c r="P31" s="124"/>
-      <c r="Q31" s="175">
+      <c r="Q31" s="172">
         <v>0</v>
       </c>
       <c r="R31" s="124"/>
-      <c r="S31" s="174">
+      <c r="S31" s="171">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D32" s="148"/>
+      <c r="D32" s="145"/>
       <c r="G32" s="120" t="s">
         <v>180</v>
       </c>
       <c r="H32" s="120" t="s">
         <v>181</v>
       </c>
-      <c r="I32" s="175">
+      <c r="I32" s="172">
         <v>0</v>
       </c>
       <c r="J32" s="124"/>
-      <c r="K32" s="175">
+      <c r="K32" s="172">
         <v>0</v>
       </c>
       <c r="L32" s="124"/>
-      <c r="M32" s="175">
+      <c r="M32" s="172">
         <v>0</v>
       </c>
       <c r="N32" s="124"/>
-      <c r="O32" s="175">
+      <c r="O32" s="172">
         <v>0</v>
       </c>
       <c r="P32" s="124"/>
-      <c r="Q32" s="175">
+      <c r="Q32" s="172">
         <v>0</v>
       </c>
       <c r="R32" s="124"/>
-      <c r="S32" s="174">
+      <c r="S32" s="171">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D33" s="148"/>
-      <c r="H33" s="151" t="s">
+      <c r="D33" s="145"/>
+      <c r="H33" s="148" t="s">
         <v>182</v>
       </c>
-      <c r="I33" s="174">
+      <c r="I33" s="171">
         <f>SUM(I22:I32)</f>
-        <v>0</v>
-      </c>
-      <c r="J33" s="177"/>
-      <c r="K33" s="174">
+        <v>20</v>
+      </c>
+      <c r="J33" s="174"/>
+      <c r="K33" s="171">
         <f>SUM(K22:K32)</f>
-        <v>0</v>
-      </c>
-      <c r="L33" s="178"/>
-      <c r="M33" s="174">
+        <v>13</v>
+      </c>
+      <c r="L33" s="175"/>
+      <c r="M33" s="171">
         <f>SUM(M22:M32)</f>
         <v>0</v>
       </c>
-      <c r="N33" s="178"/>
-      <c r="O33" s="174">
+      <c r="N33" s="175"/>
+      <c r="O33" s="171">
         <f>SUM(O22:O32)</f>
         <v>0</v>
       </c>
-      <c r="P33" s="178"/>
-      <c r="Q33" s="174">
+      <c r="P33" s="175"/>
+      <c r="Q33" s="171">
         <f>SUM(Q22:Q32)</f>
         <v>0</v>
       </c>
-      <c r="S33" s="174">
+      <c r="S33" s="171">
         <f>SUM(S22:S32)</f>
-        <v>0</v>
+        <v>33</v>
       </c>
     </row>
     <row r="34" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="179"/>
-      <c r="B34" s="179"/>
-      <c r="D34" s="148"/>
-      <c r="I34" s="180"/>
-      <c r="J34" s="181"/>
-      <c r="K34" s="180"/>
-      <c r="L34" s="181"/>
+      <c r="A34" s="176"/>
+      <c r="B34" s="176"/>
+      <c r="D34" s="145"/>
+      <c r="I34" s="177"/>
+      <c r="J34" s="178"/>
+      <c r="K34" s="177"/>
+      <c r="L34" s="178"/>
       <c r="M34" s="124"/>
-      <c r="N34" s="181"/>
+      <c r="N34" s="178"/>
       <c r="O34" s="124"/>
-      <c r="P34" s="181"/>
-      <c r="Q34" s="180"/>
-      <c r="R34" s="178"/>
-      <c r="S34" s="182"/>
+      <c r="P34" s="178"/>
+      <c r="Q34" s="177"/>
+      <c r="R34" s="175"/>
+      <c r="S34" s="179"/>
     </row>
     <row r="35" spans="1:19" s="120" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="148" t="s">
+      <c r="A35" s="145" t="s">
         <v>183</v>
       </c>
-      <c r="B35" s="148"/>
-      <c r="C35" s="148"/>
-      <c r="D35" s="148"/>
-      <c r="G35" s="151"/>
+      <c r="B35" s="145"/>
+      <c r="C35" s="145"/>
+      <c r="D35" s="145"/>
+      <c r="G35" s="148"/>
       <c r="I35" s="118"/>
       <c r="K35" s="118"/>
       <c r="Q35" s="118"/>
       <c r="S35" s="118"/>
     </row>
     <row r="36" spans="1:19" s="120" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="148" t="s">
+      <c r="A36" s="145" t="s">
         <v>184</v>
       </c>
-      <c r="B36" s="148"/>
-      <c r="C36" s="148"/>
-      <c r="D36" s="148"/>
+      <c r="B36" s="145"/>
+      <c r="C36" s="145"/>
+      <c r="D36" s="145"/>
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="E37" s="148"/>
-      <c r="F37" s="148"/>
-      <c r="G37" s="148"/>
-      <c r="H37" s="148"/>
-      <c r="I37" s="148"/>
-      <c r="J37" s="148"/>
-      <c r="K37" s="148"/>
-      <c r="L37" s="148"/>
-      <c r="M37" s="148"/>
-      <c r="N37" s="148"/>
-      <c r="O37" s="148"/>
-      <c r="P37" s="148"/>
-      <c r="Q37" s="148"/>
-      <c r="R37" s="148"/>
-      <c r="S37" s="148"/>
+      <c r="E37" s="145"/>
+      <c r="F37" s="145"/>
+      <c r="G37" s="145"/>
+      <c r="H37" s="145"/>
+      <c r="I37" s="145"/>
+      <c r="J37" s="145"/>
+      <c r="K37" s="145"/>
+      <c r="L37" s="145"/>
+      <c r="M37" s="145"/>
+      <c r="N37" s="145"/>
+      <c r="O37" s="145"/>
+      <c r="P37" s="145"/>
+      <c r="Q37" s="145"/>
+      <c r="R37" s="145"/>
+      <c r="S37" s="145"/>
     </row>
     <row r="38" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="E38" s="148"/>
-      <c r="F38" s="148"/>
-      <c r="G38" s="148"/>
-      <c r="H38" s="148"/>
-      <c r="I38" s="148"/>
-      <c r="J38" s="148"/>
-      <c r="K38" s="148"/>
-      <c r="L38" s="148"/>
-      <c r="M38" s="148"/>
-      <c r="N38" s="148"/>
-      <c r="O38" s="148"/>
-      <c r="P38" s="148"/>
-      <c r="Q38" s="148"/>
-      <c r="R38" s="148"/>
-      <c r="S38" s="148"/>
+      <c r="E38" s="145"/>
+      <c r="F38" s="145"/>
+      <c r="G38" s="145"/>
+      <c r="H38" s="145"/>
+      <c r="I38" s="145"/>
+      <c r="J38" s="145"/>
+      <c r="K38" s="145"/>
+      <c r="L38" s="145"/>
+      <c r="M38" s="145"/>
+      <c r="N38" s="145"/>
+      <c r="O38" s="145"/>
+      <c r="P38" s="145"/>
+      <c r="Q38" s="145"/>
+      <c r="R38" s="145"/>
+      <c r="S38" s="145"/>
     </row>
     <row r="39" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="E39" s="148"/>
-      <c r="F39" s="148"/>
-      <c r="G39" s="148"/>
-      <c r="H39" s="148"/>
-      <c r="I39" s="148"/>
-      <c r="J39" s="148"/>
-      <c r="K39" s="148"/>
-      <c r="L39" s="148"/>
-      <c r="M39" s="148"/>
-      <c r="N39" s="148"/>
-      <c r="O39" s="148"/>
-      <c r="P39" s="148"/>
-      <c r="Q39" s="148"/>
-      <c r="R39" s="148"/>
-      <c r="S39" s="148"/>
+      <c r="E39" s="145"/>
+      <c r="F39" s="145"/>
+      <c r="G39" s="145"/>
+      <c r="H39" s="145"/>
+      <c r="I39" s="145"/>
+      <c r="J39" s="145"/>
+      <c r="K39" s="145"/>
+      <c r="L39" s="145"/>
+      <c r="M39" s="145"/>
+      <c r="N39" s="145"/>
+      <c r="O39" s="145"/>
+      <c r="P39" s="145"/>
+      <c r="Q39" s="145"/>
+      <c r="R39" s="145"/>
+      <c r="S39" s="145"/>
     </row>
   </sheetData>
   <sheetProtection sheet="1" formatCells="0" formatColumns="0" formatRows="0"/>
@@ -7094,8 +7097,8 @@
     <mergeCell ref="F20:H20"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.75" right="0.75" top="0.5" bottom="0.5" header="0.51180555555555551" footer="0.51180555555555551"/>
-  <pageSetup paperSize="14" scale="73" firstPageNumber="0" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <pageMargins left="0.74803149606299213" right="0.74803149606299213" top="0.51181102362204722" bottom="0.51181102362204722" header="0.51181102362204722" footer="0.51181102362204722"/>
+  <pageSetup paperSize="256" scale="90" firstPageNumber="0" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -7131,337 +7134,335 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="321" t="s">
+      <c r="A1" s="251" t="s">
         <v>185</v>
       </c>
-      <c r="B1" s="306"/>
-      <c r="C1" s="306"/>
-      <c r="D1" s="306"/>
-      <c r="E1" s="306"/>
-      <c r="F1" s="306"/>
-      <c r="G1" s="306"/>
-      <c r="H1" s="306"/>
-      <c r="I1" s="306"/>
-      <c r="J1" s="306"/>
-      <c r="K1" s="306"/>
-      <c r="L1" s="306"/>
-      <c r="M1" s="306"/>
-      <c r="N1" s="306"/>
-      <c r="O1" s="306"/>
-      <c r="P1" s="306"/>
-      <c r="Q1" s="306"/>
-      <c r="R1" s="306"/>
-      <c r="S1" s="306"/>
-      <c r="T1" s="306"/>
-      <c r="U1" s="306"/>
-      <c r="V1" s="306"/>
-      <c r="W1" s="306"/>
-      <c r="X1" s="306"/>
-      <c r="Y1" s="306"/>
-      <c r="Z1" s="306"/>
-      <c r="AA1" s="306"/>
+      <c r="B1" s="244"/>
+      <c r="C1" s="244"/>
+      <c r="D1" s="244"/>
+      <c r="E1" s="244"/>
+      <c r="F1" s="244"/>
+      <c r="G1" s="244"/>
+      <c r="H1" s="244"/>
+      <c r="I1" s="244"/>
+      <c r="J1" s="244"/>
+      <c r="K1" s="244"/>
+      <c r="L1" s="244"/>
+      <c r="M1" s="244"/>
+      <c r="N1" s="244"/>
+      <c r="O1" s="244"/>
+      <c r="P1" s="244"/>
+      <c r="Q1" s="244"/>
+      <c r="R1" s="244"/>
+      <c r="S1" s="244"/>
+      <c r="T1" s="244"/>
+      <c r="U1" s="244"/>
+      <c r="V1" s="244"/>
+      <c r="W1" s="244"/>
+      <c r="X1" s="244"/>
+      <c r="Y1" s="244"/>
+      <c r="Z1" s="244"/>
+      <c r="AA1" s="244"/>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A2" s="151" t="s">
+      <c r="A2" s="148" t="s">
         <v>186</v>
       </c>
-      <c r="B2" s="151"/>
-      <c r="C2" s="151"/>
-      <c r="D2" s="151"/>
-      <c r="E2" s="151"/>
-      <c r="F2" s="151"/>
-      <c r="G2" s="151"/>
-      <c r="N2" s="183"/>
-      <c r="P2" s="151" t="s">
+      <c r="B2" s="148"/>
+      <c r="C2" s="148"/>
+      <c r="D2" s="148"/>
+      <c r="E2" s="148"/>
+      <c r="F2" s="148"/>
+      <c r="G2" s="148"/>
+      <c r="N2" s="180"/>
+      <c r="P2" s="148" t="s">
         <v>187</v>
       </c>
-      <c r="Q2" s="151"/>
-      <c r="R2" s="151"/>
-      <c r="S2" s="151"/>
-      <c r="T2" s="151"/>
-      <c r="U2" s="151"/>
-      <c r="V2" s="151"/>
-      <c r="W2" s="151"/>
-      <c r="X2" s="151"/>
-      <c r="Y2" s="151"/>
-      <c r="Z2" s="151"/>
-      <c r="AA2" s="151"/>
+      <c r="Q2" s="148"/>
+      <c r="R2" s="148"/>
+      <c r="S2" s="148"/>
+      <c r="T2" s="148"/>
+      <c r="U2" s="148"/>
+      <c r="V2" s="148"/>
+      <c r="W2" s="148"/>
+      <c r="X2" s="148"/>
+      <c r="Y2" s="148"/>
+      <c r="Z2" s="148"/>
+      <c r="AA2" s="148"/>
     </row>
     <row r="3" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="151" t="s">
+      <c r="A3" s="148" t="s">
         <v>188</v>
       </c>
-      <c r="B3" s="151"/>
-      <c r="C3" s="151"/>
-      <c r="D3" s="151"/>
-      <c r="E3" s="151"/>
-      <c r="F3" s="151"/>
-      <c r="G3" s="151"/>
-      <c r="N3" s="183"/>
+      <c r="B3" s="148"/>
+      <c r="C3" s="148"/>
+      <c r="D3" s="148"/>
+      <c r="E3" s="148"/>
+      <c r="F3" s="148"/>
+      <c r="G3" s="148"/>
+      <c r="N3" s="180"/>
       <c r="Q3" s="120" t="s">
         <v>110</v>
       </c>
       <c r="R3" s="120" t="s">
         <v>189</v>
       </c>
-      <c r="Z3" s="184">
-        <v>0</v>
-      </c>
+      <c r="Z3" s="181"/>
     </row>
     <row r="4" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="H4" s="168"/>
-      <c r="I4" s="168"/>
-      <c r="J4" s="168"/>
-      <c r="K4" s="168"/>
-      <c r="L4" s="168"/>
-      <c r="M4" s="168"/>
-      <c r="N4" s="185"/>
-      <c r="W4" s="165"/>
+      <c r="H4" s="165"/>
+      <c r="I4" s="165"/>
+      <c r="J4" s="165"/>
+      <c r="K4" s="165"/>
+      <c r="L4" s="165"/>
+      <c r="M4" s="165"/>
+      <c r="N4" s="182"/>
+      <c r="W4" s="162"/>
     </row>
     <row r="5" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="120" t="s">
         <v>110</v>
       </c>
-      <c r="C5" s="310" t="s">
+      <c r="C5" s="243" t="s">
         <v>190</v>
       </c>
-      <c r="D5" s="306"/>
-      <c r="E5" s="306"/>
-      <c r="F5" s="306"/>
-      <c r="G5" s="306"/>
-      <c r="H5" s="168"/>
-      <c r="I5" s="168"/>
-      <c r="J5" s="168"/>
-      <c r="K5" s="168"/>
-      <c r="L5" s="168"/>
-      <c r="M5" s="168"/>
-      <c r="N5" s="185"/>
+      <c r="D5" s="244"/>
+      <c r="E5" s="244"/>
+      <c r="F5" s="244"/>
+      <c r="G5" s="244"/>
+      <c r="H5" s="165"/>
+      <c r="I5" s="165"/>
+      <c r="J5" s="165"/>
+      <c r="K5" s="165"/>
+      <c r="L5" s="165"/>
+      <c r="M5" s="165"/>
+      <c r="N5" s="182"/>
       <c r="Q5" s="120" t="s">
         <v>120</v>
       </c>
       <c r="R5" s="120" t="s">
         <v>191</v>
       </c>
-      <c r="X5" s="186"/>
-      <c r="Y5" s="186"/>
-      <c r="Z5" s="186"/>
+      <c r="X5" s="183"/>
+      <c r="Y5" s="183"/>
+      <c r="Z5" s="183"/>
     </row>
     <row r="6" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C6" s="310" t="s">
+      <c r="C6" s="243" t="s">
         <v>192</v>
       </c>
-      <c r="D6" s="306"/>
-      <c r="E6" s="306"/>
-      <c r="F6" s="306"/>
-      <c r="G6" s="306"/>
-      <c r="H6" s="184">
-        <v>0</v>
-      </c>
-      <c r="N6" s="183"/>
-      <c r="R6" s="317" t="s">
+      <c r="D6" s="244"/>
+      <c r="E6" s="244"/>
+      <c r="F6" s="244"/>
+      <c r="G6" s="244"/>
+      <c r="H6" s="181">
+        <v>0</v>
+      </c>
+      <c r="N6" s="180"/>
+      <c r="R6" s="249" t="s">
         <v>193</v>
       </c>
-      <c r="S6" s="314"/>
-      <c r="T6" s="314"/>
-      <c r="U6" s="314"/>
-      <c r="V6" s="314"/>
-      <c r="W6" s="314"/>
-      <c r="X6" s="314"/>
-      <c r="Y6" s="314"/>
-      <c r="Z6" s="314"/>
-      <c r="AA6" s="187"/>
+      <c r="S6" s="250"/>
+      <c r="T6" s="250"/>
+      <c r="U6" s="250"/>
+      <c r="V6" s="250"/>
+      <c r="W6" s="250"/>
+      <c r="X6" s="250"/>
+      <c r="Y6" s="250"/>
+      <c r="Z6" s="250"/>
+      <c r="AA6" s="184"/>
     </row>
     <row r="7" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C7" s="310" t="s">
+      <c r="C7" s="243" t="s">
         <v>194</v>
       </c>
-      <c r="D7" s="306"/>
-      <c r="E7" s="306"/>
-      <c r="F7" s="306"/>
-      <c r="G7" s="306"/>
-      <c r="H7" s="188">
-        <v>0</v>
-      </c>
-      <c r="N7" s="183"/>
-      <c r="R7" s="314"/>
-      <c r="S7" s="314"/>
-      <c r="T7" s="314"/>
-      <c r="U7" s="314"/>
-      <c r="V7" s="314"/>
-      <c r="W7" s="314"/>
-      <c r="X7" s="314"/>
-      <c r="Y7" s="314"/>
-      <c r="Z7" s="314"/>
-      <c r="AA7" s="187"/>
+      <c r="D7" s="244"/>
+      <c r="E7" s="244"/>
+      <c r="F7" s="244"/>
+      <c r="G7" s="244"/>
+      <c r="H7" s="185">
+        <v>0</v>
+      </c>
+      <c r="N7" s="180"/>
+      <c r="R7" s="250"/>
+      <c r="S7" s="250"/>
+      <c r="T7" s="250"/>
+      <c r="U7" s="250"/>
+      <c r="V7" s="250"/>
+      <c r="W7" s="250"/>
+      <c r="X7" s="250"/>
+      <c r="Y7" s="250"/>
+      <c r="Z7" s="250"/>
+      <c r="AA7" s="184"/>
     </row>
     <row r="8" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C8" s="148"/>
-      <c r="D8" s="148"/>
-      <c r="E8" s="148"/>
-      <c r="F8" s="148"/>
-      <c r="G8" s="148"/>
-      <c r="H8" s="189">
+      <c r="C8" s="145"/>
+      <c r="D8" s="145"/>
+      <c r="E8" s="145"/>
+      <c r="F8" s="145"/>
+      <c r="G8" s="145"/>
+      <c r="H8" s="186">
         <f>SUM(H6:H7)</f>
         <v>0</v>
       </c>
-      <c r="N8" s="183"/>
-      <c r="R8" s="314"/>
-      <c r="S8" s="314"/>
-      <c r="T8" s="314"/>
-      <c r="U8" s="314"/>
-      <c r="V8" s="314"/>
-      <c r="W8" s="314"/>
-      <c r="X8" s="314"/>
-      <c r="Y8" s="314"/>
-      <c r="Z8" s="314"/>
-      <c r="AA8" s="187"/>
+      <c r="N8" s="180"/>
+      <c r="R8" s="250"/>
+      <c r="S8" s="250"/>
+      <c r="T8" s="250"/>
+      <c r="U8" s="250"/>
+      <c r="V8" s="250"/>
+      <c r="W8" s="250"/>
+      <c r="X8" s="250"/>
+      <c r="Y8" s="250"/>
+      <c r="Z8" s="250"/>
+      <c r="AA8" s="184"/>
     </row>
     <row r="9" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H9" s="190" t="s">
+      <c r="H9" s="187" t="s">
         <v>195</v>
       </c>
-      <c r="J9" s="191" t="s">
+      <c r="J9" s="188" t="s">
         <v>196</v>
       </c>
-      <c r="K9" s="191"/>
-      <c r="L9" s="191" t="s">
+      <c r="K9" s="188"/>
+      <c r="L9" s="188" t="s">
         <v>197</v>
       </c>
-      <c r="N9" s="183"/>
-      <c r="R9" s="312"/>
-      <c r="S9" s="312"/>
-      <c r="T9" s="312"/>
-      <c r="U9" s="312"/>
-      <c r="V9" s="312"/>
-      <c r="W9" s="312"/>
-      <c r="X9" s="312"/>
-      <c r="Y9" s="312"/>
-      <c r="Z9" s="312"/>
-      <c r="AA9" s="151"/>
+      <c r="N9" s="180"/>
+      <c r="R9" s="248"/>
+      <c r="S9" s="248"/>
+      <c r="T9" s="248"/>
+      <c r="U9" s="248"/>
+      <c r="V9" s="248"/>
+      <c r="W9" s="248"/>
+      <c r="X9" s="248"/>
+      <c r="Y9" s="248"/>
+      <c r="Z9" s="248"/>
+      <c r="AA9" s="148"/>
     </row>
     <row r="10" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C10" s="120" t="s">
         <v>198</v>
       </c>
-      <c r="H10" s="184">
-        <v>0</v>
-      </c>
-      <c r="I10" s="168"/>
-      <c r="J10" s="184">
-        <v>0</v>
-      </c>
-      <c r="K10" s="192"/>
-      <c r="L10" s="184">
-        <v>0</v>
-      </c>
-      <c r="N10" s="183"/>
-      <c r="X10" s="151"/>
-      <c r="Y10" s="151"/>
-      <c r="Z10" s="193"/>
+      <c r="H10" s="181">
+        <v>0</v>
+      </c>
+      <c r="I10" s="165"/>
+      <c r="J10" s="181">
+        <v>0</v>
+      </c>
+      <c r="K10" s="189"/>
+      <c r="L10" s="181">
+        <v>0</v>
+      </c>
+      <c r="N10" s="180"/>
+      <c r="X10" s="148"/>
+      <c r="Y10" s="148"/>
+      <c r="Z10" s="190"/>
     </row>
     <row r="11" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="M11" s="168"/>
-      <c r="N11" s="185"/>
-      <c r="P11" s="151" t="s">
+      <c r="M11" s="165"/>
+      <c r="N11" s="182"/>
+      <c r="P11" s="148" t="s">
         <v>199</v>
       </c>
-      <c r="W11" s="151"/>
-      <c r="Z11" s="184">
-        <v>6</v>
-      </c>
-      <c r="AA11" s="194"/>
+      <c r="W11" s="148"/>
+      <c r="Z11" s="181">
+        <v>4</v>
+      </c>
+      <c r="AA11" s="191"/>
     </row>
     <row r="12" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="H12" s="168"/>
-      <c r="M12" s="168"/>
-      <c r="N12" s="185"/>
-      <c r="Q12" s="151"/>
-      <c r="R12" s="151"/>
-      <c r="S12" s="151"/>
-      <c r="T12" s="151"/>
-      <c r="U12" s="151"/>
-      <c r="V12" s="151"/>
-      <c r="W12" s="165"/>
-      <c r="AA12" s="194"/>
+      <c r="H12" s="165"/>
+      <c r="M12" s="165"/>
+      <c r="N12" s="182"/>
+      <c r="Q12" s="148"/>
+      <c r="R12" s="148"/>
+      <c r="S12" s="148"/>
+      <c r="T12" s="148"/>
+      <c r="U12" s="148"/>
+      <c r="V12" s="148"/>
+      <c r="W12" s="162"/>
+      <c r="AA12" s="191"/>
     </row>
     <row r="13" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="120" t="s">
         <v>120</v>
       </c>
-      <c r="C13" s="148" t="s">
+      <c r="C13" s="145" t="s">
         <v>200</v>
       </c>
-      <c r="D13" s="148"/>
-      <c r="E13" s="148"/>
-      <c r="F13" s="148"/>
-      <c r="G13" s="148"/>
-      <c r="H13" s="168"/>
-      <c r="N13" s="183"/>
-      <c r="P13" s="151" t="s">
+      <c r="D13" s="145"/>
+      <c r="E13" s="145"/>
+      <c r="F13" s="145"/>
+      <c r="G13" s="145"/>
+      <c r="H13" s="165"/>
+      <c r="N13" s="180"/>
+      <c r="P13" s="148" t="s">
         <v>201</v>
       </c>
-      <c r="W13" s="165"/>
+      <c r="W13" s="162"/>
       <c r="Z13" s="11"/>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="C14" s="148" t="s">
+      <c r="C14" s="145" t="s">
         <v>202</v>
       </c>
-      <c r="D14" s="148"/>
-      <c r="E14" s="148"/>
-      <c r="F14" s="148"/>
-      <c r="G14" s="148"/>
-      <c r="N14" s="183"/>
+      <c r="D14" s="145"/>
+      <c r="E14" s="145"/>
+      <c r="F14" s="145"/>
+      <c r="G14" s="145"/>
+      <c r="N14" s="180"/>
     </row>
     <row r="15" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C15" s="310" t="s">
+      <c r="C15" s="243" t="s">
         <v>192</v>
       </c>
-      <c r="D15" s="306"/>
-      <c r="E15" s="306"/>
-      <c r="F15" s="306"/>
-      <c r="G15" s="306"/>
-      <c r="H15" s="184">
-        <v>0</v>
-      </c>
-      <c r="N15" s="183"/>
+      <c r="D15" s="244"/>
+      <c r="E15" s="244"/>
+      <c r="F15" s="244"/>
+      <c r="G15" s="244"/>
+      <c r="H15" s="181">
+        <v>0</v>
+      </c>
+      <c r="N15" s="180"/>
       <c r="Q15" s="120" t="s">
         <v>203</v>
       </c>
-      <c r="Z15" s="184">
-        <v>0</v>
-      </c>
-      <c r="AA15" s="151"/>
+      <c r="Z15" s="181">
+        <v>0</v>
+      </c>
+      <c r="AA15" s="148"/>
     </row>
     <row r="16" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C16" s="310" t="s">
+      <c r="C16" s="243" t="s">
         <v>194</v>
       </c>
-      <c r="D16" s="306"/>
-      <c r="E16" s="306"/>
-      <c r="F16" s="306"/>
-      <c r="G16" s="306"/>
-      <c r="H16" s="188">
-        <v>0</v>
-      </c>
-      <c r="N16" s="183"/>
+      <c r="D16" s="244"/>
+      <c r="E16" s="244"/>
+      <c r="F16" s="244"/>
+      <c r="G16" s="244"/>
+      <c r="H16" s="185">
+        <v>0</v>
+      </c>
+      <c r="N16" s="180"/>
       <c r="Q16" s="120" t="s">
         <v>204</v>
       </c>
-      <c r="Z16" s="188">
+      <c r="Z16" s="185">
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="H17" s="189">
+      <c r="H17" s="186">
         <f>SUM(H15:H16)</f>
         <v>0</v>
       </c>
-      <c r="N17" s="183"/>
+      <c r="N17" s="180"/>
       <c r="Q17" s="120" t="s">
         <v>205</v>
       </c>
-      <c r="Z17" s="188">
+      <c r="Z17" s="185">
         <v>0</v>
       </c>
     </row>
@@ -7469,18 +7470,18 @@
       <c r="C18" s="120" t="s">
         <v>206</v>
       </c>
-      <c r="F18" s="168"/>
-      <c r="H18" s="168" t="s">
+      <c r="F18" s="165"/>
+      <c r="H18" s="165" t="s">
         <v>207</v>
       </c>
-      <c r="J18" s="168" t="s">
+      <c r="J18" s="165" t="s">
         <v>208</v>
       </c>
-      <c r="N18" s="183"/>
+      <c r="N18" s="180"/>
       <c r="Q18" s="120" t="s">
         <v>209</v>
       </c>
-      <c r="Z18" s="188">
+      <c r="Z18" s="185">
         <v>0</v>
       </c>
     </row>
@@ -7488,448 +7489,439 @@
       <c r="C19" s="120" t="s">
         <v>210</v>
       </c>
-      <c r="F19" s="165"/>
-      <c r="H19" s="184">
-        <v>0</v>
-      </c>
-      <c r="I19" s="168"/>
-      <c r="J19" s="184">
-        <v>0</v>
-      </c>
-      <c r="K19" s="168"/>
-      <c r="N19" s="183"/>
-      <c r="P19" s="195"/>
-      <c r="Q19" s="148"/>
-      <c r="R19" s="148"/>
-      <c r="S19" s="148"/>
-      <c r="T19" s="148"/>
-      <c r="U19" s="148"/>
-      <c r="V19" s="148"/>
-      <c r="W19" s="195"/>
-      <c r="X19" s="148"/>
-      <c r="Y19" s="148"/>
-      <c r="Z19" s="170"/>
+      <c r="F19" s="162"/>
+      <c r="H19" s="181">
+        <v>0</v>
+      </c>
+      <c r="I19" s="165"/>
+      <c r="J19" s="181">
+        <v>0</v>
+      </c>
+      <c r="K19" s="165"/>
+      <c r="N19" s="180"/>
+      <c r="P19" s="192"/>
+      <c r="Q19" s="145"/>
+      <c r="R19" s="145"/>
+      <c r="S19" s="145"/>
+      <c r="T19" s="145"/>
+      <c r="U19" s="145"/>
+      <c r="V19" s="145"/>
+      <c r="W19" s="192"/>
+      <c r="X19" s="145"/>
+      <c r="Y19" s="145"/>
+      <c r="Z19" s="167"/>
     </row>
     <row r="20" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="N20" s="183"/>
-      <c r="Q20" s="195"/>
-      <c r="R20" s="195"/>
-      <c r="S20" s="195"/>
-      <c r="T20" s="195"/>
-      <c r="U20" s="195"/>
-      <c r="V20" s="195"/>
-      <c r="X20" s="195"/>
-      <c r="Y20" s="195"/>
-      <c r="Z20" s="195"/>
+      <c r="N20" s="180"/>
+      <c r="Q20" s="192"/>
+      <c r="R20" s="192"/>
+      <c r="S20" s="192"/>
+      <c r="T20" s="192"/>
+      <c r="U20" s="192"/>
+      <c r="V20" s="192"/>
+      <c r="X20" s="192"/>
+      <c r="Y20" s="192"/>
+      <c r="Z20" s="192"/>
     </row>
     <row r="21" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="N21" s="183"/>
+      <c r="N21" s="180"/>
     </row>
     <row r="23" spans="1:27" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="315" t="s">
+      <c r="A23" s="257" t="s">
         <v>211</v>
       </c>
-      <c r="B23" s="306"/>
-      <c r="C23" s="306"/>
-      <c r="D23" s="306"/>
-      <c r="E23" s="306"/>
-      <c r="F23" s="306"/>
-      <c r="G23" s="306"/>
-      <c r="H23" s="306"/>
-      <c r="I23" s="306"/>
-      <c r="J23" s="306"/>
-      <c r="K23" s="306"/>
-      <c r="L23" s="306"/>
-      <c r="M23" s="306"/>
-      <c r="N23" s="306"/>
-      <c r="O23" s="306"/>
-      <c r="P23" s="306"/>
-      <c r="Q23" s="306"/>
-      <c r="R23" s="306"/>
-      <c r="S23" s="306"/>
-      <c r="T23" s="306"/>
-      <c r="U23" s="306"/>
-      <c r="V23" s="306"/>
-      <c r="W23" s="306"/>
-      <c r="X23" s="306"/>
-      <c r="Y23" s="306"/>
-      <c r="Z23" s="306"/>
-      <c r="AA23" s="306"/>
+      <c r="B23" s="244"/>
+      <c r="C23" s="244"/>
+      <c r="D23" s="244"/>
+      <c r="E23" s="244"/>
+      <c r="F23" s="244"/>
+      <c r="G23" s="244"/>
+      <c r="H23" s="244"/>
+      <c r="I23" s="244"/>
+      <c r="J23" s="244"/>
+      <c r="K23" s="244"/>
+      <c r="L23" s="244"/>
+      <c r="M23" s="244"/>
+      <c r="N23" s="244"/>
+      <c r="O23" s="244"/>
+      <c r="P23" s="244"/>
+      <c r="Q23" s="244"/>
+      <c r="R23" s="244"/>
+      <c r="S23" s="244"/>
+      <c r="T23" s="244"/>
+      <c r="U23" s="244"/>
+      <c r="V23" s="244"/>
+      <c r="W23" s="244"/>
+      <c r="X23" s="244"/>
+      <c r="Y23" s="244"/>
+      <c r="Z23" s="244"/>
+      <c r="AA23" s="244"/>
     </row>
     <row r="26" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="151"/>
-      <c r="B26" s="196"/>
-      <c r="C26" s="196"/>
-      <c r="D26" s="311" t="s">
+      <c r="A26" s="148"/>
+      <c r="B26" s="193"/>
+      <c r="C26" s="193"/>
+      <c r="D26" s="247" t="s">
+        <v>233</v>
+      </c>
+      <c r="E26" s="248"/>
+      <c r="F26" s="248"/>
+      <c r="G26" s="248"/>
+      <c r="H26" s="248"/>
+      <c r="I26" s="248"/>
+      <c r="J26" s="248"/>
+      <c r="K26" s="248"/>
+      <c r="L26" s="248"/>
+      <c r="M26" s="193"/>
+      <c r="N26" s="193"/>
+      <c r="O26" s="148"/>
+      <c r="P26" s="148"/>
+      <c r="Q26" s="148"/>
+      <c r="R26" s="247" t="s">
+        <v>231</v>
+      </c>
+      <c r="S26" s="248"/>
+      <c r="T26" s="248"/>
+      <c r="U26" s="248"/>
+      <c r="V26" s="248"/>
+      <c r="W26" s="248"/>
+      <c r="X26" s="248"/>
+      <c r="Y26" s="248"/>
+      <c r="Z26" s="248"/>
+      <c r="AA26" s="148"/>
+    </row>
+    <row r="27" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="C27" s="148"/>
+      <c r="D27" s="245" t="s">
+        <v>234</v>
+      </c>
+      <c r="E27" s="246"/>
+      <c r="F27" s="246"/>
+      <c r="G27" s="246"/>
+      <c r="H27" s="246"/>
+      <c r="I27" s="246"/>
+      <c r="J27" s="246"/>
+      <c r="K27" s="246"/>
+      <c r="L27" s="246"/>
+      <c r="M27" s="148"/>
+      <c r="N27" s="148"/>
+      <c r="O27" s="148"/>
+      <c r="P27" s="148"/>
+      <c r="Q27" s="148"/>
+      <c r="R27" s="245" t="s">
+        <v>232</v>
+      </c>
+      <c r="S27" s="246"/>
+      <c r="T27" s="246"/>
+      <c r="U27" s="246"/>
+      <c r="V27" s="246"/>
+      <c r="W27" s="246"/>
+      <c r="X27" s="246"/>
+      <c r="Y27" s="246"/>
+      <c r="Z27" s="246"/>
+      <c r="AA27" s="148"/>
+    </row>
+    <row r="28" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="D28" s="256"/>
+      <c r="E28" s="250"/>
+      <c r="F28" s="250"/>
+      <c r="G28" s="250"/>
+      <c r="H28" s="250"/>
+      <c r="I28" s="250"/>
+      <c r="J28" s="250"/>
+      <c r="K28" s="250"/>
+      <c r="L28" s="250"/>
+      <c r="R28" s="256"/>
+      <c r="S28" s="250"/>
+      <c r="T28" s="250"/>
+      <c r="U28" s="250"/>
+      <c r="V28" s="250"/>
+      <c r="W28" s="250"/>
+      <c r="X28" s="250"/>
+      <c r="Y28" s="250"/>
+      <c r="Z28" s="250"/>
+    </row>
+    <row r="29" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="D29" s="254" t="s">
         <v>212</v>
       </c>
-      <c r="E26" s="312"/>
-      <c r="F26" s="312"/>
-      <c r="G26" s="312"/>
-      <c r="H26" s="312"/>
-      <c r="I26" s="312"/>
-      <c r="J26" s="312"/>
-      <c r="K26" s="312"/>
-      <c r="L26" s="312"/>
-      <c r="M26" s="196"/>
-      <c r="N26" s="196"/>
-      <c r="O26" s="151"/>
-      <c r="P26" s="151"/>
-      <c r="Q26" s="151"/>
-      <c r="R26" s="311" t="s">
+      <c r="E29" s="244"/>
+      <c r="F29" s="244"/>
+      <c r="G29" s="244"/>
+      <c r="H29" s="244"/>
+      <c r="I29" s="244"/>
+      <c r="J29" s="244"/>
+      <c r="K29" s="244"/>
+      <c r="L29" s="244"/>
+      <c r="P29" s="165"/>
+      <c r="Q29" s="165"/>
+      <c r="R29" s="165"/>
+      <c r="S29" s="165"/>
+      <c r="T29" s="165"/>
+      <c r="U29" s="165"/>
+      <c r="V29" s="165"/>
+      <c r="W29" s="165"/>
+      <c r="X29" s="165"/>
+      <c r="Y29" s="165"/>
+      <c r="Z29" s="165"/>
+      <c r="AA29" s="165"/>
+    </row>
+    <row r="30" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="C30" s="159"/>
+      <c r="D30" s="159" t="s">
         <v>213</v>
       </c>
-      <c r="S26" s="312"/>
-      <c r="T26" s="312"/>
-      <c r="U26" s="312"/>
-      <c r="V26" s="312"/>
-      <c r="W26" s="312"/>
-      <c r="X26" s="312"/>
-      <c r="Y26" s="312"/>
-      <c r="Z26" s="312"/>
-      <c r="AA26" s="151"/>
-    </row>
-    <row r="27" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="C27" s="151"/>
-      <c r="D27" s="308" t="s">
+      <c r="E30" s="159"/>
+      <c r="F30" s="159"/>
+      <c r="G30" s="159"/>
+      <c r="H30" s="159"/>
+      <c r="I30" s="159"/>
+      <c r="J30" s="159"/>
+      <c r="K30" s="159"/>
+      <c r="L30" s="159"/>
+      <c r="M30" s="159"/>
+      <c r="P30" s="165"/>
+      <c r="Q30" s="165"/>
+      <c r="R30" s="165"/>
+      <c r="S30" s="165"/>
+      <c r="T30" s="165"/>
+      <c r="U30" s="165"/>
+      <c r="V30" s="165"/>
+      <c r="W30" s="165"/>
+      <c r="X30" s="165"/>
+      <c r="Y30" s="165"/>
+      <c r="Z30" s="165"/>
+      <c r="AA30" s="165"/>
+    </row>
+    <row r="31" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C31" s="165"/>
+      <c r="D31" s="194"/>
+      <c r="E31" s="195" t="s">
         <v>214</v>
       </c>
-      <c r="E27" s="309"/>
-      <c r="F27" s="309"/>
-      <c r="G27" s="309"/>
-      <c r="H27" s="309"/>
-      <c r="I27" s="309"/>
-      <c r="J27" s="309"/>
-      <c r="K27" s="309"/>
-      <c r="L27" s="309"/>
-      <c r="M27" s="151"/>
-      <c r="N27" s="151"/>
-      <c r="O27" s="151"/>
-      <c r="P27" s="151"/>
-      <c r="Q27" s="151"/>
-      <c r="R27" s="308" t="s">
+      <c r="F31" s="194"/>
+      <c r="G31" s="194"/>
+      <c r="H31" s="194"/>
+      <c r="I31" s="194"/>
+      <c r="J31" s="194"/>
+      <c r="K31" s="194"/>
+      <c r="L31" s="194"/>
+      <c r="P31" s="165"/>
+      <c r="Q31" s="165"/>
+      <c r="R31" s="165"/>
+      <c r="S31" s="165"/>
+      <c r="T31" s="165"/>
+      <c r="U31" s="165"/>
+      <c r="V31" s="165"/>
+      <c r="W31" s="165"/>
+      <c r="X31" s="165"/>
+      <c r="Y31" s="165"/>
+      <c r="Z31" s="165"/>
+      <c r="AA31" s="165"/>
+    </row>
+    <row r="32" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="B32" s="165"/>
+      <c r="C32" s="165"/>
+      <c r="D32" s="165"/>
+      <c r="E32" s="145" t="s">
         <v>215</v>
       </c>
-      <c r="S27" s="309"/>
-      <c r="T27" s="309"/>
-      <c r="U27" s="309"/>
-      <c r="V27" s="309"/>
-      <c r="W27" s="309"/>
-      <c r="X27" s="309"/>
-      <c r="Y27" s="309"/>
-      <c r="Z27" s="309"/>
-      <c r="AA27" s="151"/>
-    </row>
-    <row r="28" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="D28" s="313" t="s">
+      <c r="F32" s="165"/>
+      <c r="H32" s="145"/>
+      <c r="P32" s="165"/>
+      <c r="Q32" s="165"/>
+      <c r="R32" s="165"/>
+      <c r="S32" s="165"/>
+      <c r="T32" s="165"/>
+      <c r="U32" s="165"/>
+      <c r="V32" s="165"/>
+      <c r="W32" s="165"/>
+      <c r="X32" s="165"/>
+      <c r="Y32" s="165"/>
+      <c r="Z32" s="165"/>
+      <c r="AA32" s="165"/>
+    </row>
+    <row r="33" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="B33" s="165"/>
+      <c r="C33" s="165"/>
+      <c r="D33" s="165"/>
+      <c r="E33" s="145"/>
+      <c r="F33" s="165"/>
+      <c r="H33" s="145"/>
+      <c r="P33" s="165"/>
+      <c r="Q33" s="165"/>
+      <c r="R33" s="165"/>
+      <c r="S33" s="165"/>
+      <c r="T33" s="165"/>
+      <c r="U33" s="165"/>
+      <c r="V33" s="165"/>
+      <c r="W33" s="165"/>
+      <c r="X33" s="165"/>
+      <c r="Y33" s="165"/>
+      <c r="Z33" s="165"/>
+      <c r="AA33" s="165"/>
+    </row>
+    <row r="34" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="254" t="s">
         <v>216</v>
       </c>
-      <c r="E28" s="314"/>
-      <c r="F28" s="314"/>
-      <c r="G28" s="314"/>
-      <c r="H28" s="314"/>
-      <c r="I28" s="314"/>
-      <c r="J28" s="314"/>
-      <c r="K28" s="314"/>
-      <c r="L28" s="314"/>
-      <c r="R28" s="313" t="s">
+      <c r="B34" s="244"/>
+      <c r="C34" s="244"/>
+      <c r="D34" s="244"/>
+      <c r="E34" s="244"/>
+      <c r="F34" s="244"/>
+      <c r="G34" s="196"/>
+      <c r="H34" s="165" t="s">
         <v>217</v>
       </c>
-      <c r="S28" s="314"/>
-      <c r="T28" s="314"/>
-      <c r="U28" s="314"/>
-      <c r="V28" s="314"/>
-      <c r="W28" s="314"/>
-      <c r="X28" s="314"/>
-      <c r="Y28" s="314"/>
-      <c r="Z28" s="314"/>
-    </row>
-    <row r="29" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="D29" s="302" t="s">
+      <c r="I34" s="255" t="s">
+        <v>235</v>
+      </c>
+      <c r="J34" s="248"/>
+      <c r="K34" s="248"/>
+      <c r="L34" s="248"/>
+      <c r="M34" s="248"/>
+      <c r="N34" s="248"/>
+      <c r="O34" s="165" t="s">
         <v>218</v>
       </c>
-      <c r="E29" s="306"/>
-      <c r="F29" s="306"/>
-      <c r="G29" s="306"/>
-      <c r="H29" s="306"/>
-      <c r="I29" s="306"/>
-      <c r="J29" s="306"/>
-      <c r="K29" s="306"/>
-      <c r="L29" s="306"/>
-      <c r="P29" s="168"/>
-      <c r="Q29" s="168"/>
-      <c r="R29" s="168"/>
-      <c r="S29" s="168"/>
-      <c r="T29" s="168"/>
-      <c r="U29" s="168"/>
-      <c r="V29" s="168"/>
-      <c r="W29" s="168"/>
-      <c r="X29" s="168"/>
-      <c r="Y29" s="168"/>
-      <c r="Z29" s="168"/>
-      <c r="AA29" s="168"/>
-    </row>
-    <row r="30" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="C30" s="162"/>
-      <c r="D30" s="162" t="s">
+      <c r="P34" s="242" t="s">
+        <v>236</v>
+      </c>
+      <c r="Q34" s="242"/>
+      <c r="R34" s="242"/>
+      <c r="S34" s="242"/>
+      <c r="T34" s="242"/>
+      <c r="U34" s="183"/>
+      <c r="V34" s="194"/>
+      <c r="W34" s="194"/>
+      <c r="X34" s="194"/>
+      <c r="Y34" s="194"/>
+      <c r="Z34" s="194"/>
+      <c r="AA34" s="194"/>
+    </row>
+    <row r="36" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="V36" s="197"/>
+      <c r="W36" s="197"/>
+      <c r="X36" s="197"/>
+      <c r="Y36" s="197"/>
+      <c r="Z36" s="197"/>
+      <c r="AA36" s="197"/>
+    </row>
+    <row r="37" spans="1:27" ht="29.1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="J37" s="258"/>
+      <c r="K37" s="248"/>
+      <c r="L37" s="248"/>
+      <c r="M37" s="248"/>
+      <c r="N37" s="248"/>
+      <c r="O37" s="248"/>
+      <c r="P37" s="248"/>
+      <c r="Q37" s="248"/>
+      <c r="R37" s="248"/>
+      <c r="S37" s="248"/>
+      <c r="T37" s="148"/>
+      <c r="U37" s="148"/>
+      <c r="V37" s="148"/>
+      <c r="W37" s="148"/>
+      <c r="X37" s="148"/>
+      <c r="Y37" s="148"/>
+      <c r="Z37" s="148"/>
+      <c r="AA37" s="148"/>
+    </row>
+    <row r="38" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="J38" s="245" t="s">
         <v>219</v>
       </c>
-      <c r="E30" s="162"/>
-      <c r="F30" s="162"/>
-      <c r="G30" s="162"/>
-      <c r="H30" s="162"/>
-      <c r="I30" s="162"/>
-      <c r="J30" s="162"/>
-      <c r="K30" s="162"/>
-      <c r="L30" s="162"/>
-      <c r="M30" s="162"/>
-      <c r="P30" s="168"/>
-      <c r="Q30" s="168"/>
-      <c r="R30" s="168"/>
-      <c r="S30" s="168"/>
-      <c r="T30" s="168"/>
-      <c r="U30" s="168"/>
-      <c r="V30" s="168"/>
-      <c r="W30" s="168"/>
-      <c r="X30" s="168"/>
-      <c r="Y30" s="168"/>
-      <c r="Z30" s="168"/>
-      <c r="AA30" s="168"/>
-    </row>
-    <row r="31" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C31" s="168"/>
-      <c r="D31" s="197"/>
-      <c r="E31" s="198" t="s">
+      <c r="K38" s="246"/>
+      <c r="L38" s="246"/>
+      <c r="M38" s="246"/>
+      <c r="N38" s="246"/>
+      <c r="O38" s="246"/>
+      <c r="P38" s="246"/>
+      <c r="Q38" s="246"/>
+      <c r="R38" s="246"/>
+      <c r="S38" s="246"/>
+      <c r="T38" s="148"/>
+      <c r="U38" s="148"/>
+      <c r="V38" s="148"/>
+      <c r="W38" s="148"/>
+      <c r="X38" s="148"/>
+      <c r="Y38" s="148"/>
+      <c r="Z38" s="148"/>
+      <c r="AA38" s="148"/>
+    </row>
+    <row r="40" spans="1:27" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="253" t="s">
         <v>220</v>
       </c>
-      <c r="F31" s="197"/>
-      <c r="G31" s="197"/>
-      <c r="H31" s="197"/>
-      <c r="I31" s="197"/>
-      <c r="J31" s="197"/>
-      <c r="K31" s="197"/>
-      <c r="L31" s="197"/>
-      <c r="P31" s="168"/>
-      <c r="Q31" s="168"/>
-      <c r="R31" s="168"/>
-      <c r="S31" s="168"/>
-      <c r="T31" s="168"/>
-      <c r="U31" s="168"/>
-      <c r="V31" s="168"/>
-      <c r="W31" s="168"/>
-      <c r="X31" s="168"/>
-      <c r="Y31" s="168"/>
-      <c r="Z31" s="168"/>
-      <c r="AA31" s="168"/>
-    </row>
-    <row r="32" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="B32" s="168"/>
-      <c r="C32" s="168"/>
-      <c r="D32" s="168"/>
-      <c r="E32" s="148" t="s">
+      <c r="B40" s="244"/>
+      <c r="C40" s="244"/>
+      <c r="D40" s="252" t="s">
         <v>221</v>
       </c>
-      <c r="F32" s="168"/>
-      <c r="H32" s="148"/>
-      <c r="P32" s="168"/>
-      <c r="Q32" s="168"/>
-      <c r="R32" s="168"/>
-      <c r="S32" s="168"/>
-      <c r="T32" s="168"/>
-      <c r="U32" s="168"/>
-      <c r="V32" s="168"/>
-      <c r="W32" s="168"/>
-      <c r="X32" s="168"/>
-      <c r="Y32" s="168"/>
-      <c r="Z32" s="168"/>
-      <c r="AA32" s="168"/>
-    </row>
-    <row r="33" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="B33" s="168"/>
-      <c r="C33" s="168"/>
-      <c r="D33" s="168"/>
-      <c r="E33" s="148"/>
-      <c r="F33" s="168"/>
-      <c r="H33" s="148"/>
-      <c r="P33" s="168"/>
-      <c r="Q33" s="168"/>
-      <c r="R33" s="168"/>
-      <c r="S33" s="168"/>
-      <c r="T33" s="168"/>
-      <c r="U33" s="168"/>
-      <c r="V33" s="168"/>
-      <c r="W33" s="168"/>
-      <c r="X33" s="168"/>
-      <c r="Y33" s="168"/>
-      <c r="Z33" s="168"/>
-      <c r="AA33" s="168"/>
-    </row>
-    <row r="34" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="302" t="s">
-        <v>222</v>
-      </c>
-      <c r="B34" s="306"/>
-      <c r="C34" s="306"/>
-      <c r="D34" s="306"/>
-      <c r="E34" s="306"/>
-      <c r="F34" s="306"/>
-      <c r="G34" s="199"/>
-      <c r="H34" s="168" t="s">
-        <v>223</v>
-      </c>
-      <c r="I34" s="320" t="s">
-        <v>224</v>
-      </c>
-      <c r="J34" s="312"/>
-      <c r="K34" s="312"/>
-      <c r="L34" s="312"/>
-      <c r="M34" s="312"/>
-      <c r="N34" s="312"/>
-      <c r="O34" s="168" t="s">
-        <v>225</v>
-      </c>
-      <c r="P34" s="319" t="s">
-        <v>226</v>
-      </c>
-      <c r="Q34" s="312"/>
-      <c r="R34" s="312"/>
-      <c r="S34" s="312"/>
-      <c r="T34" s="186" t="s">
-        <v>227</v>
-      </c>
-      <c r="U34" s="186"/>
-      <c r="V34" s="197"/>
-      <c r="W34" s="197"/>
-      <c r="X34" s="197"/>
-      <c r="Y34" s="197"/>
-      <c r="Z34" s="197"/>
-      <c r="AA34" s="197"/>
-    </row>
-    <row r="36" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="V36" s="200"/>
-      <c r="W36" s="200"/>
-      <c r="X36" s="200"/>
-      <c r="Y36" s="200"/>
-      <c r="Z36" s="200"/>
-      <c r="AA36" s="200"/>
-    </row>
-    <row r="37" spans="1:27" ht="29.1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="J37" s="316" t="s">
-        <v>228</v>
-      </c>
-      <c r="K37" s="312"/>
-      <c r="L37" s="312"/>
-      <c r="M37" s="312"/>
-      <c r="N37" s="312"/>
-      <c r="O37" s="312"/>
-      <c r="P37" s="312"/>
-      <c r="Q37" s="312"/>
-      <c r="R37" s="312"/>
-      <c r="S37" s="312"/>
-      <c r="T37" s="151"/>
-      <c r="U37" s="151"/>
-      <c r="V37" s="151"/>
-      <c r="W37" s="151"/>
-      <c r="X37" s="151"/>
-      <c r="Y37" s="151"/>
-      <c r="Z37" s="151"/>
-      <c r="AA37" s="151"/>
-    </row>
-    <row r="38" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="J38" s="308" t="s">
-        <v>229</v>
-      </c>
-      <c r="K38" s="309"/>
-      <c r="L38" s="309"/>
-      <c r="M38" s="309"/>
-      <c r="N38" s="309"/>
-      <c r="O38" s="309"/>
-      <c r="P38" s="309"/>
-      <c r="Q38" s="309"/>
-      <c r="R38" s="309"/>
-      <c r="S38" s="309"/>
-      <c r="T38" s="151"/>
-      <c r="U38" s="151"/>
-      <c r="V38" s="151"/>
-      <c r="W38" s="151"/>
-      <c r="X38" s="151"/>
-      <c r="Y38" s="151"/>
-      <c r="Z38" s="151"/>
-      <c r="AA38" s="151"/>
-    </row>
-    <row r="40" spans="1:27" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="318" t="s">
-        <v>230</v>
-      </c>
-      <c r="B40" s="306"/>
-      <c r="C40" s="306"/>
-      <c r="D40" s="322" t="s">
-        <v>231</v>
-      </c>
-      <c r="E40" s="306"/>
-      <c r="F40" s="306"/>
-      <c r="G40" s="306"/>
-      <c r="H40" s="306"/>
-      <c r="I40" s="306"/>
-      <c r="J40" s="306"/>
-      <c r="K40" s="306"/>
-      <c r="L40" s="306"/>
-      <c r="M40" s="306"/>
-      <c r="N40" s="306"/>
-      <c r="O40" s="306"/>
-      <c r="P40" s="306"/>
-      <c r="Q40" s="306"/>
-      <c r="R40" s="306"/>
-      <c r="S40" s="306"/>
-      <c r="T40" s="306"/>
-      <c r="U40" s="306"/>
-      <c r="V40" s="306"/>
-      <c r="W40" s="306"/>
-      <c r="X40" s="306"/>
-      <c r="Y40" s="306"/>
-      <c r="Z40" s="306"/>
-      <c r="AA40" s="306"/>
+      <c r="E40" s="244"/>
+      <c r="F40" s="244"/>
+      <c r="G40" s="244"/>
+      <c r="H40" s="244"/>
+      <c r="I40" s="244"/>
+      <c r="J40" s="244"/>
+      <c r="K40" s="244"/>
+      <c r="L40" s="244"/>
+      <c r="M40" s="244"/>
+      <c r="N40" s="244"/>
+      <c r="O40" s="244"/>
+      <c r="P40" s="244"/>
+      <c r="Q40" s="244"/>
+      <c r="R40" s="244"/>
+      <c r="S40" s="244"/>
+      <c r="T40" s="244"/>
+      <c r="U40" s="244"/>
+      <c r="V40" s="244"/>
+      <c r="W40" s="244"/>
+      <c r="X40" s="244"/>
+      <c r="Y40" s="244"/>
+      <c r="Z40" s="244"/>
+      <c r="AA40" s="244"/>
     </row>
     <row r="41" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="C41" s="148"/>
-      <c r="D41" s="148"/>
-      <c r="E41" s="148"/>
-      <c r="F41" s="148"/>
-      <c r="G41" s="148"/>
-      <c r="H41" s="148"/>
-      <c r="J41" s="148"/>
-      <c r="K41" s="148"/>
-      <c r="L41" s="148"/>
+      <c r="C41" s="145"/>
+      <c r="D41" s="145"/>
+      <c r="E41" s="145"/>
+      <c r="F41" s="145"/>
+      <c r="G41" s="145"/>
+      <c r="H41" s="145"/>
+      <c r="J41" s="145"/>
+      <c r="K41" s="145"/>
+      <c r="L41" s="145"/>
     </row>
     <row r="42" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="C42" s="195"/>
-      <c r="D42" s="195"/>
-      <c r="E42" s="195"/>
-      <c r="F42" s="195"/>
-      <c r="G42" s="195"/>
-      <c r="H42" s="195"/>
-      <c r="J42" s="195"/>
-      <c r="K42" s="195"/>
-      <c r="L42" s="195"/>
-      <c r="M42" s="148"/>
-      <c r="N42" s="148"/>
-      <c r="O42" s="148"/>
-      <c r="AA42" s="148"/>
+      <c r="C42" s="192"/>
+      <c r="D42" s="192"/>
+      <c r="E42" s="192"/>
+      <c r="F42" s="192"/>
+      <c r="G42" s="192"/>
+      <c r="H42" s="192"/>
+      <c r="J42" s="192"/>
+      <c r="K42" s="192"/>
+      <c r="L42" s="192"/>
+      <c r="M42" s="145"/>
+      <c r="N42" s="145"/>
+      <c r="O42" s="145"/>
+      <c r="AA42" s="145"/>
     </row>
     <row r="43" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A43" s="148"/>
-      <c r="I43" s="148"/>
-      <c r="M43" s="195"/>
-      <c r="N43" s="195"/>
-      <c r="O43" s="195"/>
-      <c r="AA43" s="195"/>
+      <c r="A43" s="145"/>
+      <c r="I43" s="145"/>
+      <c r="M43" s="192"/>
+      <c r="N43" s="192"/>
+      <c r="O43" s="192"/>
+      <c r="AA43" s="192"/>
     </row>
   </sheetData>
   <mergeCells count="22">
     <mergeCell ref="A1:AA1"/>
     <mergeCell ref="D40:AA40"/>
     <mergeCell ref="A40:C40"/>
-    <mergeCell ref="P34:S34"/>
     <mergeCell ref="D26:L26"/>
     <mergeCell ref="A34:F34"/>
     <mergeCell ref="I34:N34"/>
@@ -7942,6 +7934,7 @@
     <mergeCell ref="D27:L27"/>
     <mergeCell ref="C6:G6"/>
     <mergeCell ref="C15:G15"/>
+    <mergeCell ref="P34:T34"/>
     <mergeCell ref="C5:G5"/>
     <mergeCell ref="R27:Z27"/>
     <mergeCell ref="R26:Z26"/>
@@ -7950,8 +7943,8 @@
     <mergeCell ref="C7:G7"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
-  <pageMargins left="0" right="0" top="0" bottom="0" header="0.51180555555555551" footer="0.51180555555555551"/>
-  <pageSetup paperSize="14" scale="88" firstPageNumber="0" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <pageMargins left="0" right="0" top="0" bottom="0" header="0.51181102362204722" footer="0.51181102362204722"/>
+  <pageSetup paperSize="133" scale="90" firstPageNumber="0" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -7961,96 +7954,96 @@
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="29" spans="4:11" x14ac:dyDescent="0.2">
-      <c r="D29" s="201"/>
-      <c r="E29" s="202"/>
-      <c r="F29" s="202"/>
-      <c r="G29" s="202"/>
-      <c r="H29" s="202"/>
-      <c r="I29" s="202"/>
-      <c r="J29" s="202"/>
-      <c r="K29" s="203"/>
+      <c r="D29" s="198"/>
+      <c r="E29" s="199"/>
+      <c r="F29" s="199"/>
+      <c r="G29" s="199"/>
+      <c r="H29" s="199"/>
+      <c r="I29" s="199"/>
+      <c r="J29" s="199"/>
+      <c r="K29" s="200"/>
     </row>
     <row r="30" spans="4:11" x14ac:dyDescent="0.2">
-      <c r="D30" s="204"/>
-      <c r="E30" s="327" t="s">
-        <v>232</v>
-      </c>
-      <c r="F30" s="324"/>
-      <c r="G30" s="324"/>
-      <c r="H30" s="324"/>
-      <c r="I30" s="324"/>
-      <c r="J30" s="324"/>
-      <c r="K30" s="258"/>
+      <c r="D30" s="201"/>
+      <c r="E30" s="334" t="s">
+        <v>222</v>
+      </c>
+      <c r="F30" s="331"/>
+      <c r="G30" s="331"/>
+      <c r="H30" s="331"/>
+      <c r="I30" s="331"/>
+      <c r="J30" s="331"/>
+      <c r="K30" s="286"/>
     </row>
     <row r="31" spans="4:11" x14ac:dyDescent="0.2">
-      <c r="D31" s="204"/>
-      <c r="K31" s="205"/>
+      <c r="D31" s="201"/>
+      <c r="K31" s="202"/>
     </row>
     <row r="32" spans="4:11" x14ac:dyDescent="0.2">
-      <c r="D32" s="204"/>
-      <c r="E32" s="206"/>
-      <c r="F32" s="326" t="s">
-        <v>233</v>
-      </c>
-      <c r="G32" s="324"/>
-      <c r="H32" s="324"/>
-      <c r="I32" s="324"/>
-      <c r="J32" s="324"/>
-      <c r="K32" s="258"/>
+      <c r="D32" s="201"/>
+      <c r="E32" s="203"/>
+      <c r="F32" s="333" t="s">
+        <v>223</v>
+      </c>
+      <c r="G32" s="331"/>
+      <c r="H32" s="331"/>
+      <c r="I32" s="331"/>
+      <c r="J32" s="331"/>
+      <c r="K32" s="286"/>
     </row>
     <row r="33" spans="4:11" x14ac:dyDescent="0.2">
-      <c r="D33" s="204"/>
-      <c r="K33" s="205"/>
+      <c r="D33" s="201"/>
+      <c r="K33" s="202"/>
     </row>
     <row r="34" spans="4:11" x14ac:dyDescent="0.2">
-      <c r="D34" s="204"/>
-      <c r="E34" s="207"/>
-      <c r="F34" s="323" t="s">
-        <v>234</v>
-      </c>
-      <c r="G34" s="324"/>
-      <c r="H34" s="324"/>
-      <c r="I34" s="324"/>
-      <c r="J34" s="324"/>
-      <c r="K34" s="258"/>
+      <c r="D34" s="201"/>
+      <c r="E34" s="204"/>
+      <c r="F34" s="330" t="s">
+        <v>224</v>
+      </c>
+      <c r="G34" s="331"/>
+      <c r="H34" s="331"/>
+      <c r="I34" s="331"/>
+      <c r="J34" s="331"/>
+      <c r="K34" s="286"/>
     </row>
     <row r="35" spans="4:11" x14ac:dyDescent="0.2">
-      <c r="D35" s="204"/>
-      <c r="K35" s="205"/>
+      <c r="D35" s="201"/>
+      <c r="K35" s="202"/>
     </row>
     <row r="36" spans="4:11" x14ac:dyDescent="0.2">
-      <c r="D36" s="204"/>
-      <c r="E36" s="208"/>
-      <c r="F36" s="328" t="s">
-        <v>235</v>
-      </c>
-      <c r="G36" s="324"/>
-      <c r="H36" s="324"/>
-      <c r="I36" s="324"/>
-      <c r="J36" s="324"/>
-      <c r="K36" s="205"/>
+      <c r="D36" s="201"/>
+      <c r="E36" s="205"/>
+      <c r="F36" s="335" t="s">
+        <v>225</v>
+      </c>
+      <c r="G36" s="331"/>
+      <c r="H36" s="331"/>
+      <c r="I36" s="331"/>
+      <c r="J36" s="331"/>
+      <c r="K36" s="202"/>
     </row>
     <row r="37" spans="4:11" x14ac:dyDescent="0.2">
-      <c r="D37" s="209"/>
-      <c r="E37" s="210"/>
-      <c r="F37" s="210"/>
-      <c r="G37" s="210"/>
-      <c r="H37" s="210"/>
-      <c r="I37" s="210"/>
-      <c r="J37" s="210"/>
-      <c r="K37" s="211"/>
+      <c r="D37" s="206"/>
+      <c r="E37" s="207"/>
+      <c r="F37" s="207"/>
+      <c r="G37" s="207"/>
+      <c r="H37" s="207"/>
+      <c r="I37" s="207"/>
+      <c r="J37" s="207"/>
+      <c r="K37" s="208"/>
     </row>
     <row r="39" spans="4:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D39" s="325" t="s">
-        <v>236</v>
-      </c>
-      <c r="E39" s="324"/>
-      <c r="F39" s="324"/>
-      <c r="G39" s="324"/>
-      <c r="H39" s="324"/>
-      <c r="I39" s="324"/>
-      <c r="J39" s="324"/>
-      <c r="K39" s="324"/>
+      <c r="D39" s="332" t="s">
+        <v>226</v>
+      </c>
+      <c r="E39" s="331"/>
+      <c r="F39" s="331"/>
+      <c r="G39" s="331"/>
+      <c r="H39" s="331"/>
+      <c r="I39" s="331"/>
+      <c r="J39" s="331"/>
+      <c r="K39" s="331"/>
     </row>
   </sheetData>
   <mergeCells count="5">

--- a/app/static/storage/June 2026 MTC BUENAVISTA, AGUSAN DEL NORTE.xlsx
+++ b/app/static/storage/June 2026 MTC BUENAVISTA, AGUSAN DEL NORTE.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C354453-22FF-4932-9B30-A01E2D053F3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="363" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="363" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Page 1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Page 2'!$A$1:$L$31</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Page 3'!$A$1:$G$30</definedName>
   </definedNames>
-  <calcPr calcId="191029" refMode="R1C1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -3273,95 +3273,60 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="130" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="63" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="63" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
+    <xf numFmtId="3" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="110" xfId="0" applyBorder="1"/>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="74" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="113" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="74" xfId="0" applyBorder="1"/>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="75" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="82" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="121" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="116" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="117" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="82" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="118" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="119" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="83" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="122" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="74" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="73" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="113" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="74" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="81" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="120" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="83" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="122" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="111" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="73" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="76" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="114" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="115" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="116" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="117" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3391,26 +3356,22 @@
     <xf numFmtId="3" fontId="3" fillId="0" borderId="77" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="75" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="81" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="120" xfId="0" applyBorder="1"/>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="87" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="82" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="121" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="82" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="118" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="119" xfId="0" applyBorder="1"/>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="73" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="78" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="88" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="111" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="73" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="112" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="88" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="84" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3430,23 +3391,17 @@
     <xf numFmtId="3" fontId="3" fillId="0" borderId="78" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="78" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="87" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="88" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="112" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="88" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="89" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -3464,10 +3419,58 @@
     <xf numFmtId="164" fontId="20" fillId="0" borderId="89" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="63" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="63" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="3" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="130" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -3483,9 +3486,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3973,23 +3973,23 @@
       <c r="O2" s="4"/>
     </row>
     <row r="3" spans="1:20" s="8" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="282" t="s">
+      <c r="A3" s="276" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="283"/>
-      <c r="C3" s="283"/>
-      <c r="D3" s="283"/>
-      <c r="E3" s="283"/>
-      <c r="F3" s="283"/>
-      <c r="G3" s="283"/>
-      <c r="H3" s="283"/>
-      <c r="I3" s="283"/>
-      <c r="J3" s="283"/>
-      <c r="K3" s="283"/>
-      <c r="L3" s="283"/>
-      <c r="M3" s="283"/>
-      <c r="N3" s="283"/>
-      <c r="O3" s="283"/>
+      <c r="B3" s="277"/>
+      <c r="C3" s="277"/>
+      <c r="D3" s="277"/>
+      <c r="E3" s="277"/>
+      <c r="F3" s="277"/>
+      <c r="G3" s="277"/>
+      <c r="H3" s="277"/>
+      <c r="I3" s="277"/>
+      <c r="J3" s="277"/>
+      <c r="K3" s="277"/>
+      <c r="L3" s="277"/>
+      <c r="M3" s="277"/>
+      <c r="N3" s="277"/>
+      <c r="O3" s="277"/>
       <c r="P3" s="6"/>
       <c r="Q3" s="6"/>
       <c r="R3" s="6"/>
@@ -3997,23 +3997,23 @@
       <c r="T3" s="7"/>
     </row>
     <row r="4" spans="1:20" s="11" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="287" t="s">
+      <c r="A4" s="281" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="283"/>
-      <c r="C4" s="283"/>
-      <c r="D4" s="283"/>
-      <c r="E4" s="283"/>
-      <c r="F4" s="283"/>
-      <c r="G4" s="283"/>
-      <c r="H4" s="283"/>
-      <c r="I4" s="283"/>
-      <c r="J4" s="283"/>
-      <c r="K4" s="283"/>
-      <c r="L4" s="283"/>
-      <c r="M4" s="283"/>
-      <c r="N4" s="283"/>
-      <c r="O4" s="283"/>
+      <c r="B4" s="277"/>
+      <c r="C4" s="277"/>
+      <c r="D4" s="277"/>
+      <c r="E4" s="277"/>
+      <c r="F4" s="277"/>
+      <c r="G4" s="277"/>
+      <c r="H4" s="277"/>
+      <c r="I4" s="277"/>
+      <c r="J4" s="277"/>
+      <c r="K4" s="277"/>
+      <c r="L4" s="277"/>
+      <c r="M4" s="277"/>
+      <c r="N4" s="277"/>
+      <c r="O4" s="277"/>
       <c r="P4" s="9"/>
       <c r="Q4" s="9"/>
       <c r="R4" s="9"/>
@@ -4038,62 +4038,62 @@
       <c r="O5" s="12"/>
     </row>
     <row r="6" spans="1:20" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="276" t="s">
+      <c r="A6" s="270" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="277"/>
-      <c r="C6" s="277"/>
-      <c r="D6" s="278"/>
-      <c r="E6" s="288" t="s">
+      <c r="B6" s="271"/>
+      <c r="C6" s="271"/>
+      <c r="D6" s="272"/>
+      <c r="E6" s="282" t="s">
         <v>5</v>
       </c>
-      <c r="F6" s="289"/>
-      <c r="G6" s="289"/>
-      <c r="H6" s="289"/>
-      <c r="I6" s="289"/>
-      <c r="J6" s="289"/>
-      <c r="K6" s="289"/>
-      <c r="L6" s="289"/>
-      <c r="M6" s="289"/>
-      <c r="N6" s="289"/>
-      <c r="O6" s="260"/>
+      <c r="F6" s="283"/>
+      <c r="G6" s="283"/>
+      <c r="H6" s="283"/>
+      <c r="I6" s="283"/>
+      <c r="J6" s="283"/>
+      <c r="K6" s="283"/>
+      <c r="L6" s="283"/>
+      <c r="M6" s="283"/>
+      <c r="N6" s="283"/>
+      <c r="O6" s="247"/>
     </row>
     <row r="7" spans="1:20" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="279"/>
-      <c r="B7" s="280"/>
-      <c r="C7" s="280"/>
-      <c r="D7" s="281"/>
-      <c r="E7" s="298" t="s">
+      <c r="A7" s="273"/>
+      <c r="B7" s="274"/>
+      <c r="C7" s="274"/>
+      <c r="D7" s="275"/>
+      <c r="E7" s="264" t="s">
         <v>6</v>
       </c>
-      <c r="F7" s="262" t="s">
+      <c r="F7" s="248" t="s">
         <v>7</v>
       </c>
-      <c r="G7" s="262" t="s">
+      <c r="G7" s="248" t="s">
         <v>8</v>
       </c>
-      <c r="H7" s="291" t="s">
+      <c r="H7" s="251" t="s">
         <v>9</v>
       </c>
-      <c r="I7" s="291" t="s">
+      <c r="I7" s="251" t="s">
         <v>10</v>
       </c>
-      <c r="J7" s="291" t="s">
+      <c r="J7" s="251" t="s">
         <v>11</v>
       </c>
-      <c r="K7" s="262" t="s">
+      <c r="K7" s="248" t="s">
         <v>12</v>
       </c>
-      <c r="L7" s="262" t="s">
+      <c r="L7" s="248" t="s">
         <v>13</v>
       </c>
-      <c r="M7" s="291" t="s">
+      <c r="M7" s="251" t="s">
         <v>14</v>
       </c>
-      <c r="N7" s="270" t="s">
+      <c r="N7" s="267" t="s">
         <v>15</v>
       </c>
-      <c r="O7" s="290" t="s">
+      <c r="O7" s="284" t="s">
         <v>16</v>
       </c>
     </row>
@@ -4104,17 +4104,17 @@
       <c r="B8" s="14"/>
       <c r="C8" s="14"/>
       <c r="D8" s="15"/>
-      <c r="E8" s="299"/>
-      <c r="F8" s="263"/>
-      <c r="G8" s="263"/>
-      <c r="H8" s="263"/>
-      <c r="I8" s="263"/>
-      <c r="J8" s="263"/>
-      <c r="K8" s="263"/>
-      <c r="L8" s="263"/>
-      <c r="M8" s="263"/>
-      <c r="N8" s="271"/>
-      <c r="O8" s="286"/>
+      <c r="E8" s="265"/>
+      <c r="F8" s="249"/>
+      <c r="G8" s="249"/>
+      <c r="H8" s="249"/>
+      <c r="I8" s="249"/>
+      <c r="J8" s="249"/>
+      <c r="K8" s="249"/>
+      <c r="L8" s="249"/>
+      <c r="M8" s="249"/>
+      <c r="N8" s="268"/>
+      <c r="O8" s="280"/>
     </row>
     <row r="9" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="16" t="s">
@@ -4125,86 +4125,86 @@
       <c r="D9" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="E9" s="299"/>
-      <c r="F9" s="263"/>
-      <c r="G9" s="263"/>
-      <c r="H9" s="263"/>
-      <c r="I9" s="263"/>
-      <c r="J9" s="263"/>
-      <c r="K9" s="263"/>
-      <c r="L9" s="263"/>
-      <c r="M9" s="263"/>
-      <c r="N9" s="271"/>
-      <c r="O9" s="286"/>
+      <c r="E9" s="265"/>
+      <c r="F9" s="249"/>
+      <c r="G9" s="249"/>
+      <c r="H9" s="249"/>
+      <c r="I9" s="249"/>
+      <c r="J9" s="249"/>
+      <c r="K9" s="249"/>
+      <c r="L9" s="249"/>
+      <c r="M9" s="249"/>
+      <c r="N9" s="268"/>
+      <c r="O9" s="280"/>
     </row>
     <row r="10" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="273" t="s">
+      <c r="A10" s="254" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="274"/>
-      <c r="C10" s="275"/>
+      <c r="B10" s="255"/>
+      <c r="C10" s="256"/>
       <c r="D10" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="E10" s="299"/>
-      <c r="F10" s="263"/>
-      <c r="G10" s="263"/>
-      <c r="H10" s="263"/>
-      <c r="I10" s="263"/>
-      <c r="J10" s="263"/>
-      <c r="K10" s="263"/>
-      <c r="L10" s="263"/>
-      <c r="M10" s="263"/>
-      <c r="N10" s="271"/>
-      <c r="O10" s="286"/>
+      <c r="E10" s="265"/>
+      <c r="F10" s="249"/>
+      <c r="G10" s="249"/>
+      <c r="H10" s="249"/>
+      <c r="I10" s="249"/>
+      <c r="J10" s="249"/>
+      <c r="K10" s="249"/>
+      <c r="L10" s="249"/>
+      <c r="M10" s="249"/>
+      <c r="N10" s="268"/>
+      <c r="O10" s="280"/>
     </row>
     <row r="11" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="273" t="s">
+      <c r="A11" s="254" t="s">
         <v>22</v>
       </c>
-      <c r="B11" s="274"/>
-      <c r="C11" s="275"/>
+      <c r="B11" s="255"/>
+      <c r="C11" s="256"/>
       <c r="D11" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="E11" s="299"/>
-      <c r="F11" s="263"/>
-      <c r="G11" s="263"/>
-      <c r="H11" s="263"/>
-      <c r="I11" s="263"/>
-      <c r="J11" s="263"/>
-      <c r="K11" s="263"/>
-      <c r="L11" s="263"/>
-      <c r="M11" s="263"/>
-      <c r="N11" s="271"/>
-      <c r="O11" s="286"/>
+      <c r="E11" s="265"/>
+      <c r="F11" s="249"/>
+      <c r="G11" s="249"/>
+      <c r="H11" s="249"/>
+      <c r="I11" s="249"/>
+      <c r="J11" s="249"/>
+      <c r="K11" s="249"/>
+      <c r="L11" s="249"/>
+      <c r="M11" s="249"/>
+      <c r="N11" s="268"/>
+      <c r="O11" s="280"/>
     </row>
     <row r="12" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="273" t="s">
+      <c r="A12" s="254" t="s">
         <v>24</v>
       </c>
-      <c r="B12" s="274"/>
-      <c r="C12" s="275"/>
+      <c r="B12" s="255"/>
+      <c r="C12" s="256"/>
       <c r="D12" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="E12" s="300"/>
-      <c r="F12" s="264"/>
-      <c r="G12" s="264"/>
-      <c r="H12" s="264"/>
-      <c r="I12" s="264"/>
-      <c r="J12" s="264"/>
-      <c r="K12" s="264"/>
-      <c r="L12" s="264"/>
-      <c r="M12" s="264"/>
-      <c r="N12" s="272"/>
-      <c r="O12" s="281"/>
+      <c r="E12" s="266"/>
+      <c r="F12" s="250"/>
+      <c r="G12" s="250"/>
+      <c r="H12" s="250"/>
+      <c r="I12" s="250"/>
+      <c r="J12" s="250"/>
+      <c r="K12" s="250"/>
+      <c r="L12" s="250"/>
+      <c r="M12" s="250"/>
+      <c r="N12" s="269"/>
+      <c r="O12" s="275"/>
     </row>
     <row r="13" spans="1:20" s="25" customFormat="1" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="284"/>
-      <c r="B13" s="285"/>
-      <c r="C13" s="285"/>
-      <c r="D13" s="286"/>
+      <c r="A13" s="278"/>
+      <c r="B13" s="279"/>
+      <c r="C13" s="279"/>
+      <c r="D13" s="280"/>
       <c r="E13" s="20" t="s">
         <v>26</v>
       </c>
@@ -4246,10 +4246,10 @@
       <c r="B14" s="27" t="s">
         <v>38</v>
       </c>
-      <c r="C14" s="265" t="s">
+      <c r="C14" s="285" t="s">
         <v>39</v>
       </c>
-      <c r="D14" s="260"/>
+      <c r="D14" s="247"/>
       <c r="E14" s="209">
         <v>0</v>
       </c>
@@ -4292,10 +4292,10 @@
       <c r="B15" s="30" t="s">
         <v>40</v>
       </c>
-      <c r="C15" s="261" t="s">
+      <c r="C15" s="263" t="s">
         <v>41</v>
       </c>
-      <c r="D15" s="260"/>
+      <c r="D15" s="247"/>
       <c r="E15" s="209">
         <f t="shared" ref="E15:N15" si="1">SUM(E16:E18)</f>
         <v>0</v>
@@ -4342,16 +4342,16 @@
       </c>
     </row>
     <row r="16" spans="1:20" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="295" t="s">
+      <c r="A16" s="258" t="s">
         <v>42</v>
       </c>
       <c r="B16" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="C16" s="266" t="s">
+      <c r="C16" s="286" t="s">
         <v>44</v>
       </c>
-      <c r="D16" s="267"/>
+      <c r="D16" s="287"/>
       <c r="E16" s="210">
         <v>0</v>
       </c>
@@ -4388,14 +4388,14 @@
       </c>
     </row>
     <row r="17" spans="1:15" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="296"/>
+      <c r="A17" s="259"/>
       <c r="B17" s="32" t="s">
         <v>45</v>
       </c>
-      <c r="C17" s="292" t="s">
+      <c r="C17" s="252" t="s">
         <v>46</v>
       </c>
-      <c r="D17" s="293"/>
+      <c r="D17" s="253"/>
       <c r="E17" s="210">
         <v>0</v>
       </c>
@@ -4432,14 +4432,14 @@
       </c>
     </row>
     <row r="18" spans="1:15" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="297"/>
+      <c r="A18" s="260"/>
       <c r="B18" s="36" t="s">
         <v>47</v>
       </c>
-      <c r="C18" s="268" t="s">
+      <c r="C18" s="261" t="s">
         <v>48</v>
       </c>
-      <c r="D18" s="269"/>
+      <c r="D18" s="262"/>
       <c r="E18" s="210">
         <v>0</v>
       </c>
@@ -4482,10 +4482,10 @@
       <c r="B19" s="30" t="s">
         <v>49</v>
       </c>
-      <c r="C19" s="261" t="s">
+      <c r="C19" s="263" t="s">
         <v>50</v>
       </c>
-      <c r="D19" s="260"/>
+      <c r="D19" s="247"/>
       <c r="E19" s="209">
         <f t="shared" ref="E19:N19" si="2">SUM(E20:E23)</f>
         <v>0</v>
@@ -4532,16 +4532,16 @@
       </c>
     </row>
     <row r="20" spans="1:15" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="295" t="s">
+      <c r="A20" s="258" t="s">
         <v>51</v>
       </c>
       <c r="B20" s="37" t="s">
         <v>52</v>
       </c>
-      <c r="C20" s="266" t="s">
+      <c r="C20" s="286" t="s">
         <v>53</v>
       </c>
-      <c r="D20" s="267"/>
+      <c r="D20" s="287"/>
       <c r="E20" s="211">
         <v>0</v>
       </c>
@@ -4578,14 +4578,14 @@
       </c>
     </row>
     <row r="21" spans="1:15" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="296"/>
+      <c r="A21" s="259"/>
       <c r="B21" s="32" t="s">
         <v>54</v>
       </c>
-      <c r="C21" s="294" t="s">
+      <c r="C21" s="257" t="s">
         <v>55</v>
       </c>
-      <c r="D21" s="293"/>
+      <c r="D21" s="253"/>
       <c r="E21" s="210">
         <v>0</v>
       </c>
@@ -4622,14 +4622,14 @@
       </c>
     </row>
     <row r="22" spans="1:15" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="296"/>
+      <c r="A22" s="259"/>
       <c r="B22" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="C22" s="292" t="s">
+      <c r="C22" s="252" t="s">
         <v>57</v>
       </c>
-      <c r="D22" s="293"/>
+      <c r="D22" s="253"/>
       <c r="E22" s="210">
         <v>0</v>
       </c>
@@ -4666,14 +4666,14 @@
       </c>
     </row>
     <row r="23" spans="1:15" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="297"/>
+      <c r="A23" s="260"/>
       <c r="B23" s="38" t="s">
         <v>58</v>
       </c>
-      <c r="C23" s="268" t="s">
+      <c r="C23" s="261" t="s">
         <v>59</v>
       </c>
-      <c r="D23" s="269"/>
+      <c r="D23" s="262"/>
       <c r="E23" s="212">
         <v>0</v>
       </c>
@@ -4716,10 +4716,10 @@
       <c r="B24" s="30" t="s">
         <v>60</v>
       </c>
-      <c r="C24" s="259" t="s">
+      <c r="C24" s="246" t="s">
         <v>61</v>
       </c>
-      <c r="D24" s="260"/>
+      <c r="D24" s="247"/>
       <c r="E24" s="29">
         <f t="shared" ref="E24:M24" si="3">(E14+E15)-E19</f>
         <v>0</v>
@@ -4772,10 +4772,10 @@
       <c r="B25" s="30" t="s">
         <v>62</v>
       </c>
-      <c r="C25" s="259" t="s">
+      <c r="C25" s="246" t="s">
         <v>63</v>
       </c>
-      <c r="D25" s="260"/>
+      <c r="D25" s="247"/>
       <c r="E25" s="41"/>
       <c r="F25" s="213"/>
       <c r="G25" s="41"/>
@@ -4937,6 +4937,23 @@
     </row>
   </sheetData>
   <mergeCells count="33">
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F7:F12"/>
+    <mergeCell ref="L7:L12"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="N7:N12"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="A6:D7"/>
+    <mergeCell ref="A3:O3"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A4:O4"/>
+    <mergeCell ref="E6:O6"/>
+    <mergeCell ref="K7:K12"/>
+    <mergeCell ref="O7:O12"/>
     <mergeCell ref="C25:D25"/>
     <mergeCell ref="G7:G12"/>
     <mergeCell ref="I7:I12"/>
@@ -4953,23 +4970,6 @@
     <mergeCell ref="A16:A18"/>
     <mergeCell ref="C19:D19"/>
     <mergeCell ref="E7:E12"/>
-    <mergeCell ref="N7:N12"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="A6:D7"/>
-    <mergeCell ref="A3:O3"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="A4:O4"/>
-    <mergeCell ref="E6:O6"/>
-    <mergeCell ref="K7:K12"/>
-    <mergeCell ref="O7:O12"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F7:F12"/>
-    <mergeCell ref="L7:L12"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C18:D18"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.23622047244094491" bottom="0.23622047244094491" header="0.51181102362204722" footer="0.51181102362204722"/>
@@ -5025,98 +5025,98 @@
       <c r="L2" s="68"/>
     </row>
     <row r="3" spans="1:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="301" t="s">
+      <c r="A3" s="293" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="302"/>
-      <c r="C3" s="302"/>
-      <c r="D3" s="302"/>
-      <c r="E3" s="302"/>
-      <c r="F3" s="302"/>
-      <c r="G3" s="302"/>
-      <c r="H3" s="302"/>
-      <c r="I3" s="302"/>
-      <c r="J3" s="302"/>
-      <c r="K3" s="302"/>
-      <c r="L3" s="303"/>
+      <c r="B3" s="294"/>
+      <c r="C3" s="294"/>
+      <c r="D3" s="294"/>
+      <c r="E3" s="294"/>
+      <c r="F3" s="294"/>
+      <c r="G3" s="294"/>
+      <c r="H3" s="294"/>
+      <c r="I3" s="294"/>
+      <c r="J3" s="294"/>
+      <c r="K3" s="294"/>
+      <c r="L3" s="295"/>
     </row>
     <row r="4" spans="1:12" s="11" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="308" t="s">
+      <c r="A4" s="300" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="309"/>
-      <c r="C4" s="309"/>
-      <c r="D4" s="309"/>
-      <c r="E4" s="309"/>
-      <c r="F4" s="309"/>
-      <c r="G4" s="309"/>
-      <c r="H4" s="309"/>
-      <c r="I4" s="309"/>
-      <c r="J4" s="309"/>
-      <c r="K4" s="309"/>
-      <c r="L4" s="310"/>
+      <c r="B4" s="301"/>
+      <c r="C4" s="301"/>
+      <c r="D4" s="301"/>
+      <c r="E4" s="301"/>
+      <c r="F4" s="301"/>
+      <c r="G4" s="301"/>
+      <c r="H4" s="301"/>
+      <c r="I4" s="301"/>
+      <c r="J4" s="301"/>
+      <c r="K4" s="301"/>
+      <c r="L4" s="302"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="12"/>
       <c r="B5" s="12"/>
       <c r="C5" s="12"/>
       <c r="D5" s="12"/>
-      <c r="E5" s="304"/>
-      <c r="F5" s="305"/>
-      <c r="G5" s="305"/>
-      <c r="H5" s="305"/>
-      <c r="I5" s="305"/>
-      <c r="J5" s="305"/>
-      <c r="K5" s="305"/>
-      <c r="L5" s="306"/>
+      <c r="E5" s="296"/>
+      <c r="F5" s="297"/>
+      <c r="G5" s="297"/>
+      <c r="H5" s="297"/>
+      <c r="I5" s="297"/>
+      <c r="J5" s="297"/>
+      <c r="K5" s="297"/>
+      <c r="L5" s="298"/>
     </row>
     <row r="6" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="276" t="s">
+      <c r="A6" s="270" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="277"/>
-      <c r="C6" s="277"/>
-      <c r="D6" s="278"/>
-      <c r="E6" s="313" t="s">
+      <c r="B6" s="271"/>
+      <c r="C6" s="271"/>
+      <c r="D6" s="272"/>
+      <c r="E6" s="304" t="s">
         <v>72</v>
       </c>
-      <c r="F6" s="289"/>
-      <c r="G6" s="289"/>
-      <c r="H6" s="289"/>
-      <c r="I6" s="289"/>
-      <c r="J6" s="289"/>
-      <c r="K6" s="260"/>
-      <c r="L6" s="314" t="s">
+      <c r="F6" s="283"/>
+      <c r="G6" s="283"/>
+      <c r="H6" s="283"/>
+      <c r="I6" s="283"/>
+      <c r="J6" s="283"/>
+      <c r="K6" s="247"/>
+      <c r="L6" s="288" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="7" spans="1:12" s="69" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="279"/>
-      <c r="B7" s="280"/>
-      <c r="C7" s="280"/>
-      <c r="D7" s="281"/>
-      <c r="E7" s="298" t="s">
+      <c r="A7" s="273"/>
+      <c r="B7" s="274"/>
+      <c r="C7" s="274"/>
+      <c r="D7" s="275"/>
+      <c r="E7" s="264" t="s">
         <v>74</v>
       </c>
-      <c r="F7" s="291" t="s">
+      <c r="F7" s="251" t="s">
         <v>75</v>
       </c>
-      <c r="G7" s="262" t="s">
+      <c r="G7" s="248" t="s">
         <v>76</v>
       </c>
-      <c r="H7" s="262" t="s">
+      <c r="H7" s="248" t="s">
         <v>77</v>
       </c>
-      <c r="I7" s="262" t="s">
+      <c r="I7" s="248" t="s">
         <v>78</v>
       </c>
-      <c r="J7" s="315" t="s">
+      <c r="J7" s="290" t="s">
         <v>79</v>
       </c>
-      <c r="K7" s="311" t="s">
+      <c r="K7" s="303" t="s">
         <v>80</v>
       </c>
-      <c r="L7" s="312"/>
+      <c r="L7" s="289"/>
     </row>
     <row r="8" spans="1:12" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
@@ -5128,14 +5128,14 @@
         <f>'Page 1'!D8</f>
         <v>0</v>
       </c>
-      <c r="E8" s="299"/>
-      <c r="F8" s="263"/>
-      <c r="G8" s="263"/>
-      <c r="H8" s="263"/>
-      <c r="I8" s="263"/>
-      <c r="J8" s="316"/>
-      <c r="K8" s="312"/>
-      <c r="L8" s="312"/>
+      <c r="E8" s="265"/>
+      <c r="F8" s="249"/>
+      <c r="G8" s="249"/>
+      <c r="H8" s="249"/>
+      <c r="I8" s="249"/>
+      <c r="J8" s="291"/>
+      <c r="K8" s="289"/>
+      <c r="L8" s="289"/>
     </row>
     <row r="9" spans="1:12" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="16" t="s">
@@ -5147,77 +5147,77 @@
         <f>'Page 1'!D9</f>
         <v>BUENAVISTA</v>
       </c>
-      <c r="E9" s="299"/>
-      <c r="F9" s="263"/>
-      <c r="G9" s="263"/>
-      <c r="H9" s="263"/>
-      <c r="I9" s="263"/>
-      <c r="J9" s="316"/>
-      <c r="K9" s="312"/>
-      <c r="L9" s="312"/>
+      <c r="E9" s="265"/>
+      <c r="F9" s="249"/>
+      <c r="G9" s="249"/>
+      <c r="H9" s="249"/>
+      <c r="I9" s="249"/>
+      <c r="J9" s="291"/>
+      <c r="K9" s="289"/>
+      <c r="L9" s="289"/>
     </row>
     <row r="10" spans="1:12" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="273" t="s">
+      <c r="A10" s="254" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="274"/>
-      <c r="C10" s="275"/>
+      <c r="B10" s="255"/>
+      <c r="C10" s="256"/>
       <c r="D10" s="71" t="str">
         <f>'Page 1'!D10</f>
         <v>AGUSAN DEL NORTE</v>
       </c>
-      <c r="E10" s="299"/>
-      <c r="F10" s="263"/>
-      <c r="G10" s="263"/>
-      <c r="H10" s="263"/>
-      <c r="I10" s="263"/>
-      <c r="J10" s="316"/>
-      <c r="K10" s="312"/>
-      <c r="L10" s="312"/>
+      <c r="E10" s="265"/>
+      <c r="F10" s="249"/>
+      <c r="G10" s="249"/>
+      <c r="H10" s="249"/>
+      <c r="I10" s="249"/>
+      <c r="J10" s="291"/>
+      <c r="K10" s="289"/>
+      <c r="L10" s="289"/>
     </row>
     <row r="11" spans="1:12" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="273" t="s">
+      <c r="A11" s="254" t="s">
         <v>22</v>
       </c>
-      <c r="B11" s="274"/>
-      <c r="C11" s="275"/>
+      <c r="B11" s="255"/>
+      <c r="C11" s="256"/>
       <c r="D11" s="72" t="str">
         <f>'Page 1'!D11</f>
         <v>10TH JUDICIAL REGION</v>
       </c>
-      <c r="E11" s="299"/>
-      <c r="F11" s="263"/>
-      <c r="G11" s="263"/>
-      <c r="H11" s="263"/>
-      <c r="I11" s="263"/>
-      <c r="J11" s="316"/>
-      <c r="K11" s="312"/>
-      <c r="L11" s="312"/>
+      <c r="E11" s="265"/>
+      <c r="F11" s="249"/>
+      <c r="G11" s="249"/>
+      <c r="H11" s="249"/>
+      <c r="I11" s="249"/>
+      <c r="J11" s="291"/>
+      <c r="K11" s="289"/>
+      <c r="L11" s="289"/>
     </row>
     <row r="12" spans="1:12" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="273" t="s">
+      <c r="A12" s="254" t="s">
         <v>24</v>
       </c>
-      <c r="B12" s="274"/>
-      <c r="C12" s="275"/>
+      <c r="B12" s="255"/>
+      <c r="C12" s="256"/>
       <c r="D12" s="227" t="str">
         <f>'Page 1'!D12</f>
         <v>June 2026</v>
       </c>
-      <c r="E12" s="300"/>
-      <c r="F12" s="264"/>
-      <c r="G12" s="264"/>
-      <c r="H12" s="264"/>
-      <c r="I12" s="264"/>
-      <c r="J12" s="317"/>
-      <c r="K12" s="312"/>
-      <c r="L12" s="312"/>
+      <c r="E12" s="266"/>
+      <c r="F12" s="250"/>
+      <c r="G12" s="250"/>
+      <c r="H12" s="250"/>
+      <c r="I12" s="250"/>
+      <c r="J12" s="292"/>
+      <c r="K12" s="289"/>
+      <c r="L12" s="289"/>
     </row>
     <row r="13" spans="1:12" s="69" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="284"/>
-      <c r="B13" s="307"/>
-      <c r="C13" s="307"/>
-      <c r="D13" s="286"/>
+      <c r="A13" s="278"/>
+      <c r="B13" s="299"/>
+      <c r="C13" s="299"/>
+      <c r="D13" s="280"/>
       <c r="E13" s="73" t="s">
         <v>81</v>
       </c>
@@ -5250,10 +5250,10 @@
       <c r="B14" s="27" t="s">
         <v>38</v>
       </c>
-      <c r="C14" s="265" t="s">
+      <c r="C14" s="285" t="s">
         <v>39</v>
       </c>
-      <c r="D14" s="260"/>
+      <c r="D14" s="247"/>
       <c r="E14" s="28">
         <v>5</v>
       </c>
@@ -5288,10 +5288,10 @@
       <c r="B15" s="30" t="s">
         <v>40</v>
       </c>
-      <c r="C15" s="261" t="s">
+      <c r="C15" s="263" t="s">
         <v>41</v>
       </c>
-      <c r="D15" s="260"/>
+      <c r="D15" s="247"/>
       <c r="E15" s="28">
         <f t="shared" ref="E15:J15" si="1">SUM(E16:E18)</f>
         <v>1</v>
@@ -5326,16 +5326,16 @@
       </c>
     </row>
     <row r="16" spans="1:12" s="53" customFormat="1" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="295" t="s">
+      <c r="A16" s="258" t="s">
         <v>42</v>
       </c>
       <c r="B16" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="C16" s="266" t="s">
+      <c r="C16" s="286" t="s">
         <v>44</v>
       </c>
-      <c r="D16" s="267"/>
+      <c r="D16" s="287"/>
       <c r="E16" s="78">
         <v>1</v>
       </c>
@@ -5364,14 +5364,14 @@
       </c>
     </row>
     <row r="17" spans="1:27" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="296"/>
+      <c r="A17" s="259"/>
       <c r="B17" s="32" t="s">
         <v>45</v>
       </c>
-      <c r="C17" s="292" t="s">
+      <c r="C17" s="252" t="s">
         <v>46</v>
       </c>
-      <c r="D17" s="293"/>
+      <c r="D17" s="253"/>
       <c r="E17" s="33">
         <v>0</v>
       </c>
@@ -5400,14 +5400,14 @@
       </c>
     </row>
     <row r="18" spans="1:27" s="53" customFormat="1" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="297"/>
+      <c r="A18" s="260"/>
       <c r="B18" s="36" t="s">
         <v>47</v>
       </c>
-      <c r="C18" s="268" t="s">
+      <c r="C18" s="261" t="s">
         <v>48</v>
       </c>
-      <c r="D18" s="269"/>
+      <c r="D18" s="262"/>
       <c r="E18" s="85">
         <v>0</v>
       </c>
@@ -5442,10 +5442,10 @@
       <c r="B19" s="30" t="s">
         <v>49</v>
       </c>
-      <c r="C19" s="261" t="s">
+      <c r="C19" s="263" t="s">
         <v>50</v>
       </c>
-      <c r="D19" s="260"/>
+      <c r="D19" s="247"/>
       <c r="E19" s="28">
         <f t="shared" ref="E19:J19" si="2">SUM(E20:E23)</f>
         <v>2</v>
@@ -5480,16 +5480,16 @@
       </c>
     </row>
     <row r="20" spans="1:27" s="53" customFormat="1" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="295" t="s">
+      <c r="A20" s="258" t="s">
         <v>51</v>
       </c>
       <c r="B20" s="37" t="s">
         <v>52</v>
       </c>
-      <c r="C20" s="266" t="s">
+      <c r="C20" s="286" t="s">
         <v>53</v>
       </c>
-      <c r="D20" s="267"/>
+      <c r="D20" s="287"/>
       <c r="E20" s="78">
         <v>0</v>
       </c>
@@ -5518,14 +5518,14 @@
       </c>
     </row>
     <row r="21" spans="1:27" s="53" customFormat="1" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="296"/>
+      <c r="A21" s="259"/>
       <c r="B21" s="32" t="s">
         <v>54</v>
       </c>
-      <c r="C21" s="294" t="s">
+      <c r="C21" s="257" t="s">
         <v>55</v>
       </c>
-      <c r="D21" s="293"/>
+      <c r="D21" s="253"/>
       <c r="E21" s="33">
         <v>2</v>
       </c>
@@ -5554,14 +5554,14 @@
       </c>
     </row>
     <row r="22" spans="1:27" s="53" customFormat="1" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="296"/>
+      <c r="A22" s="259"/>
       <c r="B22" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="C22" s="292" t="s">
+      <c r="C22" s="252" t="s">
         <v>57</v>
       </c>
-      <c r="D22" s="293"/>
+      <c r="D22" s="253"/>
       <c r="E22" s="33">
         <v>0</v>
       </c>
@@ -5590,14 +5590,14 @@
       </c>
     </row>
     <row r="23" spans="1:27" s="53" customFormat="1" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="297"/>
+      <c r="A23" s="260"/>
       <c r="B23" s="38" t="s">
         <v>58</v>
       </c>
-      <c r="C23" s="268" t="s">
+      <c r="C23" s="261" t="s">
         <v>59</v>
       </c>
-      <c r="D23" s="269"/>
+      <c r="D23" s="262"/>
       <c r="E23" s="85">
         <v>0</v>
       </c>
@@ -5635,10 +5635,10 @@
       <c r="B24" s="30" t="s">
         <v>60</v>
       </c>
-      <c r="C24" s="259" t="s">
+      <c r="C24" s="246" t="s">
         <v>61</v>
       </c>
-      <c r="D24" s="260"/>
+      <c r="D24" s="247"/>
       <c r="E24" s="28">
         <f>(E14+E15)-E19</f>
         <v>4</v>
@@ -5679,10 +5679,10 @@
       <c r="B25" s="30" t="s">
         <v>62</v>
       </c>
-      <c r="C25" s="259" t="s">
+      <c r="C25" s="246" t="s">
         <v>90</v>
       </c>
-      <c r="D25" s="260"/>
+      <c r="D25" s="247"/>
       <c r="E25" s="40"/>
       <c r="F25" s="90"/>
       <c r="G25" s="41"/>
@@ -5847,6 +5847,21 @@
     </row>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F7:F12"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="A3:L3"/>
+    <mergeCell ref="E5:L5"/>
+    <mergeCell ref="A6:D7"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A4:L4"/>
+    <mergeCell ref="K7:K12"/>
+    <mergeCell ref="E6:K6"/>
+    <mergeCell ref="C18:D18"/>
     <mergeCell ref="C25:D25"/>
     <mergeCell ref="G7:G12"/>
     <mergeCell ref="L6:L12"/>
@@ -5863,21 +5878,6 @@
     <mergeCell ref="A16:A18"/>
     <mergeCell ref="C19:D19"/>
     <mergeCell ref="E7:E12"/>
-    <mergeCell ref="A3:L3"/>
-    <mergeCell ref="E5:L5"/>
-    <mergeCell ref="A6:D7"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="A4:L4"/>
-    <mergeCell ref="K7:K12"/>
-    <mergeCell ref="E6:K6"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F7:F12"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="A12:C12"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0.51181102362204722" footer="0.51181102362204722"/>
@@ -5914,85 +5914,85 @@
       <c r="G2" s="125"/>
     </row>
     <row r="3" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="318" t="s">
+      <c r="A3" s="305" t="s">
         <v>95</v>
       </c>
-      <c r="B3" s="319"/>
-      <c r="C3" s="320"/>
-      <c r="D3" s="320"/>
-      <c r="E3" s="320"/>
-      <c r="F3" s="319"/>
-      <c r="G3" s="319"/>
+      <c r="B3" s="306"/>
+      <c r="C3" s="307"/>
+      <c r="D3" s="307"/>
+      <c r="E3" s="307"/>
+      <c r="F3" s="306"/>
+      <c r="G3" s="306"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="254"/>
-      <c r="B4" s="319"/>
-      <c r="C4" s="320"/>
-      <c r="D4" s="320"/>
-      <c r="E4" s="320"/>
-      <c r="F4" s="319"/>
-      <c r="G4" s="319"/>
+      <c r="A4" s="308"/>
+      <c r="B4" s="306"/>
+      <c r="C4" s="307"/>
+      <c r="D4" s="307"/>
+      <c r="E4" s="307"/>
+      <c r="F4" s="306"/>
+      <c r="G4" s="306"/>
     </row>
     <row r="5" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="324" t="s">
+      <c r="A5" s="312" t="s">
         <v>96</v>
       </c>
-      <c r="B5" s="326" t="s">
+      <c r="B5" s="314" t="s">
         <v>97</v>
       </c>
-      <c r="C5" s="327" t="s">
+      <c r="C5" s="315" t="s">
         <v>98</v>
       </c>
-      <c r="D5" s="325" t="s">
+      <c r="D5" s="313" t="s">
         <v>99</v>
       </c>
-      <c r="E5" s="325" t="s">
+      <c r="E5" s="313" t="s">
         <v>100</v>
       </c>
-      <c r="F5" s="326" t="s">
+      <c r="F5" s="314" t="s">
         <v>101</v>
       </c>
-      <c r="G5" s="326" t="s">
+      <c r="G5" s="314" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="263"/>
-      <c r="B6" s="263"/>
-      <c r="C6" s="263"/>
-      <c r="D6" s="263"/>
-      <c r="E6" s="263"/>
-      <c r="F6" s="263"/>
-      <c r="G6" s="263"/>
+      <c r="A6" s="249"/>
+      <c r="B6" s="249"/>
+      <c r="C6" s="249"/>
+      <c r="D6" s="249"/>
+      <c r="E6" s="249"/>
+      <c r="F6" s="249"/>
+      <c r="G6" s="249"/>
     </row>
     <row r="7" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="263"/>
-      <c r="B7" s="263"/>
-      <c r="C7" s="263"/>
-      <c r="D7" s="263"/>
-      <c r="E7" s="263"/>
-      <c r="F7" s="263"/>
-      <c r="G7" s="263"/>
+      <c r="A7" s="249"/>
+      <c r="B7" s="249"/>
+      <c r="C7" s="249"/>
+      <c r="D7" s="249"/>
+      <c r="E7" s="249"/>
+      <c r="F7" s="249"/>
+      <c r="G7" s="249"/>
     </row>
     <row r="8" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="264"/>
-      <c r="B8" s="264"/>
-      <c r="C8" s="264"/>
-      <c r="D8" s="264"/>
-      <c r="E8" s="264"/>
-      <c r="F8" s="264"/>
-      <c r="G8" s="264"/>
+      <c r="A8" s="250"/>
+      <c r="B8" s="250"/>
+      <c r="C8" s="250"/>
+      <c r="D8" s="250"/>
+      <c r="E8" s="250"/>
+      <c r="F8" s="250"/>
+      <c r="G8" s="250"/>
     </row>
     <row r="9" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="321" t="s">
+      <c r="A9" s="309" t="s">
         <v>103</v>
       </c>
-      <c r="B9" s="322"/>
-      <c r="C9" s="322"/>
-      <c r="D9" s="322"/>
-      <c r="E9" s="322"/>
-      <c r="F9" s="322"/>
-      <c r="G9" s="323"/>
+      <c r="B9" s="310"/>
+      <c r="C9" s="310"/>
+      <c r="D9" s="310"/>
+      <c r="E9" s="310"/>
+      <c r="F9" s="310"/>
+      <c r="G9" s="311"/>
     </row>
     <row r="10" spans="1:7" s="130" customFormat="1" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="126"/>
@@ -6085,15 +6085,15 @@
       <c r="G19" s="136"/>
     </row>
     <row r="20" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="321" t="s">
+      <c r="A20" s="309" t="s">
         <v>104</v>
       </c>
-      <c r="B20" s="322"/>
-      <c r="C20" s="322"/>
-      <c r="D20" s="322"/>
-      <c r="E20" s="322"/>
-      <c r="F20" s="322"/>
-      <c r="G20" s="323"/>
+      <c r="B20" s="310"/>
+      <c r="C20" s="310"/>
+      <c r="D20" s="310"/>
+      <c r="E20" s="310"/>
+      <c r="F20" s="310"/>
+      <c r="G20" s="311"/>
     </row>
     <row r="21" spans="1:7" s="130" customFormat="1" ht="111" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="241">
@@ -6119,7 +6119,7 @@
       </c>
     </row>
     <row r="22" spans="1:7" s="132" customFormat="1" ht="26.85" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="336">
+      <c r="A22" s="242">
         <v>754</v>
       </c>
       <c r="B22" s="240" t="s">
@@ -6255,11 +6255,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A1" s="328" t="s">
+      <c r="A1" s="243" t="s">
         <v>106</v>
       </c>
       <c r="B1" s="244"/>
-      <c r="C1" s="329"/>
+      <c r="C1" s="245"/>
       <c r="F1" s="147" t="s">
         <v>107</v>
       </c>
@@ -6507,7 +6507,7 @@
         <v>1</v>
       </c>
       <c r="D20" s="150"/>
-      <c r="F20" s="328" t="s">
+      <c r="F20" s="243" t="s">
         <v>144</v>
       </c>
       <c r="G20" s="244"/>
@@ -7134,7 +7134,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="251" t="s">
+      <c r="A1" s="316" t="s">
         <v>185</v>
       </c>
       <c r="B1" s="244"/>
@@ -7223,7 +7223,7 @@
       <c r="B5" s="120" t="s">
         <v>110</v>
       </c>
-      <c r="C5" s="243" t="s">
+      <c r="C5" s="328" t="s">
         <v>190</v>
       </c>
       <c r="D5" s="244"/>
@@ -7248,7 +7248,7 @@
       <c r="Z5" s="183"/>
     </row>
     <row r="6" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C6" s="243" t="s">
+      <c r="C6" s="328" t="s">
         <v>192</v>
       </c>
       <c r="D6" s="244"/>
@@ -7259,21 +7259,21 @@
         <v>0</v>
       </c>
       <c r="N6" s="180"/>
-      <c r="R6" s="249" t="s">
+      <c r="R6" s="330" t="s">
         <v>193</v>
       </c>
-      <c r="S6" s="250"/>
-      <c r="T6" s="250"/>
-      <c r="U6" s="250"/>
-      <c r="V6" s="250"/>
-      <c r="W6" s="250"/>
-      <c r="X6" s="250"/>
-      <c r="Y6" s="250"/>
-      <c r="Z6" s="250"/>
+      <c r="S6" s="323"/>
+      <c r="T6" s="323"/>
+      <c r="U6" s="323"/>
+      <c r="V6" s="323"/>
+      <c r="W6" s="323"/>
+      <c r="X6" s="323"/>
+      <c r="Y6" s="323"/>
+      <c r="Z6" s="323"/>
       <c r="AA6" s="184"/>
     </row>
     <row r="7" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C7" s="243" t="s">
+      <c r="C7" s="328" t="s">
         <v>194</v>
       </c>
       <c r="D7" s="244"/>
@@ -7284,15 +7284,15 @@
         <v>0</v>
       </c>
       <c r="N7" s="180"/>
-      <c r="R7" s="250"/>
-      <c r="S7" s="250"/>
-      <c r="T7" s="250"/>
-      <c r="U7" s="250"/>
-      <c r="V7" s="250"/>
-      <c r="W7" s="250"/>
-      <c r="X7" s="250"/>
-      <c r="Y7" s="250"/>
-      <c r="Z7" s="250"/>
+      <c r="R7" s="323"/>
+      <c r="S7" s="323"/>
+      <c r="T7" s="323"/>
+      <c r="U7" s="323"/>
+      <c r="V7" s="323"/>
+      <c r="W7" s="323"/>
+      <c r="X7" s="323"/>
+      <c r="Y7" s="323"/>
+      <c r="Z7" s="323"/>
       <c r="AA7" s="184"/>
     </row>
     <row r="8" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -7306,15 +7306,15 @@
         <v>0</v>
       </c>
       <c r="N8" s="180"/>
-      <c r="R8" s="250"/>
-      <c r="S8" s="250"/>
-      <c r="T8" s="250"/>
-      <c r="U8" s="250"/>
-      <c r="V8" s="250"/>
-      <c r="W8" s="250"/>
-      <c r="X8" s="250"/>
-      <c r="Y8" s="250"/>
-      <c r="Z8" s="250"/>
+      <c r="R8" s="323"/>
+      <c r="S8" s="323"/>
+      <c r="T8" s="323"/>
+      <c r="U8" s="323"/>
+      <c r="V8" s="323"/>
+      <c r="W8" s="323"/>
+      <c r="X8" s="323"/>
+      <c r="Y8" s="323"/>
+      <c r="Z8" s="323"/>
       <c r="AA8" s="184"/>
     </row>
     <row r="9" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7329,15 +7329,15 @@
         <v>197</v>
       </c>
       <c r="N9" s="180"/>
-      <c r="R9" s="248"/>
-      <c r="S9" s="248"/>
-      <c r="T9" s="248"/>
-      <c r="U9" s="248"/>
-      <c r="V9" s="248"/>
-      <c r="W9" s="248"/>
-      <c r="X9" s="248"/>
-      <c r="Y9" s="248"/>
-      <c r="Z9" s="248"/>
+      <c r="R9" s="320"/>
+      <c r="S9" s="320"/>
+      <c r="T9" s="320"/>
+      <c r="U9" s="320"/>
+      <c r="V9" s="320"/>
+      <c r="W9" s="320"/>
+      <c r="X9" s="320"/>
+      <c r="Y9" s="320"/>
+      <c r="Z9" s="320"/>
       <c r="AA9" s="148"/>
     </row>
     <row r="10" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -7415,7 +7415,7 @@
       <c r="N14" s="180"/>
     </row>
     <row r="15" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C15" s="243" t="s">
+      <c r="C15" s="328" t="s">
         <v>192</v>
       </c>
       <c r="D15" s="244"/>
@@ -7435,7 +7435,7 @@
       <c r="AA15" s="148"/>
     </row>
     <row r="16" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C16" s="243" t="s">
+      <c r="C16" s="328" t="s">
         <v>194</v>
       </c>
       <c r="D16" s="244"/>
@@ -7527,7 +7527,7 @@
       <c r="N21" s="180"/>
     </row>
     <row r="23" spans="1:27" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="257" t="s">
+      <c r="A23" s="324" t="s">
         <v>211</v>
       </c>
       <c r="B23" s="244"/>
@@ -7561,88 +7561,88 @@
       <c r="A26" s="148"/>
       <c r="B26" s="193"/>
       <c r="C26" s="193"/>
-      <c r="D26" s="247" t="s">
+      <c r="D26" s="319" t="s">
         <v>233</v>
       </c>
-      <c r="E26" s="248"/>
-      <c r="F26" s="248"/>
-      <c r="G26" s="248"/>
-      <c r="H26" s="248"/>
-      <c r="I26" s="248"/>
-      <c r="J26" s="248"/>
-      <c r="K26" s="248"/>
-      <c r="L26" s="248"/>
+      <c r="E26" s="320"/>
+      <c r="F26" s="320"/>
+      <c r="G26" s="320"/>
+      <c r="H26" s="320"/>
+      <c r="I26" s="320"/>
+      <c r="J26" s="320"/>
+      <c r="K26" s="320"/>
+      <c r="L26" s="320"/>
       <c r="M26" s="193"/>
       <c r="N26" s="193"/>
       <c r="O26" s="148"/>
       <c r="P26" s="148"/>
       <c r="Q26" s="148"/>
-      <c r="R26" s="247" t="s">
+      <c r="R26" s="319" t="s">
         <v>231</v>
       </c>
-      <c r="S26" s="248"/>
-      <c r="T26" s="248"/>
-      <c r="U26" s="248"/>
-      <c r="V26" s="248"/>
-      <c r="W26" s="248"/>
-      <c r="X26" s="248"/>
-      <c r="Y26" s="248"/>
-      <c r="Z26" s="248"/>
+      <c r="S26" s="320"/>
+      <c r="T26" s="320"/>
+      <c r="U26" s="320"/>
+      <c r="V26" s="320"/>
+      <c r="W26" s="320"/>
+      <c r="X26" s="320"/>
+      <c r="Y26" s="320"/>
+      <c r="Z26" s="320"/>
       <c r="AA26" s="148"/>
     </row>
     <row r="27" spans="1:27" x14ac:dyDescent="0.25">
       <c r="C27" s="148"/>
-      <c r="D27" s="245" t="s">
+      <c r="D27" s="325" t="s">
         <v>234</v>
       </c>
-      <c r="E27" s="246"/>
-      <c r="F27" s="246"/>
-      <c r="G27" s="246"/>
-      <c r="H27" s="246"/>
-      <c r="I27" s="246"/>
-      <c r="J27" s="246"/>
-      <c r="K27" s="246"/>
-      <c r="L27" s="246"/>
+      <c r="E27" s="326"/>
+      <c r="F27" s="326"/>
+      <c r="G27" s="326"/>
+      <c r="H27" s="326"/>
+      <c r="I27" s="326"/>
+      <c r="J27" s="326"/>
+      <c r="K27" s="326"/>
+      <c r="L27" s="326"/>
       <c r="M27" s="148"/>
       <c r="N27" s="148"/>
       <c r="O27" s="148"/>
       <c r="P27" s="148"/>
       <c r="Q27" s="148"/>
-      <c r="R27" s="245" t="s">
+      <c r="R27" s="325" t="s">
         <v>232</v>
       </c>
-      <c r="S27" s="246"/>
-      <c r="T27" s="246"/>
-      <c r="U27" s="246"/>
-      <c r="V27" s="246"/>
-      <c r="W27" s="246"/>
-      <c r="X27" s="246"/>
-      <c r="Y27" s="246"/>
-      <c r="Z27" s="246"/>
+      <c r="S27" s="326"/>
+      <c r="T27" s="326"/>
+      <c r="U27" s="326"/>
+      <c r="V27" s="326"/>
+      <c r="W27" s="326"/>
+      <c r="X27" s="326"/>
+      <c r="Y27" s="326"/>
+      <c r="Z27" s="326"/>
       <c r="AA27" s="148"/>
     </row>
     <row r="28" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="D28" s="256"/>
-      <c r="E28" s="250"/>
-      <c r="F28" s="250"/>
-      <c r="G28" s="250"/>
-      <c r="H28" s="250"/>
-      <c r="I28" s="250"/>
-      <c r="J28" s="250"/>
-      <c r="K28" s="250"/>
-      <c r="L28" s="250"/>
-      <c r="R28" s="256"/>
-      <c r="S28" s="250"/>
-      <c r="T28" s="250"/>
-      <c r="U28" s="250"/>
-      <c r="V28" s="250"/>
-      <c r="W28" s="250"/>
-      <c r="X28" s="250"/>
-      <c r="Y28" s="250"/>
-      <c r="Z28" s="250"/>
+      <c r="D28" s="322"/>
+      <c r="E28" s="323"/>
+      <c r="F28" s="323"/>
+      <c r="G28" s="323"/>
+      <c r="H28" s="323"/>
+      <c r="I28" s="323"/>
+      <c r="J28" s="323"/>
+      <c r="K28" s="323"/>
+      <c r="L28" s="323"/>
+      <c r="R28" s="322"/>
+      <c r="S28" s="323"/>
+      <c r="T28" s="323"/>
+      <c r="U28" s="323"/>
+      <c r="V28" s="323"/>
+      <c r="W28" s="323"/>
+      <c r="X28" s="323"/>
+      <c r="Y28" s="323"/>
+      <c r="Z28" s="323"/>
     </row>
     <row r="29" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="D29" s="254" t="s">
+      <c r="D29" s="308" t="s">
         <v>212</v>
       </c>
       <c r="E29" s="244"/>
@@ -7762,7 +7762,7 @@
       <c r="AA33" s="165"/>
     </row>
     <row r="34" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="254" t="s">
+      <c r="A34" s="308" t="s">
         <v>216</v>
       </c>
       <c r="B34" s="244"/>
@@ -7774,24 +7774,24 @@
       <c r="H34" s="165" t="s">
         <v>217</v>
       </c>
-      <c r="I34" s="255" t="s">
+      <c r="I34" s="321" t="s">
         <v>235</v>
       </c>
-      <c r="J34" s="248"/>
-      <c r="K34" s="248"/>
-      <c r="L34" s="248"/>
-      <c r="M34" s="248"/>
-      <c r="N34" s="248"/>
+      <c r="J34" s="320"/>
+      <c r="K34" s="320"/>
+      <c r="L34" s="320"/>
+      <c r="M34" s="320"/>
+      <c r="N34" s="320"/>
       <c r="O34" s="165" t="s">
         <v>218</v>
       </c>
-      <c r="P34" s="242" t="s">
+      <c r="P34" s="329" t="s">
         <v>236</v>
       </c>
-      <c r="Q34" s="242"/>
-      <c r="R34" s="242"/>
-      <c r="S34" s="242"/>
-      <c r="T34" s="242"/>
+      <c r="Q34" s="329"/>
+      <c r="R34" s="329"/>
+      <c r="S34" s="329"/>
+      <c r="T34" s="329"/>
       <c r="U34" s="183"/>
       <c r="V34" s="194"/>
       <c r="W34" s="194"/>
@@ -7809,16 +7809,16 @@
       <c r="AA36" s="197"/>
     </row>
     <row r="37" spans="1:27" ht="29.1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="J37" s="258"/>
-      <c r="K37" s="248"/>
-      <c r="L37" s="248"/>
-      <c r="M37" s="248"/>
-      <c r="N37" s="248"/>
-      <c r="O37" s="248"/>
-      <c r="P37" s="248"/>
-      <c r="Q37" s="248"/>
-      <c r="R37" s="248"/>
-      <c r="S37" s="248"/>
+      <c r="J37" s="327"/>
+      <c r="K37" s="320"/>
+      <c r="L37" s="320"/>
+      <c r="M37" s="320"/>
+      <c r="N37" s="320"/>
+      <c r="O37" s="320"/>
+      <c r="P37" s="320"/>
+      <c r="Q37" s="320"/>
+      <c r="R37" s="320"/>
+      <c r="S37" s="320"/>
       <c r="T37" s="148"/>
       <c r="U37" s="148"/>
       <c r="V37" s="148"/>
@@ -7829,18 +7829,18 @@
       <c r="AA37" s="148"/>
     </row>
     <row r="38" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="J38" s="245" t="s">
+      <c r="J38" s="325" t="s">
         <v>219</v>
       </c>
-      <c r="K38" s="246"/>
-      <c r="L38" s="246"/>
-      <c r="M38" s="246"/>
-      <c r="N38" s="246"/>
-      <c r="O38" s="246"/>
-      <c r="P38" s="246"/>
-      <c r="Q38" s="246"/>
-      <c r="R38" s="246"/>
-      <c r="S38" s="246"/>
+      <c r="K38" s="326"/>
+      <c r="L38" s="326"/>
+      <c r="M38" s="326"/>
+      <c r="N38" s="326"/>
+      <c r="O38" s="326"/>
+      <c r="P38" s="326"/>
+      <c r="Q38" s="326"/>
+      <c r="R38" s="326"/>
+      <c r="S38" s="326"/>
       <c r="T38" s="148"/>
       <c r="U38" s="148"/>
       <c r="V38" s="148"/>
@@ -7851,12 +7851,12 @@
       <c r="AA38" s="148"/>
     </row>
     <row r="40" spans="1:27" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="253" t="s">
+      <c r="A40" s="318" t="s">
         <v>220</v>
       </c>
       <c r="B40" s="244"/>
       <c r="C40" s="244"/>
-      <c r="D40" s="252" t="s">
+      <c r="D40" s="317" t="s">
         <v>221</v>
       </c>
       <c r="E40" s="244"/>
@@ -7919,6 +7919,12 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="R27:Z27"/>
+    <mergeCell ref="R26:Z26"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="R6:Z9"/>
+    <mergeCell ref="C7:G7"/>
     <mergeCell ref="A1:AA1"/>
     <mergeCell ref="D40:AA40"/>
     <mergeCell ref="A40:C40"/>
@@ -7935,12 +7941,6 @@
     <mergeCell ref="C6:G6"/>
     <mergeCell ref="C15:G15"/>
     <mergeCell ref="P34:T34"/>
-    <mergeCell ref="C5:G5"/>
-    <mergeCell ref="R27:Z27"/>
-    <mergeCell ref="R26:Z26"/>
-    <mergeCell ref="C16:G16"/>
-    <mergeCell ref="R6:Z9"/>
-    <mergeCell ref="C7:G7"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0.51181102362204722" footer="0.51181102362204722"/>
@@ -7965,15 +7965,15 @@
     </row>
     <row r="30" spans="4:11" x14ac:dyDescent="0.2">
       <c r="D30" s="201"/>
-      <c r="E30" s="334" t="s">
+      <c r="E30" s="335" t="s">
         <v>222</v>
       </c>
-      <c r="F30" s="331"/>
-      <c r="G30" s="331"/>
-      <c r="H30" s="331"/>
-      <c r="I30" s="331"/>
-      <c r="J30" s="331"/>
-      <c r="K30" s="286"/>
+      <c r="F30" s="332"/>
+      <c r="G30" s="332"/>
+      <c r="H30" s="332"/>
+      <c r="I30" s="332"/>
+      <c r="J30" s="332"/>
+      <c r="K30" s="280"/>
     </row>
     <row r="31" spans="4:11" x14ac:dyDescent="0.2">
       <c r="D31" s="201"/>
@@ -7982,14 +7982,14 @@
     <row r="32" spans="4:11" x14ac:dyDescent="0.2">
       <c r="D32" s="201"/>
       <c r="E32" s="203"/>
-      <c r="F32" s="333" t="s">
+      <c r="F32" s="334" t="s">
         <v>223</v>
       </c>
-      <c r="G32" s="331"/>
-      <c r="H32" s="331"/>
-      <c r="I32" s="331"/>
-      <c r="J32" s="331"/>
-      <c r="K32" s="286"/>
+      <c r="G32" s="332"/>
+      <c r="H32" s="332"/>
+      <c r="I32" s="332"/>
+      <c r="J32" s="332"/>
+      <c r="K32" s="280"/>
     </row>
     <row r="33" spans="4:11" x14ac:dyDescent="0.2">
       <c r="D33" s="201"/>
@@ -7998,14 +7998,14 @@
     <row r="34" spans="4:11" x14ac:dyDescent="0.2">
       <c r="D34" s="201"/>
       <c r="E34" s="204"/>
-      <c r="F34" s="330" t="s">
+      <c r="F34" s="331" t="s">
         <v>224</v>
       </c>
-      <c r="G34" s="331"/>
-      <c r="H34" s="331"/>
-      <c r="I34" s="331"/>
-      <c r="J34" s="331"/>
-      <c r="K34" s="286"/>
+      <c r="G34" s="332"/>
+      <c r="H34" s="332"/>
+      <c r="I34" s="332"/>
+      <c r="J34" s="332"/>
+      <c r="K34" s="280"/>
     </row>
     <row r="35" spans="4:11" x14ac:dyDescent="0.2">
       <c r="D35" s="201"/>
@@ -8014,13 +8014,13 @@
     <row r="36" spans="4:11" x14ac:dyDescent="0.2">
       <c r="D36" s="201"/>
       <c r="E36" s="205"/>
-      <c r="F36" s="335" t="s">
+      <c r="F36" s="336" t="s">
         <v>225</v>
       </c>
-      <c r="G36" s="331"/>
-      <c r="H36" s="331"/>
-      <c r="I36" s="331"/>
-      <c r="J36" s="331"/>
+      <c r="G36" s="332"/>
+      <c r="H36" s="332"/>
+      <c r="I36" s="332"/>
+      <c r="J36" s="332"/>
       <c r="K36" s="202"/>
     </row>
     <row r="37" spans="4:11" x14ac:dyDescent="0.2">
@@ -8034,16 +8034,16 @@
       <c r="K37" s="208"/>
     </row>
     <row r="39" spans="4:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D39" s="332" t="s">
+      <c r="D39" s="333" t="s">
         <v>226</v>
       </c>
-      <c r="E39" s="331"/>
-      <c r="F39" s="331"/>
-      <c r="G39" s="331"/>
-      <c r="H39" s="331"/>
-      <c r="I39" s="331"/>
-      <c r="J39" s="331"/>
-      <c r="K39" s="331"/>
+      <c r="E39" s="332"/>
+      <c r="F39" s="332"/>
+      <c r="G39" s="332"/>
+      <c r="H39" s="332"/>
+      <c r="I39" s="332"/>
+      <c r="J39" s="332"/>
+      <c r="K39" s="332"/>
     </row>
   </sheetData>
   <mergeCells count="5">

--- a/app/static/storage/June 2026 MTC BUENAVISTA, AGUSAN DEL NORTE.xlsx
+++ b/app/static/storage/June 2026 MTC BUENAVISTA, AGUSAN DEL NORTE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PyZar\app\static\storage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C354453-22FF-4932-9B30-A01E2D053F3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07FA82CB-D413-41F9-AAC0-19F801FFDA63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="363" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="363" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Page 1" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="233">
   <si>
     <t>SC FORM MRC-FLC UPDATED JANUARY 2018 VER. 2.0</t>
   </si>
@@ -726,18 +726,6 @@
   </si>
   <si>
     <t>PRINT ALL SHEETS IN FOLIO SIZE</t>
-  </si>
-  <si>
-    <t>HRS. OF MAGDALINA TIMTIM NAMELY: EVANGELINE A. ALEGADO, NILDA M. ALEGADO, ZENAIDA A. ANDOY, ALBERTO BETARMOS, MIGUEL D. YONSON, FLORENCIO A. NAKILA, PACITA F. MARTINEZ, MARCELINA A. AMPO, DONATO T. ALEGADO, EMILIO T. ALEGADO ALL REP. BY RICARDO A. TAC-AN VS. CORAZON BUAL-CUYNO, ROEL B. ALNGOG, EVANGELINE A. DUMAGAN, SPS. RAMMEL &amp; MERIEL AUTOR, &amp; FICCO, &amp; THE REGISTRY OF DEEDS OF AGUSAN DEL NORTE</t>
-  </si>
-  <si>
-    <t>HON.SAIDAMEN M. GANIA</t>
-  </si>
-  <si>
-    <t>Not yet due</t>
-  </si>
-  <si>
-    <t>HRS. OF FLOCERPIDA A. SAAGUNDO, REP BY FLORLITA SAAGUNDO ASIO VS. TIRSO CANATOY, JR.</t>
   </si>
   <si>
     <t>GHAIZAR A. BAUTISTA - 09277294457</t>
@@ -3276,57 +3264,95 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="63" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="63" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="130" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="110" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="74" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="113" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="74" xfId="0" applyBorder="1"/>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="75" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="81" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="120" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="83" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="122" xfId="0" applyBorder="1"/>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="76" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="82" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="121" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="114" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="115" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="116" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="117" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="82" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="118" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="119" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="83" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="122" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="73" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="111" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="73" xfId="0" applyBorder="1"/>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="76" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="114" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="115" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3356,22 +3382,26 @@
     <xf numFmtId="3" fontId="3" fillId="0" borderId="77" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="81" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="75" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="82" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="121" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="82" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="120" xfId="0" applyBorder="1"/>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="87" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="118" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="119" xfId="0" applyBorder="1"/>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="73" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="78" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="88" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="112" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="88" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="111" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="73" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="84" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3391,17 +3421,23 @@
     <xf numFmtId="3" fontId="3" fillId="0" borderId="78" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="78" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="87" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="88" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="112" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="88" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="89" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -3419,58 +3455,10 @@
     <xf numFmtId="164" fontId="20" fillId="0" borderId="89" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="63" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="63" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="130" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
+    <xf numFmtId="3" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -3973,23 +3961,23 @@
       <c r="O2" s="4"/>
     </row>
     <row r="3" spans="1:20" s="8" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="276" t="s">
+      <c r="A3" s="283" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="277"/>
-      <c r="C3" s="277"/>
-      <c r="D3" s="277"/>
-      <c r="E3" s="277"/>
-      <c r="F3" s="277"/>
-      <c r="G3" s="277"/>
-      <c r="H3" s="277"/>
-      <c r="I3" s="277"/>
-      <c r="J3" s="277"/>
-      <c r="K3" s="277"/>
-      <c r="L3" s="277"/>
-      <c r="M3" s="277"/>
-      <c r="N3" s="277"/>
-      <c r="O3" s="277"/>
+      <c r="B3" s="284"/>
+      <c r="C3" s="284"/>
+      <c r="D3" s="284"/>
+      <c r="E3" s="284"/>
+      <c r="F3" s="284"/>
+      <c r="G3" s="284"/>
+      <c r="H3" s="284"/>
+      <c r="I3" s="284"/>
+      <c r="J3" s="284"/>
+      <c r="K3" s="284"/>
+      <c r="L3" s="284"/>
+      <c r="M3" s="284"/>
+      <c r="N3" s="284"/>
+      <c r="O3" s="284"/>
       <c r="P3" s="6"/>
       <c r="Q3" s="6"/>
       <c r="R3" s="6"/>
@@ -3997,23 +3985,23 @@
       <c r="T3" s="7"/>
     </row>
     <row r="4" spans="1:20" s="11" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="281" t="s">
+      <c r="A4" s="288" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="277"/>
-      <c r="C4" s="277"/>
-      <c r="D4" s="277"/>
-      <c r="E4" s="277"/>
-      <c r="F4" s="277"/>
-      <c r="G4" s="277"/>
-      <c r="H4" s="277"/>
-      <c r="I4" s="277"/>
-      <c r="J4" s="277"/>
-      <c r="K4" s="277"/>
-      <c r="L4" s="277"/>
-      <c r="M4" s="277"/>
-      <c r="N4" s="277"/>
-      <c r="O4" s="277"/>
+      <c r="B4" s="284"/>
+      <c r="C4" s="284"/>
+      <c r="D4" s="284"/>
+      <c r="E4" s="284"/>
+      <c r="F4" s="284"/>
+      <c r="G4" s="284"/>
+      <c r="H4" s="284"/>
+      <c r="I4" s="284"/>
+      <c r="J4" s="284"/>
+      <c r="K4" s="284"/>
+      <c r="L4" s="284"/>
+      <c r="M4" s="284"/>
+      <c r="N4" s="284"/>
+      <c r="O4" s="284"/>
       <c r="P4" s="9"/>
       <c r="Q4" s="9"/>
       <c r="R4" s="9"/>
@@ -4038,62 +4026,62 @@
       <c r="O5" s="12"/>
     </row>
     <row r="6" spans="1:20" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="270" t="s">
+      <c r="A6" s="277" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="271"/>
-      <c r="C6" s="271"/>
-      <c r="D6" s="272"/>
-      <c r="E6" s="282" t="s">
+      <c r="B6" s="278"/>
+      <c r="C6" s="278"/>
+      <c r="D6" s="279"/>
+      <c r="E6" s="289" t="s">
         <v>5</v>
       </c>
-      <c r="F6" s="283"/>
-      <c r="G6" s="283"/>
-      <c r="H6" s="283"/>
-      <c r="I6" s="283"/>
-      <c r="J6" s="283"/>
-      <c r="K6" s="283"/>
-      <c r="L6" s="283"/>
-      <c r="M6" s="283"/>
-      <c r="N6" s="283"/>
-      <c r="O6" s="247"/>
+      <c r="F6" s="290"/>
+      <c r="G6" s="290"/>
+      <c r="H6" s="290"/>
+      <c r="I6" s="290"/>
+      <c r="J6" s="290"/>
+      <c r="K6" s="290"/>
+      <c r="L6" s="290"/>
+      <c r="M6" s="290"/>
+      <c r="N6" s="290"/>
+      <c r="O6" s="261"/>
     </row>
     <row r="7" spans="1:20" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="273"/>
-      <c r="B7" s="274"/>
-      <c r="C7" s="274"/>
-      <c r="D7" s="275"/>
-      <c r="E7" s="264" t="s">
+      <c r="A7" s="280"/>
+      <c r="B7" s="281"/>
+      <c r="C7" s="281"/>
+      <c r="D7" s="282"/>
+      <c r="E7" s="299" t="s">
         <v>6</v>
       </c>
-      <c r="F7" s="248" t="s">
+      <c r="F7" s="263" t="s">
         <v>7</v>
       </c>
-      <c r="G7" s="248" t="s">
+      <c r="G7" s="263" t="s">
         <v>8</v>
       </c>
-      <c r="H7" s="251" t="s">
+      <c r="H7" s="292" t="s">
         <v>9</v>
       </c>
-      <c r="I7" s="251" t="s">
+      <c r="I7" s="292" t="s">
         <v>10</v>
       </c>
-      <c r="J7" s="251" t="s">
+      <c r="J7" s="292" t="s">
         <v>11</v>
       </c>
-      <c r="K7" s="248" t="s">
+      <c r="K7" s="263" t="s">
         <v>12</v>
       </c>
-      <c r="L7" s="248" t="s">
+      <c r="L7" s="263" t="s">
         <v>13</v>
       </c>
-      <c r="M7" s="251" t="s">
+      <c r="M7" s="292" t="s">
         <v>14</v>
       </c>
-      <c r="N7" s="267" t="s">
+      <c r="N7" s="271" t="s">
         <v>15</v>
       </c>
-      <c r="O7" s="284" t="s">
+      <c r="O7" s="291" t="s">
         <v>16</v>
       </c>
     </row>
@@ -4104,17 +4092,17 @@
       <c r="B8" s="14"/>
       <c r="C8" s="14"/>
       <c r="D8" s="15"/>
-      <c r="E8" s="265"/>
-      <c r="F8" s="249"/>
-      <c r="G8" s="249"/>
-      <c r="H8" s="249"/>
-      <c r="I8" s="249"/>
-      <c r="J8" s="249"/>
-      <c r="K8" s="249"/>
-      <c r="L8" s="249"/>
-      <c r="M8" s="249"/>
-      <c r="N8" s="268"/>
-      <c r="O8" s="280"/>
+      <c r="E8" s="300"/>
+      <c r="F8" s="264"/>
+      <c r="G8" s="264"/>
+      <c r="H8" s="264"/>
+      <c r="I8" s="264"/>
+      <c r="J8" s="264"/>
+      <c r="K8" s="264"/>
+      <c r="L8" s="264"/>
+      <c r="M8" s="264"/>
+      <c r="N8" s="272"/>
+      <c r="O8" s="287"/>
     </row>
     <row r="9" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="16" t="s">
@@ -4125,86 +4113,86 @@
       <c r="D9" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="E9" s="265"/>
-      <c r="F9" s="249"/>
-      <c r="G9" s="249"/>
-      <c r="H9" s="249"/>
-      <c r="I9" s="249"/>
-      <c r="J9" s="249"/>
-      <c r="K9" s="249"/>
-      <c r="L9" s="249"/>
-      <c r="M9" s="249"/>
-      <c r="N9" s="268"/>
-      <c r="O9" s="280"/>
+      <c r="E9" s="300"/>
+      <c r="F9" s="264"/>
+      <c r="G9" s="264"/>
+      <c r="H9" s="264"/>
+      <c r="I9" s="264"/>
+      <c r="J9" s="264"/>
+      <c r="K9" s="264"/>
+      <c r="L9" s="264"/>
+      <c r="M9" s="264"/>
+      <c r="N9" s="272"/>
+      <c r="O9" s="287"/>
     </row>
     <row r="10" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="254" t="s">
+      <c r="A10" s="274" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="255"/>
-      <c r="C10" s="256"/>
+      <c r="B10" s="275"/>
+      <c r="C10" s="276"/>
       <c r="D10" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="E10" s="265"/>
-      <c r="F10" s="249"/>
-      <c r="G10" s="249"/>
-      <c r="H10" s="249"/>
-      <c r="I10" s="249"/>
-      <c r="J10" s="249"/>
-      <c r="K10" s="249"/>
-      <c r="L10" s="249"/>
-      <c r="M10" s="249"/>
-      <c r="N10" s="268"/>
-      <c r="O10" s="280"/>
+      <c r="E10" s="300"/>
+      <c r="F10" s="264"/>
+      <c r="G10" s="264"/>
+      <c r="H10" s="264"/>
+      <c r="I10" s="264"/>
+      <c r="J10" s="264"/>
+      <c r="K10" s="264"/>
+      <c r="L10" s="264"/>
+      <c r="M10" s="264"/>
+      <c r="N10" s="272"/>
+      <c r="O10" s="287"/>
     </row>
     <row r="11" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="254" t="s">
+      <c r="A11" s="274" t="s">
         <v>22</v>
       </c>
-      <c r="B11" s="255"/>
-      <c r="C11" s="256"/>
+      <c r="B11" s="275"/>
+      <c r="C11" s="276"/>
       <c r="D11" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="E11" s="265"/>
-      <c r="F11" s="249"/>
-      <c r="G11" s="249"/>
-      <c r="H11" s="249"/>
-      <c r="I11" s="249"/>
-      <c r="J11" s="249"/>
-      <c r="K11" s="249"/>
-      <c r="L11" s="249"/>
-      <c r="M11" s="249"/>
-      <c r="N11" s="268"/>
-      <c r="O11" s="280"/>
+      <c r="E11" s="300"/>
+      <c r="F11" s="264"/>
+      <c r="G11" s="264"/>
+      <c r="H11" s="264"/>
+      <c r="I11" s="264"/>
+      <c r="J11" s="264"/>
+      <c r="K11" s="264"/>
+      <c r="L11" s="264"/>
+      <c r="M11" s="264"/>
+      <c r="N11" s="272"/>
+      <c r="O11" s="287"/>
     </row>
     <row r="12" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="254" t="s">
+      <c r="A12" s="274" t="s">
         <v>24</v>
       </c>
-      <c r="B12" s="255"/>
-      <c r="C12" s="256"/>
+      <c r="B12" s="275"/>
+      <c r="C12" s="276"/>
       <c r="D12" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="E12" s="266"/>
-      <c r="F12" s="250"/>
-      <c r="G12" s="250"/>
-      <c r="H12" s="250"/>
-      <c r="I12" s="250"/>
-      <c r="J12" s="250"/>
-      <c r="K12" s="250"/>
-      <c r="L12" s="250"/>
-      <c r="M12" s="250"/>
-      <c r="N12" s="269"/>
-      <c r="O12" s="275"/>
+      <c r="E12" s="301"/>
+      <c r="F12" s="265"/>
+      <c r="G12" s="265"/>
+      <c r="H12" s="265"/>
+      <c r="I12" s="265"/>
+      <c r="J12" s="265"/>
+      <c r="K12" s="265"/>
+      <c r="L12" s="265"/>
+      <c r="M12" s="265"/>
+      <c r="N12" s="273"/>
+      <c r="O12" s="282"/>
     </row>
     <row r="13" spans="1:20" s="25" customFormat="1" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="278"/>
-      <c r="B13" s="279"/>
-      <c r="C13" s="279"/>
-      <c r="D13" s="280"/>
+      <c r="A13" s="285"/>
+      <c r="B13" s="286"/>
+      <c r="C13" s="286"/>
+      <c r="D13" s="287"/>
       <c r="E13" s="20" t="s">
         <v>26</v>
       </c>
@@ -4246,10 +4234,10 @@
       <c r="B14" s="27" t="s">
         <v>38</v>
       </c>
-      <c r="C14" s="285" t="s">
+      <c r="C14" s="266" t="s">
         <v>39</v>
       </c>
-      <c r="D14" s="247"/>
+      <c r="D14" s="261"/>
       <c r="E14" s="209">
         <v>0</v>
       </c>
@@ -4292,10 +4280,10 @@
       <c r="B15" s="30" t="s">
         <v>40</v>
       </c>
-      <c r="C15" s="263" t="s">
+      <c r="C15" s="262" t="s">
         <v>41</v>
       </c>
-      <c r="D15" s="247"/>
+      <c r="D15" s="261"/>
       <c r="E15" s="209">
         <f t="shared" ref="E15:N15" si="1">SUM(E16:E18)</f>
         <v>0</v>
@@ -4342,16 +4330,16 @@
       </c>
     </row>
     <row r="16" spans="1:20" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="258" t="s">
+      <c r="A16" s="296" t="s">
         <v>42</v>
       </c>
       <c r="B16" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="C16" s="286" t="s">
+      <c r="C16" s="267" t="s">
         <v>44</v>
       </c>
-      <c r="D16" s="287"/>
+      <c r="D16" s="268"/>
       <c r="E16" s="210">
         <v>0</v>
       </c>
@@ -4388,14 +4376,14 @@
       </c>
     </row>
     <row r="17" spans="1:15" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="259"/>
+      <c r="A17" s="297"/>
       <c r="B17" s="32" t="s">
         <v>45</v>
       </c>
-      <c r="C17" s="252" t="s">
+      <c r="C17" s="293" t="s">
         <v>46</v>
       </c>
-      <c r="D17" s="253"/>
+      <c r="D17" s="294"/>
       <c r="E17" s="210">
         <v>0</v>
       </c>
@@ -4432,14 +4420,14 @@
       </c>
     </row>
     <row r="18" spans="1:15" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="260"/>
+      <c r="A18" s="298"/>
       <c r="B18" s="36" t="s">
         <v>47</v>
       </c>
-      <c r="C18" s="261" t="s">
+      <c r="C18" s="269" t="s">
         <v>48</v>
       </c>
-      <c r="D18" s="262"/>
+      <c r="D18" s="270"/>
       <c r="E18" s="210">
         <v>0</v>
       </c>
@@ -4482,10 +4470,10 @@
       <c r="B19" s="30" t="s">
         <v>49</v>
       </c>
-      <c r="C19" s="263" t="s">
+      <c r="C19" s="262" t="s">
         <v>50</v>
       </c>
-      <c r="D19" s="247"/>
+      <c r="D19" s="261"/>
       <c r="E19" s="209">
         <f t="shared" ref="E19:N19" si="2">SUM(E20:E23)</f>
         <v>0</v>
@@ -4532,16 +4520,16 @@
       </c>
     </row>
     <row r="20" spans="1:15" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="258" t="s">
+      <c r="A20" s="296" t="s">
         <v>51</v>
       </c>
       <c r="B20" s="37" t="s">
         <v>52</v>
       </c>
-      <c r="C20" s="286" t="s">
+      <c r="C20" s="267" t="s">
         <v>53</v>
       </c>
-      <c r="D20" s="287"/>
+      <c r="D20" s="268"/>
       <c r="E20" s="211">
         <v>0</v>
       </c>
@@ -4578,14 +4566,14 @@
       </c>
     </row>
     <row r="21" spans="1:15" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="259"/>
+      <c r="A21" s="297"/>
       <c r="B21" s="32" t="s">
         <v>54</v>
       </c>
-      <c r="C21" s="257" t="s">
+      <c r="C21" s="295" t="s">
         <v>55</v>
       </c>
-      <c r="D21" s="253"/>
+      <c r="D21" s="294"/>
       <c r="E21" s="210">
         <v>0</v>
       </c>
@@ -4622,14 +4610,14 @@
       </c>
     </row>
     <row r="22" spans="1:15" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="259"/>
+      <c r="A22" s="297"/>
       <c r="B22" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="C22" s="252" t="s">
+      <c r="C22" s="293" t="s">
         <v>57</v>
       </c>
-      <c r="D22" s="253"/>
+      <c r="D22" s="294"/>
       <c r="E22" s="210">
         <v>0</v>
       </c>
@@ -4666,14 +4654,14 @@
       </c>
     </row>
     <row r="23" spans="1:15" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="260"/>
+      <c r="A23" s="298"/>
       <c r="B23" s="38" t="s">
         <v>58</v>
       </c>
-      <c r="C23" s="261" t="s">
+      <c r="C23" s="269" t="s">
         <v>59</v>
       </c>
-      <c r="D23" s="262"/>
+      <c r="D23" s="270"/>
       <c r="E23" s="212">
         <v>0</v>
       </c>
@@ -4716,10 +4704,10 @@
       <c r="B24" s="30" t="s">
         <v>60</v>
       </c>
-      <c r="C24" s="246" t="s">
+      <c r="C24" s="260" t="s">
         <v>61</v>
       </c>
-      <c r="D24" s="247"/>
+      <c r="D24" s="261"/>
       <c r="E24" s="29">
         <f t="shared" ref="E24:M24" si="3">(E14+E15)-E19</f>
         <v>0</v>
@@ -4772,10 +4760,10 @@
       <c r="B25" s="30" t="s">
         <v>62</v>
       </c>
-      <c r="C25" s="246" t="s">
+      <c r="C25" s="260" t="s">
         <v>63</v>
       </c>
-      <c r="D25" s="247"/>
+      <c r="D25" s="261"/>
       <c r="E25" s="41"/>
       <c r="F25" s="213"/>
       <c r="G25" s="41"/>
@@ -4937,23 +4925,6 @@
     </row>
   </sheetData>
   <mergeCells count="33">
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F7:F12"/>
-    <mergeCell ref="L7:L12"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="N7:N12"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="A6:D7"/>
-    <mergeCell ref="A3:O3"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="A4:O4"/>
-    <mergeCell ref="E6:O6"/>
-    <mergeCell ref="K7:K12"/>
-    <mergeCell ref="O7:O12"/>
     <mergeCell ref="C25:D25"/>
     <mergeCell ref="G7:G12"/>
     <mergeCell ref="I7:I12"/>
@@ -4970,6 +4941,23 @@
     <mergeCell ref="A16:A18"/>
     <mergeCell ref="C19:D19"/>
     <mergeCell ref="E7:E12"/>
+    <mergeCell ref="N7:N12"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="A6:D7"/>
+    <mergeCell ref="A3:O3"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A4:O4"/>
+    <mergeCell ref="E6:O6"/>
+    <mergeCell ref="K7:K12"/>
+    <mergeCell ref="O7:O12"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F7:F12"/>
+    <mergeCell ref="L7:L12"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="C18:D18"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.23622047244094491" bottom="0.23622047244094491" header="0.51181102362204722" footer="0.51181102362204722"/>
@@ -5025,98 +5013,98 @@
       <c r="L2" s="68"/>
     </row>
     <row r="3" spans="1:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="293" t="s">
+      <c r="A3" s="302" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="294"/>
-      <c r="C3" s="294"/>
-      <c r="D3" s="294"/>
-      <c r="E3" s="294"/>
-      <c r="F3" s="294"/>
-      <c r="G3" s="294"/>
-      <c r="H3" s="294"/>
-      <c r="I3" s="294"/>
-      <c r="J3" s="294"/>
-      <c r="K3" s="294"/>
-      <c r="L3" s="295"/>
+      <c r="B3" s="303"/>
+      <c r="C3" s="303"/>
+      <c r="D3" s="303"/>
+      <c r="E3" s="303"/>
+      <c r="F3" s="303"/>
+      <c r="G3" s="303"/>
+      <c r="H3" s="303"/>
+      <c r="I3" s="303"/>
+      <c r="J3" s="303"/>
+      <c r="K3" s="303"/>
+      <c r="L3" s="304"/>
     </row>
     <row r="4" spans="1:12" s="11" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="300" t="s">
+      <c r="A4" s="309" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="301"/>
-      <c r="C4" s="301"/>
-      <c r="D4" s="301"/>
-      <c r="E4" s="301"/>
-      <c r="F4" s="301"/>
-      <c r="G4" s="301"/>
-      <c r="H4" s="301"/>
-      <c r="I4" s="301"/>
-      <c r="J4" s="301"/>
-      <c r="K4" s="301"/>
-      <c r="L4" s="302"/>
+      <c r="B4" s="310"/>
+      <c r="C4" s="310"/>
+      <c r="D4" s="310"/>
+      <c r="E4" s="310"/>
+      <c r="F4" s="310"/>
+      <c r="G4" s="310"/>
+      <c r="H4" s="310"/>
+      <c r="I4" s="310"/>
+      <c r="J4" s="310"/>
+      <c r="K4" s="310"/>
+      <c r="L4" s="311"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="12"/>
       <c r="B5" s="12"/>
       <c r="C5" s="12"/>
       <c r="D5" s="12"/>
-      <c r="E5" s="296"/>
-      <c r="F5" s="297"/>
-      <c r="G5" s="297"/>
-      <c r="H5" s="297"/>
-      <c r="I5" s="297"/>
-      <c r="J5" s="297"/>
-      <c r="K5" s="297"/>
-      <c r="L5" s="298"/>
+      <c r="E5" s="305"/>
+      <c r="F5" s="306"/>
+      <c r="G5" s="306"/>
+      <c r="H5" s="306"/>
+      <c r="I5" s="306"/>
+      <c r="J5" s="306"/>
+      <c r="K5" s="306"/>
+      <c r="L5" s="307"/>
     </row>
     <row r="6" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="270" t="s">
+      <c r="A6" s="277" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="271"/>
-      <c r="C6" s="271"/>
-      <c r="D6" s="272"/>
-      <c r="E6" s="304" t="s">
+      <c r="B6" s="278"/>
+      <c r="C6" s="278"/>
+      <c r="D6" s="279"/>
+      <c r="E6" s="314" t="s">
         <v>72</v>
       </c>
-      <c r="F6" s="283"/>
-      <c r="G6" s="283"/>
-      <c r="H6" s="283"/>
-      <c r="I6" s="283"/>
-      <c r="J6" s="283"/>
-      <c r="K6" s="247"/>
-      <c r="L6" s="288" t="s">
+      <c r="F6" s="290"/>
+      <c r="G6" s="290"/>
+      <c r="H6" s="290"/>
+      <c r="I6" s="290"/>
+      <c r="J6" s="290"/>
+      <c r="K6" s="261"/>
+      <c r="L6" s="315" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="7" spans="1:12" s="69" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="273"/>
-      <c r="B7" s="274"/>
-      <c r="C7" s="274"/>
-      <c r="D7" s="275"/>
-      <c r="E7" s="264" t="s">
+      <c r="A7" s="280"/>
+      <c r="B7" s="281"/>
+      <c r="C7" s="281"/>
+      <c r="D7" s="282"/>
+      <c r="E7" s="299" t="s">
         <v>74</v>
       </c>
-      <c r="F7" s="251" t="s">
+      <c r="F7" s="292" t="s">
         <v>75</v>
       </c>
-      <c r="G7" s="248" t="s">
+      <c r="G7" s="263" t="s">
         <v>76</v>
       </c>
-      <c r="H7" s="248" t="s">
+      <c r="H7" s="263" t="s">
         <v>77</v>
       </c>
-      <c r="I7" s="248" t="s">
+      <c r="I7" s="263" t="s">
         <v>78</v>
       </c>
-      <c r="J7" s="290" t="s">
+      <c r="J7" s="316" t="s">
         <v>79</v>
       </c>
-      <c r="K7" s="303" t="s">
+      <c r="K7" s="312" t="s">
         <v>80</v>
       </c>
-      <c r="L7" s="289"/>
+      <c r="L7" s="313"/>
     </row>
     <row r="8" spans="1:12" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
@@ -5128,14 +5116,14 @@
         <f>'Page 1'!D8</f>
         <v>0</v>
       </c>
-      <c r="E8" s="265"/>
-      <c r="F8" s="249"/>
-      <c r="G8" s="249"/>
-      <c r="H8" s="249"/>
-      <c r="I8" s="249"/>
-      <c r="J8" s="291"/>
-      <c r="K8" s="289"/>
-      <c r="L8" s="289"/>
+      <c r="E8" s="300"/>
+      <c r="F8" s="264"/>
+      <c r="G8" s="264"/>
+      <c r="H8" s="264"/>
+      <c r="I8" s="264"/>
+      <c r="J8" s="317"/>
+      <c r="K8" s="313"/>
+      <c r="L8" s="313"/>
     </row>
     <row r="9" spans="1:12" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="16" t="s">
@@ -5147,77 +5135,77 @@
         <f>'Page 1'!D9</f>
         <v>BUENAVISTA</v>
       </c>
-      <c r="E9" s="265"/>
-      <c r="F9" s="249"/>
-      <c r="G9" s="249"/>
-      <c r="H9" s="249"/>
-      <c r="I9" s="249"/>
-      <c r="J9" s="291"/>
-      <c r="K9" s="289"/>
-      <c r="L9" s="289"/>
+      <c r="E9" s="300"/>
+      <c r="F9" s="264"/>
+      <c r="G9" s="264"/>
+      <c r="H9" s="264"/>
+      <c r="I9" s="264"/>
+      <c r="J9" s="317"/>
+      <c r="K9" s="313"/>
+      <c r="L9" s="313"/>
     </row>
     <row r="10" spans="1:12" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="254" t="s">
+      <c r="A10" s="274" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="255"/>
-      <c r="C10" s="256"/>
+      <c r="B10" s="275"/>
+      <c r="C10" s="276"/>
       <c r="D10" s="71" t="str">
         <f>'Page 1'!D10</f>
         <v>AGUSAN DEL NORTE</v>
       </c>
-      <c r="E10" s="265"/>
-      <c r="F10" s="249"/>
-      <c r="G10" s="249"/>
-      <c r="H10" s="249"/>
-      <c r="I10" s="249"/>
-      <c r="J10" s="291"/>
-      <c r="K10" s="289"/>
-      <c r="L10" s="289"/>
+      <c r="E10" s="300"/>
+      <c r="F10" s="264"/>
+      <c r="G10" s="264"/>
+      <c r="H10" s="264"/>
+      <c r="I10" s="264"/>
+      <c r="J10" s="317"/>
+      <c r="K10" s="313"/>
+      <c r="L10" s="313"/>
     </row>
     <row r="11" spans="1:12" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="254" t="s">
+      <c r="A11" s="274" t="s">
         <v>22</v>
       </c>
-      <c r="B11" s="255"/>
-      <c r="C11" s="256"/>
+      <c r="B11" s="275"/>
+      <c r="C11" s="276"/>
       <c r="D11" s="72" t="str">
         <f>'Page 1'!D11</f>
         <v>10TH JUDICIAL REGION</v>
       </c>
-      <c r="E11" s="265"/>
-      <c r="F11" s="249"/>
-      <c r="G11" s="249"/>
-      <c r="H11" s="249"/>
-      <c r="I11" s="249"/>
-      <c r="J11" s="291"/>
-      <c r="K11" s="289"/>
-      <c r="L11" s="289"/>
+      <c r="E11" s="300"/>
+      <c r="F11" s="264"/>
+      <c r="G11" s="264"/>
+      <c r="H11" s="264"/>
+      <c r="I11" s="264"/>
+      <c r="J11" s="317"/>
+      <c r="K11" s="313"/>
+      <c r="L11" s="313"/>
     </row>
     <row r="12" spans="1:12" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="254" t="s">
+      <c r="A12" s="274" t="s">
         <v>24</v>
       </c>
-      <c r="B12" s="255"/>
-      <c r="C12" s="256"/>
+      <c r="B12" s="275"/>
+      <c r="C12" s="276"/>
       <c r="D12" s="227" t="str">
         <f>'Page 1'!D12</f>
         <v>June 2026</v>
       </c>
-      <c r="E12" s="266"/>
-      <c r="F12" s="250"/>
-      <c r="G12" s="250"/>
-      <c r="H12" s="250"/>
-      <c r="I12" s="250"/>
-      <c r="J12" s="292"/>
-      <c r="K12" s="289"/>
-      <c r="L12" s="289"/>
+      <c r="E12" s="301"/>
+      <c r="F12" s="265"/>
+      <c r="G12" s="265"/>
+      <c r="H12" s="265"/>
+      <c r="I12" s="265"/>
+      <c r="J12" s="318"/>
+      <c r="K12" s="313"/>
+      <c r="L12" s="313"/>
     </row>
     <row r="13" spans="1:12" s="69" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="278"/>
-      <c r="B13" s="299"/>
-      <c r="C13" s="299"/>
-      <c r="D13" s="280"/>
+      <c r="A13" s="285"/>
+      <c r="B13" s="308"/>
+      <c r="C13" s="308"/>
+      <c r="D13" s="287"/>
       <c r="E13" s="73" t="s">
         <v>81</v>
       </c>
@@ -5250,10 +5238,10 @@
       <c r="B14" s="27" t="s">
         <v>38</v>
       </c>
-      <c r="C14" s="285" t="s">
+      <c r="C14" s="266" t="s">
         <v>39</v>
       </c>
-      <c r="D14" s="247"/>
+      <c r="D14" s="261"/>
       <c r="E14" s="28">
         <v>5</v>
       </c>
@@ -5288,10 +5276,10 @@
       <c r="B15" s="30" t="s">
         <v>40</v>
       </c>
-      <c r="C15" s="263" t="s">
+      <c r="C15" s="262" t="s">
         <v>41</v>
       </c>
-      <c r="D15" s="247"/>
+      <c r="D15" s="261"/>
       <c r="E15" s="28">
         <f t="shared" ref="E15:J15" si="1">SUM(E16:E18)</f>
         <v>1</v>
@@ -5326,16 +5314,16 @@
       </c>
     </row>
     <row r="16" spans="1:12" s="53" customFormat="1" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="258" t="s">
+      <c r="A16" s="296" t="s">
         <v>42</v>
       </c>
       <c r="B16" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="C16" s="286" t="s">
+      <c r="C16" s="267" t="s">
         <v>44</v>
       </c>
-      <c r="D16" s="287"/>
+      <c r="D16" s="268"/>
       <c r="E16" s="78">
         <v>1</v>
       </c>
@@ -5364,14 +5352,14 @@
       </c>
     </row>
     <row r="17" spans="1:27" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="259"/>
+      <c r="A17" s="297"/>
       <c r="B17" s="32" t="s">
         <v>45</v>
       </c>
-      <c r="C17" s="252" t="s">
+      <c r="C17" s="293" t="s">
         <v>46</v>
       </c>
-      <c r="D17" s="253"/>
+      <c r="D17" s="294"/>
       <c r="E17" s="33">
         <v>0</v>
       </c>
@@ -5400,14 +5388,14 @@
       </c>
     </row>
     <row r="18" spans="1:27" s="53" customFormat="1" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="260"/>
+      <c r="A18" s="298"/>
       <c r="B18" s="36" t="s">
         <v>47</v>
       </c>
-      <c r="C18" s="261" t="s">
+      <c r="C18" s="269" t="s">
         <v>48</v>
       </c>
-      <c r="D18" s="262"/>
+      <c r="D18" s="270"/>
       <c r="E18" s="85">
         <v>0</v>
       </c>
@@ -5442,10 +5430,10 @@
       <c r="B19" s="30" t="s">
         <v>49</v>
       </c>
-      <c r="C19" s="263" t="s">
+      <c r="C19" s="262" t="s">
         <v>50</v>
       </c>
-      <c r="D19" s="247"/>
+      <c r="D19" s="261"/>
       <c r="E19" s="28">
         <f t="shared" ref="E19:J19" si="2">SUM(E20:E23)</f>
         <v>2</v>
@@ -5460,7 +5448,7 @@
       </c>
       <c r="H19" s="76">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I19" s="76">
         <f t="shared" si="2"/>
@@ -5472,24 +5460,24 @@
       </c>
       <c r="K19" s="77">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L19" s="229">
         <f>'Page 1'!O19+'Page 2'!K19</f>
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:27" s="53" customFormat="1" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="258" t="s">
+      <c r="A20" s="296" t="s">
         <v>51</v>
       </c>
       <c r="B20" s="37" t="s">
         <v>52</v>
       </c>
-      <c r="C20" s="286" t="s">
+      <c r="C20" s="267" t="s">
         <v>53</v>
       </c>
-      <c r="D20" s="287"/>
+      <c r="D20" s="268"/>
       <c r="E20" s="78">
         <v>0</v>
       </c>
@@ -5500,7 +5488,7 @@
         <v>0</v>
       </c>
       <c r="H20" s="79">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I20" s="79">
         <v>0</v>
@@ -5510,22 +5498,22 @@
       </c>
       <c r="K20" s="89">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L20" s="230">
         <f>'Page 1'!O20+'Page 2'!K20</f>
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:27" s="53" customFormat="1" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="259"/>
+      <c r="A21" s="297"/>
       <c r="B21" s="32" t="s">
         <v>54</v>
       </c>
-      <c r="C21" s="257" t="s">
+      <c r="C21" s="295" t="s">
         <v>55</v>
       </c>
-      <c r="D21" s="253"/>
+      <c r="D21" s="294"/>
       <c r="E21" s="33">
         <v>2</v>
       </c>
@@ -5554,14 +5542,14 @@
       </c>
     </row>
     <row r="22" spans="1:27" s="53" customFormat="1" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="259"/>
+      <c r="A22" s="297"/>
       <c r="B22" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="C22" s="252" t="s">
+      <c r="C22" s="293" t="s">
         <v>57</v>
       </c>
-      <c r="D22" s="253"/>
+      <c r="D22" s="294"/>
       <c r="E22" s="33">
         <v>0</v>
       </c>
@@ -5590,14 +5578,14 @@
       </c>
     </row>
     <row r="23" spans="1:27" s="53" customFormat="1" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="260"/>
+      <c r="A23" s="298"/>
       <c r="B23" s="38" t="s">
         <v>58</v>
       </c>
-      <c r="C23" s="261" t="s">
+      <c r="C23" s="269" t="s">
         <v>59</v>
       </c>
-      <c r="D23" s="262"/>
+      <c r="D23" s="270"/>
       <c r="E23" s="85">
         <v>0</v>
       </c>
@@ -5635,10 +5623,10 @@
       <c r="B24" s="30" t="s">
         <v>60</v>
       </c>
-      <c r="C24" s="246" t="s">
+      <c r="C24" s="260" t="s">
         <v>61</v>
       </c>
-      <c r="D24" s="247"/>
+      <c r="D24" s="261"/>
       <c r="E24" s="28">
         <f>(E14+E15)-E19</f>
         <v>4</v>
@@ -5653,7 +5641,7 @@
       </c>
       <c r="H24" s="76">
         <f>SUM(H14+H15)-H19</f>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I24" s="76">
         <f>SUM(I14+I15)-I19</f>
@@ -5665,11 +5653,11 @@
       </c>
       <c r="K24" s="77">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L24" s="229">
         <f>'Page 1'!O24+'Page 2'!K24</f>
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="25" spans="1:27" s="53" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -5679,10 +5667,10 @@
       <c r="B25" s="30" t="s">
         <v>62</v>
       </c>
-      <c r="C25" s="246" t="s">
+      <c r="C25" s="260" t="s">
         <v>90</v>
       </c>
-      <c r="D25" s="247"/>
+      <c r="D25" s="261"/>
       <c r="E25" s="40"/>
       <c r="F25" s="90"/>
       <c r="G25" s="41"/>
@@ -5847,21 +5835,6 @@
     </row>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F7:F12"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="A3:L3"/>
-    <mergeCell ref="E5:L5"/>
-    <mergeCell ref="A6:D7"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="A4:L4"/>
-    <mergeCell ref="K7:K12"/>
-    <mergeCell ref="E6:K6"/>
-    <mergeCell ref="C18:D18"/>
     <mergeCell ref="C25:D25"/>
     <mergeCell ref="G7:G12"/>
     <mergeCell ref="L6:L12"/>
@@ -5878,6 +5851,21 @@
     <mergeCell ref="A16:A18"/>
     <mergeCell ref="C19:D19"/>
     <mergeCell ref="E7:E12"/>
+    <mergeCell ref="A3:L3"/>
+    <mergeCell ref="E5:L5"/>
+    <mergeCell ref="A6:D7"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A4:L4"/>
+    <mergeCell ref="K7:K12"/>
+    <mergeCell ref="E6:K6"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F7:F12"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A12:C12"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0.51181102362204722" footer="0.51181102362204722"/>
@@ -5914,85 +5902,85 @@
       <c r="G2" s="125"/>
     </row>
     <row r="3" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="305" t="s">
+      <c r="A3" s="319" t="s">
         <v>95</v>
       </c>
-      <c r="B3" s="306"/>
-      <c r="C3" s="307"/>
-      <c r="D3" s="307"/>
-      <c r="E3" s="307"/>
-      <c r="F3" s="306"/>
-      <c r="G3" s="306"/>
+      <c r="B3" s="320"/>
+      <c r="C3" s="321"/>
+      <c r="D3" s="321"/>
+      <c r="E3" s="321"/>
+      <c r="F3" s="320"/>
+      <c r="G3" s="320"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="308"/>
-      <c r="B4" s="306"/>
-      <c r="C4" s="307"/>
-      <c r="D4" s="307"/>
-      <c r="E4" s="307"/>
-      <c r="F4" s="306"/>
-      <c r="G4" s="306"/>
+      <c r="A4" s="254"/>
+      <c r="B4" s="320"/>
+      <c r="C4" s="321"/>
+      <c r="D4" s="321"/>
+      <c r="E4" s="321"/>
+      <c r="F4" s="320"/>
+      <c r="G4" s="320"/>
     </row>
     <row r="5" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="312" t="s">
+      <c r="A5" s="325" t="s">
         <v>96</v>
       </c>
-      <c r="B5" s="314" t="s">
+      <c r="B5" s="327" t="s">
         <v>97</v>
       </c>
-      <c r="C5" s="315" t="s">
+      <c r="C5" s="328" t="s">
         <v>98</v>
       </c>
-      <c r="D5" s="313" t="s">
+      <c r="D5" s="326" t="s">
         <v>99</v>
       </c>
-      <c r="E5" s="313" t="s">
+      <c r="E5" s="326" t="s">
         <v>100</v>
       </c>
-      <c r="F5" s="314" t="s">
+      <c r="F5" s="327" t="s">
         <v>101</v>
       </c>
-      <c r="G5" s="314" t="s">
+      <c r="G5" s="327" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="249"/>
-      <c r="B6" s="249"/>
-      <c r="C6" s="249"/>
-      <c r="D6" s="249"/>
-      <c r="E6" s="249"/>
-      <c r="F6" s="249"/>
-      <c r="G6" s="249"/>
+      <c r="A6" s="264"/>
+      <c r="B6" s="264"/>
+      <c r="C6" s="264"/>
+      <c r="D6" s="264"/>
+      <c r="E6" s="264"/>
+      <c r="F6" s="264"/>
+      <c r="G6" s="264"/>
     </row>
     <row r="7" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="249"/>
-      <c r="B7" s="249"/>
-      <c r="C7" s="249"/>
-      <c r="D7" s="249"/>
-      <c r="E7" s="249"/>
-      <c r="F7" s="249"/>
-      <c r="G7" s="249"/>
+      <c r="A7" s="264"/>
+      <c r="B7" s="264"/>
+      <c r="C7" s="264"/>
+      <c r="D7" s="264"/>
+      <c r="E7" s="264"/>
+      <c r="F7" s="264"/>
+      <c r="G7" s="264"/>
     </row>
     <row r="8" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="250"/>
-      <c r="B8" s="250"/>
-      <c r="C8" s="250"/>
-      <c r="D8" s="250"/>
-      <c r="E8" s="250"/>
-      <c r="F8" s="250"/>
-      <c r="G8" s="250"/>
+      <c r="A8" s="265"/>
+      <c r="B8" s="265"/>
+      <c r="C8" s="265"/>
+      <c r="D8" s="265"/>
+      <c r="E8" s="265"/>
+      <c r="F8" s="265"/>
+      <c r="G8" s="265"/>
     </row>
     <row r="9" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="309" t="s">
+      <c r="A9" s="322" t="s">
         <v>103</v>
       </c>
-      <c r="B9" s="310"/>
-      <c r="C9" s="310"/>
-      <c r="D9" s="310"/>
-      <c r="E9" s="310"/>
-      <c r="F9" s="310"/>
-      <c r="G9" s="311"/>
+      <c r="B9" s="323"/>
+      <c r="C9" s="323"/>
+      <c r="D9" s="323"/>
+      <c r="E9" s="323"/>
+      <c r="F9" s="323"/>
+      <c r="G9" s="324"/>
     </row>
     <row r="10" spans="1:7" s="130" customFormat="1" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="126"/>
@@ -6085,63 +6073,35 @@
       <c r="G19" s="136"/>
     </row>
     <row r="20" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="309" t="s">
+      <c r="A20" s="322" t="s">
         <v>104</v>
       </c>
-      <c r="B20" s="310"/>
-      <c r="C20" s="310"/>
-      <c r="D20" s="310"/>
-      <c r="E20" s="310"/>
-      <c r="F20" s="310"/>
-      <c r="G20" s="311"/>
-    </row>
-    <row r="21" spans="1:7" s="130" customFormat="1" ht="111" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="241">
-        <v>744</v>
-      </c>
-      <c r="B21" s="239" t="s">
-        <v>227</v>
-      </c>
-      <c r="C21" s="233">
-        <v>45215</v>
-      </c>
-      <c r="D21" s="233">
-        <v>46085</v>
-      </c>
-      <c r="E21" s="234">
-        <v>46179</v>
-      </c>
-      <c r="F21" s="235" t="s">
-        <v>228</v>
-      </c>
-      <c r="G21" s="236" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" s="132" customFormat="1" ht="26.85" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="242">
-        <v>754</v>
-      </c>
-      <c r="B22" s="240" t="s">
-        <v>230</v>
-      </c>
-      <c r="C22" s="237">
-        <v>45530</v>
-      </c>
-      <c r="D22" s="237">
-        <v>46085</v>
-      </c>
-      <c r="E22" s="237">
-        <v>46179</v>
-      </c>
-      <c r="F22" s="235" t="s">
-        <v>228</v>
-      </c>
-      <c r="G22" s="238" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" s="132" customFormat="1" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="323"/>
+      <c r="C20" s="323"/>
+      <c r="D20" s="323"/>
+      <c r="E20" s="323"/>
+      <c r="F20" s="323"/>
+      <c r="G20" s="324"/>
+    </row>
+    <row r="21" spans="1:7" s="130" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="241"/>
+      <c r="B21" s="239"/>
+      <c r="C21" s="233"/>
+      <c r="D21" s="233"/>
+      <c r="E21" s="234"/>
+      <c r="F21" s="235"/>
+      <c r="G21" s="236"/>
+    </row>
+    <row r="22" spans="1:7" s="132" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="242"/>
+      <c r="B22" s="240"/>
+      <c r="C22" s="237"/>
+      <c r="D22" s="237"/>
+      <c r="E22" s="237"/>
+      <c r="F22" s="235"/>
+      <c r="G22" s="238"/>
+    </row>
+    <row r="23" spans="1:7" s="132" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="138"/>
       <c r="B23" s="138"/>
       <c r="C23" s="138"/>
@@ -6255,11 +6215,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A1" s="243" t="s">
+      <c r="A1" s="329" t="s">
         <v>106</v>
       </c>
       <c r="B1" s="244"/>
-      <c r="C1" s="245"/>
+      <c r="C1" s="330"/>
       <c r="F1" s="147" t="s">
         <v>107</v>
       </c>
@@ -6275,7 +6235,7 @@
       </c>
       <c r="C2" s="149">
         <f>SUM(D3:D6)</f>
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="D2" s="150"/>
       <c r="G2" s="120" t="s">
@@ -6290,7 +6250,9 @@
         <v>112</v>
       </c>
       <c r="C3" s="150"/>
-      <c r="D3" s="151"/>
+      <c r="D3" s="151">
+        <v>2</v>
+      </c>
       <c r="H3" s="120" t="s">
         <v>113</v>
       </c>
@@ -6304,7 +6266,9 @@
         <v>114</v>
       </c>
       <c r="C4" s="150"/>
-      <c r="D4" s="154"/>
+      <c r="D4" s="154">
+        <v>6</v>
+      </c>
       <c r="H4" s="120" t="s">
         <v>115</v>
       </c>
@@ -6318,7 +6282,9 @@
         <v>116</v>
       </c>
       <c r="C5" s="150"/>
-      <c r="D5" s="154"/>
+      <c r="D5" s="154">
+        <v>2</v>
+      </c>
       <c r="H5" s="120" t="s">
         <v>117</v>
       </c>
@@ -6332,7 +6298,9 @@
         <v>118</v>
       </c>
       <c r="C6" s="156"/>
-      <c r="D6" s="157"/>
+      <c r="D6" s="157">
+        <v>3</v>
+      </c>
     </row>
     <row r="7" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="120" t="s">
@@ -6341,7 +6309,7 @@
       <c r="C7" s="150"/>
       <c r="D7" s="158">
         <f>SUM(C8:C13)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G7" s="120" t="s">
         <v>120</v>
@@ -6354,7 +6322,9 @@
       <c r="B8" s="159" t="s">
         <v>122</v>
       </c>
-      <c r="C8" s="160"/>
+      <c r="C8" s="160">
+        <v>0</v>
+      </c>
       <c r="D8" s="161"/>
       <c r="H8" s="120" t="s">
         <v>123</v>
@@ -6368,7 +6338,9 @@
       <c r="B9" s="159" t="s">
         <v>124</v>
       </c>
-      <c r="C9" s="154"/>
+      <c r="C9" s="154">
+        <v>0</v>
+      </c>
       <c r="D9" s="150"/>
       <c r="H9" s="120" t="s">
         <v>125</v>
@@ -6382,7 +6354,9 @@
       <c r="B10" s="159" t="s">
         <v>126</v>
       </c>
-      <c r="C10" s="154"/>
+      <c r="C10" s="154">
+        <v>1</v>
+      </c>
       <c r="D10" s="150"/>
       <c r="H10" s="120" t="s">
         <v>127</v>
@@ -6397,7 +6371,9 @@
       <c r="B11" s="159" t="s">
         <v>128</v>
       </c>
-      <c r="C11" s="154"/>
+      <c r="C11" s="154">
+        <v>1</v>
+      </c>
       <c r="D11" s="150"/>
       <c r="I11" s="162"/>
       <c r="K11" s="162"/>
@@ -6406,7 +6382,9 @@
       <c r="B12" s="159" t="s">
         <v>129</v>
       </c>
-      <c r="C12" s="154"/>
+      <c r="C12" s="154">
+        <v>0</v>
+      </c>
       <c r="D12" s="150"/>
       <c r="I12" s="162"/>
       <c r="K12" s="162"/>
@@ -6415,7 +6393,9 @@
       <c r="B13" s="159" t="s">
         <v>130</v>
       </c>
-      <c r="C13" s="154"/>
+      <c r="C13" s="154">
+        <v>4</v>
+      </c>
       <c r="M13" s="118"/>
       <c r="O13" s="166" t="s">
         <v>131</v>
@@ -6455,7 +6435,7 @@
       </c>
       <c r="C16" s="150"/>
       <c r="D16" s="151">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H16" s="120" t="s">
         <v>139</v>
@@ -6507,7 +6487,7 @@
         <v>1</v>
       </c>
       <c r="D20" s="150"/>
-      <c r="F20" s="243" t="s">
+      <c r="F20" s="329" t="s">
         <v>144</v>
       </c>
       <c r="G20" s="244"/>
@@ -6535,7 +6515,7 @@
       <c r="C21" s="150"/>
       <c r="D21" s="168">
         <f>SUM(D16:D17)-D18</f>
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="I21" s="166" t="s">
         <v>150</v>
@@ -6604,7 +6584,7 @@
       </c>
       <c r="J23" s="124"/>
       <c r="K23" s="172">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L23" s="124"/>
       <c r="M23" s="172">
@@ -6621,7 +6601,7 @@
       <c r="R23" s="124"/>
       <c r="S23" s="171">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -6643,7 +6623,7 @@
       </c>
       <c r="J24" s="124"/>
       <c r="K24" s="172">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L24" s="124"/>
       <c r="M24" s="172">
@@ -6660,7 +6640,7 @@
       <c r="R24" s="124"/>
       <c r="S24" s="171">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -6980,7 +6960,7 @@
       <c r="J33" s="174"/>
       <c r="K33" s="171">
         <f>SUM(K22:K32)</f>
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L33" s="175"/>
       <c r="M33" s="171">
@@ -6999,7 +6979,7 @@
       </c>
       <c r="S33" s="171">
         <f>SUM(S22:S32)</f>
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="34" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -7134,7 +7114,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="316" t="s">
+      <c r="A1" s="251" t="s">
         <v>185</v>
       </c>
       <c r="B1" s="244"/>
@@ -7207,7 +7187,9 @@
       <c r="R3" s="120" t="s">
         <v>189</v>
       </c>
-      <c r="Z3" s="181"/>
+      <c r="Z3" s="181">
+        <v>4</v>
+      </c>
     </row>
     <row r="4" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="H4" s="165"/>
@@ -7223,7 +7205,7 @@
       <c r="B5" s="120" t="s">
         <v>110</v>
       </c>
-      <c r="C5" s="328" t="s">
+      <c r="C5" s="243" t="s">
         <v>190</v>
       </c>
       <c r="D5" s="244"/>
@@ -7248,7 +7230,7 @@
       <c r="Z5" s="183"/>
     </row>
     <row r="6" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C6" s="328" t="s">
+      <c r="C6" s="243" t="s">
         <v>192</v>
       </c>
       <c r="D6" s="244"/>
@@ -7259,21 +7241,21 @@
         <v>0</v>
       </c>
       <c r="N6" s="180"/>
-      <c r="R6" s="330" t="s">
+      <c r="R6" s="249" t="s">
         <v>193</v>
       </c>
-      <c r="S6" s="323"/>
-      <c r="T6" s="323"/>
-      <c r="U6" s="323"/>
-      <c r="V6" s="323"/>
-      <c r="W6" s="323"/>
-      <c r="X6" s="323"/>
-      <c r="Y6" s="323"/>
-      <c r="Z6" s="323"/>
+      <c r="S6" s="250"/>
+      <c r="T6" s="250"/>
+      <c r="U6" s="250"/>
+      <c r="V6" s="250"/>
+      <c r="W6" s="250"/>
+      <c r="X6" s="250"/>
+      <c r="Y6" s="250"/>
+      <c r="Z6" s="250"/>
       <c r="AA6" s="184"/>
     </row>
     <row r="7" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C7" s="328" t="s">
+      <c r="C7" s="243" t="s">
         <v>194</v>
       </c>
       <c r="D7" s="244"/>
@@ -7284,15 +7266,15 @@
         <v>0</v>
       </c>
       <c r="N7" s="180"/>
-      <c r="R7" s="323"/>
-      <c r="S7" s="323"/>
-      <c r="T7" s="323"/>
-      <c r="U7" s="323"/>
-      <c r="V7" s="323"/>
-      <c r="W7" s="323"/>
-      <c r="X7" s="323"/>
-      <c r="Y7" s="323"/>
-      <c r="Z7" s="323"/>
+      <c r="R7" s="250"/>
+      <c r="S7" s="250"/>
+      <c r="T7" s="250"/>
+      <c r="U7" s="250"/>
+      <c r="V7" s="250"/>
+      <c r="W7" s="250"/>
+      <c r="X7" s="250"/>
+      <c r="Y7" s="250"/>
+      <c r="Z7" s="250"/>
       <c r="AA7" s="184"/>
     </row>
     <row r="8" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -7306,15 +7288,15 @@
         <v>0</v>
       </c>
       <c r="N8" s="180"/>
-      <c r="R8" s="323"/>
-      <c r="S8" s="323"/>
-      <c r="T8" s="323"/>
-      <c r="U8" s="323"/>
-      <c r="V8" s="323"/>
-      <c r="W8" s="323"/>
-      <c r="X8" s="323"/>
-      <c r="Y8" s="323"/>
-      <c r="Z8" s="323"/>
+      <c r="R8" s="250"/>
+      <c r="S8" s="250"/>
+      <c r="T8" s="250"/>
+      <c r="U8" s="250"/>
+      <c r="V8" s="250"/>
+      <c r="W8" s="250"/>
+      <c r="X8" s="250"/>
+      <c r="Y8" s="250"/>
+      <c r="Z8" s="250"/>
       <c r="AA8" s="184"/>
     </row>
     <row r="9" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7329,15 +7311,15 @@
         <v>197</v>
       </c>
       <c r="N9" s="180"/>
-      <c r="R9" s="320"/>
-      <c r="S9" s="320"/>
-      <c r="T9" s="320"/>
-      <c r="U9" s="320"/>
-      <c r="V9" s="320"/>
-      <c r="W9" s="320"/>
-      <c r="X9" s="320"/>
-      <c r="Y9" s="320"/>
-      <c r="Z9" s="320"/>
+      <c r="R9" s="248"/>
+      <c r="S9" s="248"/>
+      <c r="T9" s="248"/>
+      <c r="U9" s="248"/>
+      <c r="V9" s="248"/>
+      <c r="W9" s="248"/>
+      <c r="X9" s="248"/>
+      <c r="Y9" s="248"/>
+      <c r="Z9" s="248"/>
       <c r="AA9" s="148"/>
     </row>
     <row r="10" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -7415,7 +7397,7 @@
       <c r="N14" s="180"/>
     </row>
     <row r="15" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C15" s="328" t="s">
+      <c r="C15" s="243" t="s">
         <v>192</v>
       </c>
       <c r="D15" s="244"/>
@@ -7435,7 +7417,7 @@
       <c r="AA15" s="148"/>
     </row>
     <row r="16" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C16" s="328" t="s">
+      <c r="C16" s="243" t="s">
         <v>194</v>
       </c>
       <c r="D16" s="244"/>
@@ -7527,7 +7509,7 @@
       <c r="N21" s="180"/>
     </row>
     <row r="23" spans="1:27" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="324" t="s">
+      <c r="A23" s="257" t="s">
         <v>211</v>
       </c>
       <c r="B23" s="244"/>
@@ -7561,88 +7543,88 @@
       <c r="A26" s="148"/>
       <c r="B26" s="193"/>
       <c r="C26" s="193"/>
-      <c r="D26" s="319" t="s">
-        <v>233</v>
-      </c>
-      <c r="E26" s="320"/>
-      <c r="F26" s="320"/>
-      <c r="G26" s="320"/>
-      <c r="H26" s="320"/>
-      <c r="I26" s="320"/>
-      <c r="J26" s="320"/>
-      <c r="K26" s="320"/>
-      <c r="L26" s="320"/>
+      <c r="D26" s="247" t="s">
+        <v>229</v>
+      </c>
+      <c r="E26" s="248"/>
+      <c r="F26" s="248"/>
+      <c r="G26" s="248"/>
+      <c r="H26" s="248"/>
+      <c r="I26" s="248"/>
+      <c r="J26" s="248"/>
+      <c r="K26" s="248"/>
+      <c r="L26" s="248"/>
       <c r="M26" s="193"/>
       <c r="N26" s="193"/>
       <c r="O26" s="148"/>
       <c r="P26" s="148"/>
       <c r="Q26" s="148"/>
-      <c r="R26" s="319" t="s">
-        <v>231</v>
-      </c>
-      <c r="S26" s="320"/>
-      <c r="T26" s="320"/>
-      <c r="U26" s="320"/>
-      <c r="V26" s="320"/>
-      <c r="W26" s="320"/>
-      <c r="X26" s="320"/>
-      <c r="Y26" s="320"/>
-      <c r="Z26" s="320"/>
+      <c r="R26" s="247" t="s">
+        <v>227</v>
+      </c>
+      <c r="S26" s="248"/>
+      <c r="T26" s="248"/>
+      <c r="U26" s="248"/>
+      <c r="V26" s="248"/>
+      <c r="W26" s="248"/>
+      <c r="X26" s="248"/>
+      <c r="Y26" s="248"/>
+      <c r="Z26" s="248"/>
       <c r="AA26" s="148"/>
     </row>
     <row r="27" spans="1:27" x14ac:dyDescent="0.25">
       <c r="C27" s="148"/>
-      <c r="D27" s="325" t="s">
-        <v>234</v>
-      </c>
-      <c r="E27" s="326"/>
-      <c r="F27" s="326"/>
-      <c r="G27" s="326"/>
-      <c r="H27" s="326"/>
-      <c r="I27" s="326"/>
-      <c r="J27" s="326"/>
-      <c r="K27" s="326"/>
-      <c r="L27" s="326"/>
+      <c r="D27" s="245" t="s">
+        <v>230</v>
+      </c>
+      <c r="E27" s="246"/>
+      <c r="F27" s="246"/>
+      <c r="G27" s="246"/>
+      <c r="H27" s="246"/>
+      <c r="I27" s="246"/>
+      <c r="J27" s="246"/>
+      <c r="K27" s="246"/>
+      <c r="L27" s="246"/>
       <c r="M27" s="148"/>
       <c r="N27" s="148"/>
       <c r="O27" s="148"/>
       <c r="P27" s="148"/>
       <c r="Q27" s="148"/>
-      <c r="R27" s="325" t="s">
-        <v>232</v>
-      </c>
-      <c r="S27" s="326"/>
-      <c r="T27" s="326"/>
-      <c r="U27" s="326"/>
-      <c r="V27" s="326"/>
-      <c r="W27" s="326"/>
-      <c r="X27" s="326"/>
-      <c r="Y27" s="326"/>
-      <c r="Z27" s="326"/>
+      <c r="R27" s="245" t="s">
+        <v>228</v>
+      </c>
+      <c r="S27" s="246"/>
+      <c r="T27" s="246"/>
+      <c r="U27" s="246"/>
+      <c r="V27" s="246"/>
+      <c r="W27" s="246"/>
+      <c r="X27" s="246"/>
+      <c r="Y27" s="246"/>
+      <c r="Z27" s="246"/>
       <c r="AA27" s="148"/>
     </row>
     <row r="28" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="D28" s="322"/>
-      <c r="E28" s="323"/>
-      <c r="F28" s="323"/>
-      <c r="G28" s="323"/>
-      <c r="H28" s="323"/>
-      <c r="I28" s="323"/>
-      <c r="J28" s="323"/>
-      <c r="K28" s="323"/>
-      <c r="L28" s="323"/>
-      <c r="R28" s="322"/>
-      <c r="S28" s="323"/>
-      <c r="T28" s="323"/>
-      <c r="U28" s="323"/>
-      <c r="V28" s="323"/>
-      <c r="W28" s="323"/>
-      <c r="X28" s="323"/>
-      <c r="Y28" s="323"/>
-      <c r="Z28" s="323"/>
+      <c r="D28" s="256"/>
+      <c r="E28" s="250"/>
+      <c r="F28" s="250"/>
+      <c r="G28" s="250"/>
+      <c r="H28" s="250"/>
+      <c r="I28" s="250"/>
+      <c r="J28" s="250"/>
+      <c r="K28" s="250"/>
+      <c r="L28" s="250"/>
+      <c r="R28" s="256"/>
+      <c r="S28" s="250"/>
+      <c r="T28" s="250"/>
+      <c r="U28" s="250"/>
+      <c r="V28" s="250"/>
+      <c r="W28" s="250"/>
+      <c r="X28" s="250"/>
+      <c r="Y28" s="250"/>
+      <c r="Z28" s="250"/>
     </row>
     <row r="29" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="D29" s="308" t="s">
+      <c r="D29" s="254" t="s">
         <v>212</v>
       </c>
       <c r="E29" s="244"/>
@@ -7762,7 +7744,7 @@
       <c r="AA33" s="165"/>
     </row>
     <row r="34" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="308" t="s">
+      <c r="A34" s="254" t="s">
         <v>216</v>
       </c>
       <c r="B34" s="244"/>
@@ -7774,24 +7756,24 @@
       <c r="H34" s="165" t="s">
         <v>217</v>
       </c>
-      <c r="I34" s="321" t="s">
-        <v>235</v>
-      </c>
-      <c r="J34" s="320"/>
-      <c r="K34" s="320"/>
-      <c r="L34" s="320"/>
-      <c r="M34" s="320"/>
-      <c r="N34" s="320"/>
+      <c r="I34" s="255" t="s">
+        <v>231</v>
+      </c>
+      <c r="J34" s="248"/>
+      <c r="K34" s="248"/>
+      <c r="L34" s="248"/>
+      <c r="M34" s="248"/>
+      <c r="N34" s="248"/>
       <c r="O34" s="165" t="s">
         <v>218</v>
       </c>
-      <c r="P34" s="329" t="s">
-        <v>236</v>
-      </c>
-      <c r="Q34" s="329"/>
-      <c r="R34" s="329"/>
-      <c r="S34" s="329"/>
-      <c r="T34" s="329"/>
+      <c r="P34" s="259" t="s">
+        <v>232</v>
+      </c>
+      <c r="Q34" s="259"/>
+      <c r="R34" s="259"/>
+      <c r="S34" s="259"/>
+      <c r="T34" s="259"/>
       <c r="U34" s="183"/>
       <c r="V34" s="194"/>
       <c r="W34" s="194"/>
@@ -7809,16 +7791,16 @@
       <c r="AA36" s="197"/>
     </row>
     <row r="37" spans="1:27" ht="29.1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="J37" s="327"/>
-      <c r="K37" s="320"/>
-      <c r="L37" s="320"/>
-      <c r="M37" s="320"/>
-      <c r="N37" s="320"/>
-      <c r="O37" s="320"/>
-      <c r="P37" s="320"/>
-      <c r="Q37" s="320"/>
-      <c r="R37" s="320"/>
-      <c r="S37" s="320"/>
+      <c r="J37" s="258"/>
+      <c r="K37" s="248"/>
+      <c r="L37" s="248"/>
+      <c r="M37" s="248"/>
+      <c r="N37" s="248"/>
+      <c r="O37" s="248"/>
+      <c r="P37" s="248"/>
+      <c r="Q37" s="248"/>
+      <c r="R37" s="248"/>
+      <c r="S37" s="248"/>
       <c r="T37" s="148"/>
       <c r="U37" s="148"/>
       <c r="V37" s="148"/>
@@ -7829,18 +7811,18 @@
       <c r="AA37" s="148"/>
     </row>
     <row r="38" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="J38" s="325" t="s">
+      <c r="J38" s="245" t="s">
         <v>219</v>
       </c>
-      <c r="K38" s="326"/>
-      <c r="L38" s="326"/>
-      <c r="M38" s="326"/>
-      <c r="N38" s="326"/>
-      <c r="O38" s="326"/>
-      <c r="P38" s="326"/>
-      <c r="Q38" s="326"/>
-      <c r="R38" s="326"/>
-      <c r="S38" s="326"/>
+      <c r="K38" s="246"/>
+      <c r="L38" s="246"/>
+      <c r="M38" s="246"/>
+      <c r="N38" s="246"/>
+      <c r="O38" s="246"/>
+      <c r="P38" s="246"/>
+      <c r="Q38" s="246"/>
+      <c r="R38" s="246"/>
+      <c r="S38" s="246"/>
       <c r="T38" s="148"/>
       <c r="U38" s="148"/>
       <c r="V38" s="148"/>
@@ -7851,12 +7833,12 @@
       <c r="AA38" s="148"/>
     </row>
     <row r="40" spans="1:27" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="318" t="s">
+      <c r="A40" s="253" t="s">
         <v>220</v>
       </c>
       <c r="B40" s="244"/>
       <c r="C40" s="244"/>
-      <c r="D40" s="317" t="s">
+      <c r="D40" s="252" t="s">
         <v>221</v>
       </c>
       <c r="E40" s="244"/>
@@ -7919,12 +7901,6 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="C5:G5"/>
-    <mergeCell ref="R27:Z27"/>
-    <mergeCell ref="R26:Z26"/>
-    <mergeCell ref="C16:G16"/>
-    <mergeCell ref="R6:Z9"/>
-    <mergeCell ref="C7:G7"/>
     <mergeCell ref="A1:AA1"/>
     <mergeCell ref="D40:AA40"/>
     <mergeCell ref="A40:C40"/>
@@ -7941,6 +7917,12 @@
     <mergeCell ref="C6:G6"/>
     <mergeCell ref="C15:G15"/>
     <mergeCell ref="P34:T34"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="R27:Z27"/>
+    <mergeCell ref="R26:Z26"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="R6:Z9"/>
+    <mergeCell ref="C7:G7"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0.51181102362204722" footer="0.51181102362204722"/>
@@ -7973,7 +7955,7 @@
       <c r="H30" s="332"/>
       <c r="I30" s="332"/>
       <c r="J30" s="332"/>
-      <c r="K30" s="280"/>
+      <c r="K30" s="287"/>
     </row>
     <row r="31" spans="4:11" x14ac:dyDescent="0.2">
       <c r="D31" s="201"/>
@@ -7989,7 +7971,7 @@
       <c r="H32" s="332"/>
       <c r="I32" s="332"/>
       <c r="J32" s="332"/>
-      <c r="K32" s="280"/>
+      <c r="K32" s="287"/>
     </row>
     <row r="33" spans="4:11" x14ac:dyDescent="0.2">
       <c r="D33" s="201"/>
@@ -8005,7 +7987,7 @@
       <c r="H34" s="332"/>
       <c r="I34" s="332"/>
       <c r="J34" s="332"/>
-      <c r="K34" s="280"/>
+      <c r="K34" s="287"/>
     </row>
     <row r="35" spans="4:11" x14ac:dyDescent="0.2">
       <c r="D35" s="201"/>
